--- a/data/modeles_recepta/P3_Autoroute_2x3_5km.xlsx
+++ b/data/modeles_recepta/P3_Autoroute_2x3_5km.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEGENDE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LEGENDE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PK_Coordonnees" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="OFFSETS_TRANSVERSAUX" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PK_Coordonnees'!$A$3:$F$205</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="+0.000;-0.000;0.000"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +72,77 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="000F4C35"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00475569"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F766E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -135,8 +214,58 @@
         <fgColor rgb="000D1F38"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F4C35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,11 +287,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -239,6 +382,87 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -313,36 +537,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9334500" cy="3429000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27106,6 +27300,4921 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F207"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>COORDONNÉES DE L'AXE — Autoroute 2x3 voies — 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Système de référence : Lambert 93 (EPSG:2154)  —  Données à renseigner avec les coordonnées réelles du levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>X (m)</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Y (m)</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Z axe (m)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Gisement (°)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>Dist. cumulée (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Point kilométrique</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Lambert 93 — Est</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Lambert 93 — Nord</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>Cote NGF de l'axe chaussée</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Direction route (0°=N, 90°=E)</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>Distance depuis l'origine</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>0+000</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n">
+        <v>836100</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>6512500</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>0+025</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n">
+        <v>836107.764</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>6512523.764</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>112.513</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>18.0937</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>0+050</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n">
+        <v>836115.606</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>6512547.502</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>112.575</v>
+      </c>
+      <c r="E7" s="38" t="n">
+        <v>18.1874</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>0+075</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>836123.526</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>6512571.215</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>112.638</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>18.2808</v>
+      </c>
+      <c r="F8" s="39" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>0+100</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="n">
+        <v>836131.522</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>6512594.902</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>18.374</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>0+125</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>836139.594</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>6512618.563</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>112.763</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>18.4668</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>0+150</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>836147.743</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>6512642.199</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>112.825</v>
+      </c>
+      <c r="E11" s="38" t="n">
+        <v>18.5592</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>0+175</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>836155.966</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>6512665.81</v>
+      </c>
+      <c r="D12" s="37" t="n">
+        <v>112.888</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>18.651</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>0+200</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n">
+        <v>836164.262</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>6512689.395</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>18.7422</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>0+225</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="n">
+        <v>836172.6310000001</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>6512712.955</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>113.013</v>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>18.8327</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>0+250</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="n">
+        <v>836181.071</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>6512736.49</v>
+      </c>
+      <c r="D15" s="37" t="n">
+        <v>113.075</v>
+      </c>
+      <c r="E15" s="38" t="n">
+        <v>18.9223</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>0+275</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n">
+        <v>836189.581</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>6512760</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>113.138</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>19.0111</v>
+      </c>
+      <c r="F16" s="39" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>0+300</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>836198.16</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>6512783.487</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>19.0988</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>0+325</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="n">
+        <v>836206.804</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>6512806.949</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>113.263</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>19.1855</v>
+      </c>
+      <c r="F18" s="39" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>0+350</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="n">
+        <v>836215.513</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>6512830.389</v>
+      </c>
+      <c r="D19" s="37" t="n">
+        <v>113.325</v>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>19.271</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>0+375</t>
+        </is>
+      </c>
+      <c r="B20" s="36" t="n">
+        <v>836224.285</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>6512853.806</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <v>113.388</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>19.3553</v>
+      </c>
+      <c r="F20" s="39" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>0+400</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>836233.116</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>6512877.2</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>19.4383</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>0+425</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n">
+        <v>836242.007</v>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>6512900.573</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <v>113.513</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>19.5198</v>
+      </c>
+      <c r="F22" s="39" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>0+450</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="n">
+        <v>836250.953</v>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>6512923.926</v>
+      </c>
+      <c r="D23" s="37" t="n">
+        <v>113.575</v>
+      </c>
+      <c r="E23" s="38" t="n">
+        <v>19.5999</v>
+      </c>
+      <c r="F23" s="39" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>0+475</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n">
+        <v>836259.952</v>
+      </c>
+      <c r="C24" s="36" t="n">
+        <v>6512947.259</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>113.638</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>19.6784</v>
+      </c>
+      <c r="F24" s="39" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>0+500</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n">
+        <v>836269.002</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <v>6512970.572</v>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>19.7553</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>0+525</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n">
+        <v>836278.1</v>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>6512993.868</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>113.763</v>
+      </c>
+      <c r="E26" s="38" t="n">
+        <v>19.8305</v>
+      </c>
+      <c r="F26" s="39" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>0+550</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n">
+        <v>836287.243</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>6513017.146</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>113.825</v>
+      </c>
+      <c r="E27" s="38" t="n">
+        <v>19.9038</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>0+575</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n">
+        <v>836296.429</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>6513040.408</v>
+      </c>
+      <c r="D28" s="37" t="n">
+        <v>113.888</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>19.9753</v>
+      </c>
+      <c r="F28" s="39" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>0+600</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n">
+        <v>836305.654</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>6513063.655</v>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="E29" s="33" t="n">
+        <v>20.0449</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>0+625</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n">
+        <v>836314.915</v>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>6513086.887</v>
+      </c>
+      <c r="D30" s="37" t="n">
+        <v>114.013</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>20.1125</v>
+      </c>
+      <c r="F30" s="39" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>0+650</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>836324.21</v>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>6513110.106</v>
+      </c>
+      <c r="D31" s="37" t="n">
+        <v>114.075</v>
+      </c>
+      <c r="E31" s="38" t="n">
+        <v>20.178</v>
+      </c>
+      <c r="F31" s="39" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>0+675</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>836333.534</v>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>6513133.314</v>
+      </c>
+      <c r="D32" s="37" t="n">
+        <v>114.138</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>20.2414</v>
+      </c>
+      <c r="F32" s="39" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>0+700</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="n">
+        <v>836342.885</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>6513156.511</v>
+      </c>
+      <c r="D33" s="32" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>20.3026</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>0+725</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="n">
+        <v>836352.259</v>
+      </c>
+      <c r="C34" s="36" t="n">
+        <v>6513179.699</v>
+      </c>
+      <c r="D34" s="37" t="n">
+        <v>114.263</v>
+      </c>
+      <c r="E34" s="38" t="n">
+        <v>20.3616</v>
+      </c>
+      <c r="F34" s="39" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>0+750</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n">
+        <v>836361.653</v>
+      </c>
+      <c r="C35" s="36" t="n">
+        <v>6513202.878</v>
+      </c>
+      <c r="D35" s="37" t="n">
+        <v>114.325</v>
+      </c>
+      <c r="E35" s="38" t="n">
+        <v>20.4182</v>
+      </c>
+      <c r="F35" s="39" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>0+775</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="n">
+        <v>836371.063</v>
+      </c>
+      <c r="C36" s="36" t="n">
+        <v>6513226.051</v>
+      </c>
+      <c r="D36" s="37" t="n">
+        <v>114.388</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>20.4725</v>
+      </c>
+      <c r="F36" s="39" t="n">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>0+800</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n">
+        <v>836380.485</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>6513249.218</v>
+      </c>
+      <c r="D37" s="32" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="E37" s="33" t="n">
+        <v>20.5244</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>0+825</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n">
+        <v>836389.917</v>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>6513272.382</v>
+      </c>
+      <c r="D38" s="37" t="n">
+        <v>114.513</v>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>20.5738</v>
+      </c>
+      <c r="F38" s="39" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>0+850</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="n">
+        <v>836399.353</v>
+      </c>
+      <c r="C39" s="36" t="n">
+        <v>6513295.542</v>
+      </c>
+      <c r="D39" s="37" t="n">
+        <v>114.575</v>
+      </c>
+      <c r="E39" s="38" t="n">
+        <v>20.6207</v>
+      </c>
+      <c r="F39" s="39" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>0+875</t>
+        </is>
+      </c>
+      <c r="B40" s="36" t="n">
+        <v>836408.791</v>
+      </c>
+      <c r="C40" s="36" t="n">
+        <v>6513318.702</v>
+      </c>
+      <c r="D40" s="37" t="n">
+        <v>114.638</v>
+      </c>
+      <c r="E40" s="38" t="n">
+        <v>20.6651</v>
+      </c>
+      <c r="F40" s="39" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>0+900</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>836418.227</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>6513341.862</v>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="E41" s="33" t="n">
+        <v>20.7068</v>
+      </c>
+      <c r="F41" s="34" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>0+925</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="n">
+        <v>836427.657</v>
+      </c>
+      <c r="C42" s="36" t="n">
+        <v>6513365.024</v>
+      </c>
+      <c r="D42" s="37" t="n">
+        <v>114.763</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>20.7459</v>
+      </c>
+      <c r="F42" s="39" t="n">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>0+950</t>
+        </is>
+      </c>
+      <c r="B43" s="36" t="n">
+        <v>836437.077</v>
+      </c>
+      <c r="C43" s="36" t="n">
+        <v>6513388.189</v>
+      </c>
+      <c r="D43" s="37" t="n">
+        <v>114.825</v>
+      </c>
+      <c r="E43" s="38" t="n">
+        <v>20.7823</v>
+      </c>
+      <c r="F43" s="39" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>0+975</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="n">
+        <v>836446.4840000001</v>
+      </c>
+      <c r="C44" s="36" t="n">
+        <v>6513411.358</v>
+      </c>
+      <c r="D44" s="37" t="n">
+        <v>114.888</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <v>20.816</v>
+      </c>
+      <c r="F44" s="39" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>1+000</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>836455.873</v>
+      </c>
+      <c r="C45" s="31" t="n">
+        <v>6513434.534</v>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="E45" s="33" t="n">
+        <v>20.847</v>
+      </c>
+      <c r="F45" s="34" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>1+025</t>
+        </is>
+      </c>
+      <c r="B46" s="36" t="n">
+        <v>836465.241</v>
+      </c>
+      <c r="C46" s="36" t="n">
+        <v>6513457.718</v>
+      </c>
+      <c r="D46" s="37" t="n">
+        <v>115.013</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>20.8751</v>
+      </c>
+      <c r="F46" s="39" t="n">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>1+050</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="n">
+        <v>836474.583</v>
+      </c>
+      <c r="C47" s="36" t="n">
+        <v>6513480.912</v>
+      </c>
+      <c r="D47" s="37" t="n">
+        <v>115.075</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>20.9005</v>
+      </c>
+      <c r="F47" s="39" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>1+075</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n">
+        <v>836483.897</v>
+      </c>
+      <c r="C48" s="36" t="n">
+        <v>6513504.116</v>
+      </c>
+      <c r="D48" s="37" t="n">
+        <v>115.138</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>20.923</v>
+      </c>
+      <c r="F48" s="39" t="n">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>1+100</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="n">
+        <v>836493.177</v>
+      </c>
+      <c r="C49" s="31" t="n">
+        <v>6513527.332</v>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="E49" s="33" t="n">
+        <v>20.9427</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>1+125</t>
+        </is>
+      </c>
+      <c r="B50" s="36" t="n">
+        <v>836502.421</v>
+      </c>
+      <c r="C50" s="36" t="n">
+        <v>6513550.563</v>
+      </c>
+      <c r="D50" s="37" t="n">
+        <v>115.263</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>20.9595</v>
+      </c>
+      <c r="F50" s="39" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>1+150</t>
+        </is>
+      </c>
+      <c r="B51" s="36" t="n">
+        <v>836511.624</v>
+      </c>
+      <c r="C51" s="36" t="n">
+        <v>6513573.809</v>
+      </c>
+      <c r="D51" s="37" t="n">
+        <v>115.325</v>
+      </c>
+      <c r="E51" s="38" t="n">
+        <v>20.9734</v>
+      </c>
+      <c r="F51" s="39" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>1+175</t>
+        </is>
+      </c>
+      <c r="B52" s="36" t="n">
+        <v>836520.784</v>
+      </c>
+      <c r="C52" s="36" t="n">
+        <v>6513597.072</v>
+      </c>
+      <c r="D52" s="37" t="n">
+        <v>115.388</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>20.9844</v>
+      </c>
+      <c r="F52" s="39" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>1+200</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="n">
+        <v>836529.895</v>
+      </c>
+      <c r="C53" s="31" t="n">
+        <v>6513620.353</v>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="E53" s="33" t="n">
+        <v>20.9925</v>
+      </c>
+      <c r="F53" s="34" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>1+225</t>
+        </is>
+      </c>
+      <c r="B54" s="36" t="n">
+        <v>836538.954</v>
+      </c>
+      <c r="C54" s="36" t="n">
+        <v>6513643.654</v>
+      </c>
+      <c r="D54" s="37" t="n">
+        <v>115.513</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>20.9977</v>
+      </c>
+      <c r="F54" s="39" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="inlineStr">
+        <is>
+          <t>1+250</t>
+        </is>
+      </c>
+      <c r="B55" s="36" t="n">
+        <v>836547.958</v>
+      </c>
+      <c r="C55" s="36" t="n">
+        <v>6513666.976</v>
+      </c>
+      <c r="D55" s="37" t="n">
+        <v>115.575</v>
+      </c>
+      <c r="E55" s="38" t="n">
+        <v>20.9999</v>
+      </c>
+      <c r="F55" s="39" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="inlineStr">
+        <is>
+          <t>1+275</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n">
+        <v>836556.903</v>
+      </c>
+      <c r="C56" s="36" t="n">
+        <v>6513690.321</v>
+      </c>
+      <c r="D56" s="37" t="n">
+        <v>115.638</v>
+      </c>
+      <c r="E56" s="38" t="n">
+        <v>20.9992</v>
+      </c>
+      <c r="F56" s="39" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="30" t="inlineStr">
+        <is>
+          <t>1+300</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="n">
+        <v>836565.785</v>
+      </c>
+      <c r="C57" s="31" t="n">
+        <v>6513713.69</v>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="E57" s="33" t="n">
+        <v>20.9956</v>
+      </c>
+      <c r="F57" s="34" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="35" t="inlineStr">
+        <is>
+          <t>1+325</t>
+        </is>
+      </c>
+      <c r="B58" s="36" t="n">
+        <v>836574.601</v>
+      </c>
+      <c r="C58" s="36" t="n">
+        <v>6513737.085</v>
+      </c>
+      <c r="D58" s="37" t="n">
+        <v>115.763</v>
+      </c>
+      <c r="E58" s="38" t="n">
+        <v>20.9891</v>
+      </c>
+      <c r="F58" s="39" t="n">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="35" t="inlineStr">
+        <is>
+          <t>1+350</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="n">
+        <v>836583.348</v>
+      </c>
+      <c r="C59" s="36" t="n">
+        <v>6513760.506</v>
+      </c>
+      <c r="D59" s="37" t="n">
+        <v>115.825</v>
+      </c>
+      <c r="E59" s="38" t="n">
+        <v>20.9796</v>
+      </c>
+      <c r="F59" s="39" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="35" t="inlineStr">
+        <is>
+          <t>1+375</t>
+        </is>
+      </c>
+      <c r="B60" s="36" t="n">
+        <v>836592.022</v>
+      </c>
+      <c r="C60" s="36" t="n">
+        <v>6513783.955</v>
+      </c>
+      <c r="D60" s="37" t="n">
+        <v>115.888</v>
+      </c>
+      <c r="E60" s="38" t="n">
+        <v>20.9672</v>
+      </c>
+      <c r="F60" s="39" t="n">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>1+400</t>
+        </is>
+      </c>
+      <c r="B61" s="31" t="n">
+        <v>836600.6189999999</v>
+      </c>
+      <c r="C61" s="31" t="n">
+        <v>6513807.433</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="E61" s="33" t="n">
+        <v>20.952</v>
+      </c>
+      <c r="F61" s="34" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="35" t="inlineStr">
+        <is>
+          <t>1+425</t>
+        </is>
+      </c>
+      <c r="B62" s="36" t="n">
+        <v>836609.137</v>
+      </c>
+      <c r="C62" s="36" t="n">
+        <v>6513830.941</v>
+      </c>
+      <c r="D62" s="37" t="n">
+        <v>116.013</v>
+      </c>
+      <c r="E62" s="38" t="n">
+        <v>20.9338</v>
+      </c>
+      <c r="F62" s="39" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="35" t="inlineStr">
+        <is>
+          <t>1+450</t>
+        </is>
+      </c>
+      <c r="B63" s="36" t="n">
+        <v>836617.573</v>
+      </c>
+      <c r="C63" s="36" t="n">
+        <v>6513854.481</v>
+      </c>
+      <c r="D63" s="37" t="n">
+        <v>116.075</v>
+      </c>
+      <c r="E63" s="38" t="n">
+        <v>20.9128</v>
+      </c>
+      <c r="F63" s="39" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="35" t="inlineStr">
+        <is>
+          <t>1+475</t>
+        </is>
+      </c>
+      <c r="B64" s="36" t="n">
+        <v>836625.922</v>
+      </c>
+      <c r="C64" s="36" t="n">
+        <v>6513878.053</v>
+      </c>
+      <c r="D64" s="37" t="n">
+        <v>116.138</v>
+      </c>
+      <c r="E64" s="38" t="n">
+        <v>20.8889</v>
+      </c>
+      <c r="F64" s="39" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>1+500</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="n">
+        <v>836634.184</v>
+      </c>
+      <c r="C65" s="31" t="n">
+        <v>6513901.659</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="E65" s="33" t="n">
+        <v>20.8623</v>
+      </c>
+      <c r="F65" s="34" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t>1+525</t>
+        </is>
+      </c>
+      <c r="B66" s="36" t="n">
+        <v>836642.3540000001</v>
+      </c>
+      <c r="C66" s="36" t="n">
+        <v>6513925.299</v>
+      </c>
+      <c r="D66" s="37" t="n">
+        <v>116.263</v>
+      </c>
+      <c r="E66" s="38" t="n">
+        <v>20.8328</v>
+      </c>
+      <c r="F66" s="39" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="35" t="inlineStr">
+        <is>
+          <t>1+550</t>
+        </is>
+      </c>
+      <c r="B67" s="36" t="n">
+        <v>836650.4300000001</v>
+      </c>
+      <c r="C67" s="36" t="n">
+        <v>6513948.975</v>
+      </c>
+      <c r="D67" s="37" t="n">
+        <v>116.325</v>
+      </c>
+      <c r="E67" s="38" t="n">
+        <v>20.8005</v>
+      </c>
+      <c r="F67" s="39" t="n">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="35" t="inlineStr">
+        <is>
+          <t>1+575</t>
+        </is>
+      </c>
+      <c r="B68" s="36" t="n">
+        <v>836658.409</v>
+      </c>
+      <c r="C68" s="36" t="n">
+        <v>6513972.686</v>
+      </c>
+      <c r="D68" s="37" t="n">
+        <v>116.388</v>
+      </c>
+      <c r="E68" s="38" t="n">
+        <v>20.7656</v>
+      </c>
+      <c r="F68" s="39" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>1+600</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>836666.2879999999</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>6513996.435</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="E69" s="33" t="n">
+        <v>20.7279</v>
+      </c>
+      <c r="F69" s="34" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t>1+625</t>
+        </is>
+      </c>
+      <c r="B70" s="36" t="n">
+        <v>836674.066</v>
+      </c>
+      <c r="C70" s="36" t="n">
+        <v>6514020.221</v>
+      </c>
+      <c r="D70" s="37" t="n">
+        <v>116.513</v>
+      </c>
+      <c r="E70" s="38" t="n">
+        <v>20.6876</v>
+      </c>
+      <c r="F70" s="39" t="n">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="35" t="inlineStr">
+        <is>
+          <t>1+650</t>
+        </is>
+      </c>
+      <c r="B71" s="36" t="n">
+        <v>836681.741</v>
+      </c>
+      <c r="C71" s="36" t="n">
+        <v>6514044.046</v>
+      </c>
+      <c r="D71" s="37" t="n">
+        <v>116.575</v>
+      </c>
+      <c r="E71" s="38" t="n">
+        <v>20.6446</v>
+      </c>
+      <c r="F71" s="39" t="n">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="35" t="inlineStr">
+        <is>
+          <t>1+675</t>
+        </is>
+      </c>
+      <c r="B72" s="36" t="n">
+        <v>836689.309</v>
+      </c>
+      <c r="C72" s="36" t="n">
+        <v>6514067.91</v>
+      </c>
+      <c r="D72" s="37" t="n">
+        <v>116.638</v>
+      </c>
+      <c r="E72" s="38" t="n">
+        <v>20.599</v>
+      </c>
+      <c r="F72" s="39" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>1+700</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>836696.769</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>6514091.813</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="E73" s="33" t="n">
+        <v>20.551</v>
+      </c>
+      <c r="F73" s="34" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="35" t="inlineStr">
+        <is>
+          <t>1+725</t>
+        </is>
+      </c>
+      <c r="B74" s="36" t="n">
+        <v>836704.1189999999</v>
+      </c>
+      <c r="C74" s="36" t="n">
+        <v>6514115.755</v>
+      </c>
+      <c r="D74" s="37" t="n">
+        <v>116.763</v>
+      </c>
+      <c r="E74" s="38" t="n">
+        <v>20.5004</v>
+      </c>
+      <c r="F74" s="39" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="35" t="inlineStr">
+        <is>
+          <t>1+750</t>
+        </is>
+      </c>
+      <c r="B75" s="36" t="n">
+        <v>836711.357</v>
+      </c>
+      <c r="C75" s="36" t="n">
+        <v>6514139.739</v>
+      </c>
+      <c r="D75" s="37" t="n">
+        <v>116.825</v>
+      </c>
+      <c r="E75" s="38" t="n">
+        <v>20.4474</v>
+      </c>
+      <c r="F75" s="39" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="35" t="inlineStr">
+        <is>
+          <t>1+775</t>
+        </is>
+      </c>
+      <c r="B76" s="36" t="n">
+        <v>836718.482</v>
+      </c>
+      <c r="C76" s="36" t="n">
+        <v>6514163.762</v>
+      </c>
+      <c r="D76" s="37" t="n">
+        <v>116.888</v>
+      </c>
+      <c r="E76" s="38" t="n">
+        <v>20.392</v>
+      </c>
+      <c r="F76" s="39" t="n">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>1+800</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>836725.492</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>6514187.827</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="E77" s="33" t="n">
+        <v>20.3342</v>
+      </c>
+      <c r="F77" s="34" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="35" t="inlineStr">
+        <is>
+          <t>1+825</t>
+        </is>
+      </c>
+      <c r="B78" s="36" t="n">
+        <v>836732.387</v>
+      </c>
+      <c r="C78" s="36" t="n">
+        <v>6514211.932</v>
+      </c>
+      <c r="D78" s="37" t="n">
+        <v>117.013</v>
+      </c>
+      <c r="E78" s="38" t="n">
+        <v>20.2742</v>
+      </c>
+      <c r="F78" s="39" t="n">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="35" t="inlineStr">
+        <is>
+          <t>1+850</t>
+        </is>
+      </c>
+      <c r="B79" s="36" t="n">
+        <v>836739.164</v>
+      </c>
+      <c r="C79" s="36" t="n">
+        <v>6514236.079</v>
+      </c>
+      <c r="D79" s="37" t="n">
+        <v>117.075</v>
+      </c>
+      <c r="E79" s="38" t="n">
+        <v>20.212</v>
+      </c>
+      <c r="F79" s="39" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="35" t="inlineStr">
+        <is>
+          <t>1+875</t>
+        </is>
+      </c>
+      <c r="B80" s="36" t="n">
+        <v>836745.823</v>
+      </c>
+      <c r="C80" s="36" t="n">
+        <v>6514260.266</v>
+      </c>
+      <c r="D80" s="37" t="n">
+        <v>117.138</v>
+      </c>
+      <c r="E80" s="38" t="n">
+        <v>20.1476</v>
+      </c>
+      <c r="F80" s="39" t="n">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="30" t="inlineStr">
+        <is>
+          <t>1+900</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>836752.363</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>6514284.495</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="E81" s="33" t="n">
+        <v>20.0811</v>
+      </c>
+      <c r="F81" s="34" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="35" t="inlineStr">
+        <is>
+          <t>1+925</t>
+        </is>
+      </c>
+      <c r="B82" s="36" t="n">
+        <v>836758.784</v>
+      </c>
+      <c r="C82" s="36" t="n">
+        <v>6514308.764</v>
+      </c>
+      <c r="D82" s="37" t="n">
+        <v>117.263</v>
+      </c>
+      <c r="E82" s="38" t="n">
+        <v>20.0125</v>
+      </c>
+      <c r="F82" s="39" t="n">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="35" t="inlineStr">
+        <is>
+          <t>1+950</t>
+        </is>
+      </c>
+      <c r="B83" s="36" t="n">
+        <v>836765.085</v>
+      </c>
+      <c r="C83" s="36" t="n">
+        <v>6514333.074</v>
+      </c>
+      <c r="D83" s="37" t="n">
+        <v>117.325</v>
+      </c>
+      <c r="E83" s="38" t="n">
+        <v>19.942</v>
+      </c>
+      <c r="F83" s="39" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t>1+975</t>
+        </is>
+      </c>
+      <c r="B84" s="36" t="n">
+        <v>836771.265</v>
+      </c>
+      <c r="C84" s="36" t="n">
+        <v>6514357.425</v>
+      </c>
+      <c r="D84" s="37" t="n">
+        <v>117.388</v>
+      </c>
+      <c r="E84" s="38" t="n">
+        <v>19.8696</v>
+      </c>
+      <c r="F84" s="39" t="n">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="30" t="inlineStr">
+        <is>
+          <t>2+000</t>
+        </is>
+      </c>
+      <c r="B85" s="31" t="n">
+        <v>836777.325</v>
+      </c>
+      <c r="C85" s="31" t="n">
+        <v>6514381.816</v>
+      </c>
+      <c r="D85" s="32" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="E85" s="33" t="n">
+        <v>19.7954</v>
+      </c>
+      <c r="F85" s="34" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="35" t="inlineStr">
+        <is>
+          <t>2+025</t>
+        </is>
+      </c>
+      <c r="B86" s="36" t="n">
+        <v>836783.265</v>
+      </c>
+      <c r="C86" s="36" t="n">
+        <v>6514406.246</v>
+      </c>
+      <c r="D86" s="37" t="n">
+        <v>117.513</v>
+      </c>
+      <c r="E86" s="38" t="n">
+        <v>19.7194</v>
+      </c>
+      <c r="F86" s="39" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="35" t="inlineStr">
+        <is>
+          <t>2+050</t>
+        </is>
+      </c>
+      <c r="B87" s="36" t="n">
+        <v>836789.084</v>
+      </c>
+      <c r="C87" s="36" t="n">
+        <v>6514430.716</v>
+      </c>
+      <c r="D87" s="37" t="n">
+        <v>117.575</v>
+      </c>
+      <c r="E87" s="38" t="n">
+        <v>19.6418</v>
+      </c>
+      <c r="F87" s="39" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="35" t="inlineStr">
+        <is>
+          <t>2+075</t>
+        </is>
+      </c>
+      <c r="B88" s="36" t="n">
+        <v>836794.784</v>
+      </c>
+      <c r="C88" s="36" t="n">
+        <v>6514455.224</v>
+      </c>
+      <c r="D88" s="37" t="n">
+        <v>117.638</v>
+      </c>
+      <c r="E88" s="38" t="n">
+        <v>19.5625</v>
+      </c>
+      <c r="F88" s="39" t="n">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="30" t="inlineStr">
+        <is>
+          <t>2+100</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="n">
+        <v>836800.3639999999</v>
+      </c>
+      <c r="C89" s="31" t="n">
+        <v>6514479.77</v>
+      </c>
+      <c r="D89" s="32" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="E89" s="33" t="n">
+        <v>19.4818</v>
+      </c>
+      <c r="F89" s="34" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="35" t="inlineStr">
+        <is>
+          <t>2+125</t>
+        </is>
+      </c>
+      <c r="B90" s="36" t="n">
+        <v>836805.826</v>
+      </c>
+      <c r="C90" s="36" t="n">
+        <v>6514504.354</v>
+      </c>
+      <c r="D90" s="37" t="n">
+        <v>117.763</v>
+      </c>
+      <c r="E90" s="38" t="n">
+        <v>19.3995</v>
+      </c>
+      <c r="F90" s="39" t="n">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="35" t="inlineStr">
+        <is>
+          <t>2+150</t>
+        </is>
+      </c>
+      <c r="B91" s="36" t="n">
+        <v>836811.17</v>
+      </c>
+      <c r="C91" s="36" t="n">
+        <v>6514528.974</v>
+      </c>
+      <c r="D91" s="37" t="n">
+        <v>117.825</v>
+      </c>
+      <c r="E91" s="38" t="n">
+        <v>19.3159</v>
+      </c>
+      <c r="F91" s="39" t="n">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="35" t="inlineStr">
+        <is>
+          <t>2+175</t>
+        </is>
+      </c>
+      <c r="B92" s="36" t="n">
+        <v>836816.398</v>
+      </c>
+      <c r="C92" s="36" t="n">
+        <v>6514553.631</v>
+      </c>
+      <c r="D92" s="37" t="n">
+        <v>117.888</v>
+      </c>
+      <c r="E92" s="38" t="n">
+        <v>19.2311</v>
+      </c>
+      <c r="F92" s="39" t="n">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="30" t="inlineStr">
+        <is>
+          <t>2+200</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="n">
+        <v>836821.5110000001</v>
+      </c>
+      <c r="C93" s="31" t="n">
+        <v>6514578.322</v>
+      </c>
+      <c r="D93" s="32" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="E93" s="33" t="n">
+        <v>19.145</v>
+      </c>
+      <c r="F93" s="34" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="35" t="inlineStr">
+        <is>
+          <t>2+225</t>
+        </is>
+      </c>
+      <c r="B94" s="36" t="n">
+        <v>836826.5110000001</v>
+      </c>
+      <c r="C94" s="36" t="n">
+        <v>6514603.047</v>
+      </c>
+      <c r="D94" s="37" t="n">
+        <v>118.013</v>
+      </c>
+      <c r="E94" s="38" t="n">
+        <v>19.0578</v>
+      </c>
+      <c r="F94" s="39" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="35" t="inlineStr">
+        <is>
+          <t>2+250</t>
+        </is>
+      </c>
+      <c r="B95" s="36" t="n">
+        <v>836831.398</v>
+      </c>
+      <c r="C95" s="36" t="n">
+        <v>6514627.806</v>
+      </c>
+      <c r="D95" s="37" t="n">
+        <v>118.075</v>
+      </c>
+      <c r="E95" s="38" t="n">
+        <v>18.9696</v>
+      </c>
+      <c r="F95" s="39" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="35" t="inlineStr">
+        <is>
+          <t>2+275</t>
+        </is>
+      </c>
+      <c r="B96" s="36" t="n">
+        <v>836836.175</v>
+      </c>
+      <c r="C96" s="36" t="n">
+        <v>6514652.596</v>
+      </c>
+      <c r="D96" s="37" t="n">
+        <v>118.138</v>
+      </c>
+      <c r="E96" s="38" t="n">
+        <v>18.8804</v>
+      </c>
+      <c r="F96" s="39" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="30" t="inlineStr">
+        <is>
+          <t>2+300</t>
+        </is>
+      </c>
+      <c r="B97" s="31" t="n">
+        <v>836840.844</v>
+      </c>
+      <c r="C97" s="31" t="n">
+        <v>6514677.418</v>
+      </c>
+      <c r="D97" s="32" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="E97" s="33" t="n">
+        <v>18.7903</v>
+      </c>
+      <c r="F97" s="34" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="35" t="inlineStr">
+        <is>
+          <t>2+325</t>
+        </is>
+      </c>
+      <c r="B98" s="36" t="n">
+        <v>836845.407</v>
+      </c>
+      <c r="C98" s="36" t="n">
+        <v>6514702.27</v>
+      </c>
+      <c r="D98" s="37" t="n">
+        <v>118.263</v>
+      </c>
+      <c r="E98" s="38" t="n">
+        <v>18.6995</v>
+      </c>
+      <c r="F98" s="39" t="n">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="35" t="inlineStr">
+        <is>
+          <t>2+350</t>
+        </is>
+      </c>
+      <c r="B99" s="36" t="n">
+        <v>836849.867</v>
+      </c>
+      <c r="C99" s="36" t="n">
+        <v>6514727.151</v>
+      </c>
+      <c r="D99" s="37" t="n">
+        <v>118.325</v>
+      </c>
+      <c r="E99" s="38" t="n">
+        <v>18.608</v>
+      </c>
+      <c r="F99" s="39" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="35" t="inlineStr">
+        <is>
+          <t>2+375</t>
+        </is>
+      </c>
+      <c r="B100" s="36" t="n">
+        <v>836854.226</v>
+      </c>
+      <c r="C100" s="36" t="n">
+        <v>6514752.059</v>
+      </c>
+      <c r="D100" s="37" t="n">
+        <v>118.388</v>
+      </c>
+      <c r="E100" s="38" t="n">
+        <v>18.516</v>
+      </c>
+      <c r="F100" s="39" t="n">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="30" t="inlineStr">
+        <is>
+          <t>2+400</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="n">
+        <v>836858.486</v>
+      </c>
+      <c r="C101" s="31" t="n">
+        <v>6514776.993</v>
+      </c>
+      <c r="D101" s="32" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="E101" s="33" t="n">
+        <v>18.4234</v>
+      </c>
+      <c r="F101" s="34" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="35" t="inlineStr">
+        <is>
+          <t>2+425</t>
+        </is>
+      </c>
+      <c r="B102" s="36" t="n">
+        <v>836862.651</v>
+      </c>
+      <c r="C102" s="36" t="n">
+        <v>6514801.953</v>
+      </c>
+      <c r="D102" s="37" t="n">
+        <v>118.513</v>
+      </c>
+      <c r="E102" s="38" t="n">
+        <v>18.3304</v>
+      </c>
+      <c r="F102" s="39" t="n">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="35" t="inlineStr">
+        <is>
+          <t>2+450</t>
+        </is>
+      </c>
+      <c r="B103" s="36" t="n">
+        <v>836866.725</v>
+      </c>
+      <c r="C103" s="36" t="n">
+        <v>6514826.936</v>
+      </c>
+      <c r="D103" s="37" t="n">
+        <v>118.575</v>
+      </c>
+      <c r="E103" s="38" t="n">
+        <v>18.237</v>
+      </c>
+      <c r="F103" s="39" t="n">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="35" t="inlineStr">
+        <is>
+          <t>2+475</t>
+        </is>
+      </c>
+      <c r="B104" s="36" t="n">
+        <v>836870.709</v>
+      </c>
+      <c r="C104" s="36" t="n">
+        <v>6514851.942</v>
+      </c>
+      <c r="D104" s="37" t="n">
+        <v>118.638</v>
+      </c>
+      <c r="E104" s="38" t="n">
+        <v>18.1435</v>
+      </c>
+      <c r="F104" s="39" t="n">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="30" t="inlineStr">
+        <is>
+          <t>2+500</t>
+        </is>
+      </c>
+      <c r="B105" s="31" t="n">
+        <v>836874.608</v>
+      </c>
+      <c r="C105" s="31" t="n">
+        <v>6514876.969</v>
+      </c>
+      <c r="D105" s="32" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="E105" s="33" t="n">
+        <v>18.0498</v>
+      </c>
+      <c r="F105" s="34" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="35" t="inlineStr">
+        <is>
+          <t>2+525</t>
+        </is>
+      </c>
+      <c r="B106" s="36" t="n">
+        <v>836878.425</v>
+      </c>
+      <c r="C106" s="36" t="n">
+        <v>6514902.016</v>
+      </c>
+      <c r="D106" s="37" t="n">
+        <v>118.763</v>
+      </c>
+      <c r="E106" s="38" t="n">
+        <v>17.956</v>
+      </c>
+      <c r="F106" s="39" t="n">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="35" t="inlineStr">
+        <is>
+          <t>2+550</t>
+        </is>
+      </c>
+      <c r="B107" s="36" t="n">
+        <v>836882.164</v>
+      </c>
+      <c r="C107" s="36" t="n">
+        <v>6514927.081</v>
+      </c>
+      <c r="D107" s="37" t="n">
+        <v>118.825</v>
+      </c>
+      <c r="E107" s="38" t="n">
+        <v>17.8623</v>
+      </c>
+      <c r="F107" s="39" t="n">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="35" t="inlineStr">
+        <is>
+          <t>2+575</t>
+        </is>
+      </c>
+      <c r="B108" s="36" t="n">
+        <v>836885.828</v>
+      </c>
+      <c r="C108" s="36" t="n">
+        <v>6514952.162</v>
+      </c>
+      <c r="D108" s="37" t="n">
+        <v>118.888</v>
+      </c>
+      <c r="E108" s="38" t="n">
+        <v>17.7688</v>
+      </c>
+      <c r="F108" s="39" t="n">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="30" t="inlineStr">
+        <is>
+          <t>2+600</t>
+        </is>
+      </c>
+      <c r="B109" s="31" t="n">
+        <v>836889.423</v>
+      </c>
+      <c r="C109" s="31" t="n">
+        <v>6514977.259</v>
+      </c>
+      <c r="D109" s="32" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="E109" s="33" t="n">
+        <v>17.6754</v>
+      </c>
+      <c r="F109" s="34" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="35" t="inlineStr">
+        <is>
+          <t>2+625</t>
+        </is>
+      </c>
+      <c r="B110" s="36" t="n">
+        <v>836892.952</v>
+      </c>
+      <c r="C110" s="36" t="n">
+        <v>6515002.369</v>
+      </c>
+      <c r="D110" s="37" t="n">
+        <v>119.013</v>
+      </c>
+      <c r="E110" s="38" t="n">
+        <v>17.5824</v>
+      </c>
+      <c r="F110" s="39" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="35" t="inlineStr">
+        <is>
+          <t>2+650</t>
+        </is>
+      </c>
+      <c r="B111" s="36" t="n">
+        <v>836896.419</v>
+      </c>
+      <c r="C111" s="36" t="n">
+        <v>6515027.492</v>
+      </c>
+      <c r="D111" s="37" t="n">
+        <v>119.075</v>
+      </c>
+      <c r="E111" s="38" t="n">
+        <v>17.4898</v>
+      </c>
+      <c r="F111" s="39" t="n">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="35" t="inlineStr">
+        <is>
+          <t>2+675</t>
+        </is>
+      </c>
+      <c r="B112" s="36" t="n">
+        <v>836899.829</v>
+      </c>
+      <c r="C112" s="36" t="n">
+        <v>6515052.626</v>
+      </c>
+      <c r="D112" s="37" t="n">
+        <v>119.138</v>
+      </c>
+      <c r="E112" s="38" t="n">
+        <v>17.3977</v>
+      </c>
+      <c r="F112" s="39" t="n">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="30" t="inlineStr">
+        <is>
+          <t>2+700</t>
+        </is>
+      </c>
+      <c r="B113" s="31" t="n">
+        <v>836903.187</v>
+      </c>
+      <c r="C113" s="31" t="n">
+        <v>6515077.768</v>
+      </c>
+      <c r="D113" s="32" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="E113" s="33" t="n">
+        <v>17.3061</v>
+      </c>
+      <c r="F113" s="34" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="35" t="inlineStr">
+        <is>
+          <t>2+725</t>
+        </is>
+      </c>
+      <c r="B114" s="36" t="n">
+        <v>836906.498</v>
+      </c>
+      <c r="C114" s="36" t="n">
+        <v>6515102.919</v>
+      </c>
+      <c r="D114" s="37" t="n">
+        <v>119.263</v>
+      </c>
+      <c r="E114" s="38" t="n">
+        <v>17.2153</v>
+      </c>
+      <c r="F114" s="39" t="n">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="35" t="inlineStr">
+        <is>
+          <t>2+750</t>
+        </is>
+      </c>
+      <c r="B115" s="36" t="n">
+        <v>836909.7659999999</v>
+      </c>
+      <c r="C115" s="36" t="n">
+        <v>6515128.075</v>
+      </c>
+      <c r="D115" s="37" t="n">
+        <v>119.325</v>
+      </c>
+      <c r="E115" s="38" t="n">
+        <v>17.1252</v>
+      </c>
+      <c r="F115" s="39" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="35" t="inlineStr">
+        <is>
+          <t>2+775</t>
+        </is>
+      </c>
+      <c r="B116" s="36" t="n">
+        <v>836912.996</v>
+      </c>
+      <c r="C116" s="36" t="n">
+        <v>6515153.236</v>
+      </c>
+      <c r="D116" s="37" t="n">
+        <v>119.388</v>
+      </c>
+      <c r="E116" s="38" t="n">
+        <v>17.0359</v>
+      </c>
+      <c r="F116" s="39" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="30" t="inlineStr">
+        <is>
+          <t>2+800</t>
+        </is>
+      </c>
+      <c r="B117" s="31" t="n">
+        <v>836916.194</v>
+      </c>
+      <c r="C117" s="31" t="n">
+        <v>6515178.4</v>
+      </c>
+      <c r="D117" s="32" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="E117" s="33" t="n">
+        <v>16.9477</v>
+      </c>
+      <c r="F117" s="34" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="35" t="inlineStr">
+        <is>
+          <t>2+825</t>
+        </is>
+      </c>
+      <c r="B118" s="36" t="n">
+        <v>836919.365</v>
+      </c>
+      <c r="C118" s="36" t="n">
+        <v>6515203.566</v>
+      </c>
+      <c r="D118" s="37" t="n">
+        <v>119.513</v>
+      </c>
+      <c r="E118" s="38" t="n">
+        <v>16.8604</v>
+      </c>
+      <c r="F118" s="39" t="n">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="35" t="inlineStr">
+        <is>
+          <t>2+850</t>
+        </is>
+      </c>
+      <c r="B119" s="36" t="n">
+        <v>836922.514</v>
+      </c>
+      <c r="C119" s="36" t="n">
+        <v>6515228.731</v>
+      </c>
+      <c r="D119" s="37" t="n">
+        <v>119.575</v>
+      </c>
+      <c r="E119" s="38" t="n">
+        <v>16.7742</v>
+      </c>
+      <c r="F119" s="39" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="35" t="inlineStr">
+        <is>
+          <t>2+875</t>
+        </is>
+      </c>
+      <c r="B120" s="36" t="n">
+        <v>836925.6459999999</v>
+      </c>
+      <c r="C120" s="36" t="n">
+        <v>6515253.894</v>
+      </c>
+      <c r="D120" s="37" t="n">
+        <v>119.638</v>
+      </c>
+      <c r="E120" s="38" t="n">
+        <v>16.6893</v>
+      </c>
+      <c r="F120" s="39" t="n">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="30" t="inlineStr">
+        <is>
+          <t>2+900</t>
+        </is>
+      </c>
+      <c r="B121" s="31" t="n">
+        <v>836928.768</v>
+      </c>
+      <c r="C121" s="31" t="n">
+        <v>6515279.054</v>
+      </c>
+      <c r="D121" s="32" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="E121" s="33" t="n">
+        <v>16.6056</v>
+      </c>
+      <c r="F121" s="34" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="35" t="inlineStr">
+        <is>
+          <t>2+925</t>
+        </is>
+      </c>
+      <c r="B122" s="36" t="n">
+        <v>836931.885</v>
+      </c>
+      <c r="C122" s="36" t="n">
+        <v>6515304.21</v>
+      </c>
+      <c r="D122" s="37" t="n">
+        <v>119.763</v>
+      </c>
+      <c r="E122" s="38" t="n">
+        <v>16.5233</v>
+      </c>
+      <c r="F122" s="39" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="35" t="inlineStr">
+        <is>
+          <t>2+950</t>
+        </is>
+      </c>
+      <c r="B123" s="36" t="n">
+        <v>836935.002</v>
+      </c>
+      <c r="C123" s="36" t="n">
+        <v>6515329.359</v>
+      </c>
+      <c r="D123" s="37" t="n">
+        <v>119.825</v>
+      </c>
+      <c r="E123" s="38" t="n">
+        <v>16.4424</v>
+      </c>
+      <c r="F123" s="39" t="n">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="35" t="inlineStr">
+        <is>
+          <t>2+975</t>
+        </is>
+      </c>
+      <c r="B124" s="36" t="n">
+        <v>836938.126</v>
+      </c>
+      <c r="C124" s="36" t="n">
+        <v>6515354.5</v>
+      </c>
+      <c r="D124" s="37" t="n">
+        <v>119.888</v>
+      </c>
+      <c r="E124" s="38" t="n">
+        <v>16.3631</v>
+      </c>
+      <c r="F124" s="39" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="30" t="inlineStr">
+        <is>
+          <t>3+000</t>
+        </is>
+      </c>
+      <c r="B125" s="31" t="n">
+        <v>836941.262</v>
+      </c>
+      <c r="C125" s="31" t="n">
+        <v>6515379.632</v>
+      </c>
+      <c r="D125" s="32" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="E125" s="33" t="n">
+        <v>16.2853</v>
+      </c>
+      <c r="F125" s="34" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="35" t="inlineStr">
+        <is>
+          <t>3+025</t>
+        </is>
+      </c>
+      <c r="B126" s="36" t="n">
+        <v>836944.416</v>
+      </c>
+      <c r="C126" s="36" t="n">
+        <v>6515404.752</v>
+      </c>
+      <c r="D126" s="37" t="n">
+        <v>120.013</v>
+      </c>
+      <c r="E126" s="38" t="n">
+        <v>16.2092</v>
+      </c>
+      <c r="F126" s="39" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="35" t="inlineStr">
+        <is>
+          <t>3+050</t>
+        </is>
+      </c>
+      <c r="B127" s="36" t="n">
+        <v>836947.595</v>
+      </c>
+      <c r="C127" s="36" t="n">
+        <v>6515429.861</v>
+      </c>
+      <c r="D127" s="37" t="n">
+        <v>120.075</v>
+      </c>
+      <c r="E127" s="38" t="n">
+        <v>16.1349</v>
+      </c>
+      <c r="F127" s="39" t="n">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="35" t="inlineStr">
+        <is>
+          <t>3+075</t>
+        </is>
+      </c>
+      <c r="B128" s="36" t="n">
+        <v>836950.804</v>
+      </c>
+      <c r="C128" s="36" t="n">
+        <v>6515454.955</v>
+      </c>
+      <c r="D128" s="37" t="n">
+        <v>120.138</v>
+      </c>
+      <c r="E128" s="38" t="n">
+        <v>16.0624</v>
+      </c>
+      <c r="F128" s="39" t="n">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="30" t="inlineStr">
+        <is>
+          <t>3+100</t>
+        </is>
+      </c>
+      <c r="B129" s="31" t="n">
+        <v>836954.049</v>
+      </c>
+      <c r="C129" s="31" t="n">
+        <v>6515480.034</v>
+      </c>
+      <c r="D129" s="32" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="E129" s="33" t="n">
+        <v>15.9918</v>
+      </c>
+      <c r="F129" s="34" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="35" t="inlineStr">
+        <is>
+          <t>3+125</t>
+        </is>
+      </c>
+      <c r="B130" s="36" t="n">
+        <v>836957.336</v>
+      </c>
+      <c r="C130" s="36" t="n">
+        <v>6515505.096</v>
+      </c>
+      <c r="D130" s="37" t="n">
+        <v>120.263</v>
+      </c>
+      <c r="E130" s="38" t="n">
+        <v>15.9231</v>
+      </c>
+      <c r="F130" s="39" t="n">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="35" t="inlineStr">
+        <is>
+          <t>3+150</t>
+        </is>
+      </c>
+      <c r="B131" s="36" t="n">
+        <v>836960.671</v>
+      </c>
+      <c r="C131" s="36" t="n">
+        <v>6515530.139</v>
+      </c>
+      <c r="D131" s="37" t="n">
+        <v>120.325</v>
+      </c>
+      <c r="E131" s="38" t="n">
+        <v>15.8565</v>
+      </c>
+      <c r="F131" s="39" t="n">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="35" t="inlineStr">
+        <is>
+          <t>3+175</t>
+        </is>
+      </c>
+      <c r="B132" s="36" t="n">
+        <v>836964.062</v>
+      </c>
+      <c r="C132" s="36" t="n">
+        <v>6515555.163</v>
+      </c>
+      <c r="D132" s="37" t="n">
+        <v>120.388</v>
+      </c>
+      <c r="E132" s="38" t="n">
+        <v>15.792</v>
+      </c>
+      <c r="F132" s="39" t="n">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="30" t="inlineStr">
+        <is>
+          <t>3+200</t>
+        </is>
+      </c>
+      <c r="B133" s="31" t="n">
+        <v>836967.512</v>
+      </c>
+      <c r="C133" s="31" t="n">
+        <v>6515580.166</v>
+      </c>
+      <c r="D133" s="32" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="E133" s="33" t="n">
+        <v>15.7296</v>
+      </c>
+      <c r="F133" s="34" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="35" t="inlineStr">
+        <is>
+          <t>3+225</t>
+        </is>
+      </c>
+      <c r="B134" s="36" t="n">
+        <v>836971.03</v>
+      </c>
+      <c r="C134" s="36" t="n">
+        <v>6515605.146</v>
+      </c>
+      <c r="D134" s="37" t="n">
+        <v>120.513</v>
+      </c>
+      <c r="E134" s="38" t="n">
+        <v>15.6694</v>
+      </c>
+      <c r="F134" s="39" t="n">
+        <v>3225</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="35" t="inlineStr">
+        <is>
+          <t>3+250</t>
+        </is>
+      </c>
+      <c r="B135" s="36" t="n">
+        <v>836974.62</v>
+      </c>
+      <c r="C135" s="36" t="n">
+        <v>6515630.102</v>
+      </c>
+      <c r="D135" s="37" t="n">
+        <v>120.575</v>
+      </c>
+      <c r="E135" s="38" t="n">
+        <v>15.6115</v>
+      </c>
+      <c r="F135" s="39" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="35" t="inlineStr">
+        <is>
+          <t>3+275</t>
+        </is>
+      </c>
+      <c r="B136" s="36" t="n">
+        <v>836978.289</v>
+      </c>
+      <c r="C136" s="36" t="n">
+        <v>6515655.033</v>
+      </c>
+      <c r="D136" s="37" t="n">
+        <v>120.638</v>
+      </c>
+      <c r="E136" s="38" t="n">
+        <v>15.556</v>
+      </c>
+      <c r="F136" s="39" t="n">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="30" t="inlineStr">
+        <is>
+          <t>3+300</t>
+        </is>
+      </c>
+      <c r="B137" s="31" t="n">
+        <v>836982.044</v>
+      </c>
+      <c r="C137" s="31" t="n">
+        <v>6515679.937</v>
+      </c>
+      <c r="D137" s="32" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="E137" s="33" t="n">
+        <v>15.5028</v>
+      </c>
+      <c r="F137" s="34" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="35" t="inlineStr">
+        <is>
+          <t>3+325</t>
+        </is>
+      </c>
+      <c r="B138" s="36" t="n">
+        <v>836985.889</v>
+      </c>
+      <c r="C138" s="36" t="n">
+        <v>6515704.813</v>
+      </c>
+      <c r="D138" s="37" t="n">
+        <v>120.763</v>
+      </c>
+      <c r="E138" s="38" t="n">
+        <v>15.4521</v>
+      </c>
+      <c r="F138" s="39" t="n">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="35" t="inlineStr">
+        <is>
+          <t>3+350</t>
+        </is>
+      </c>
+      <c r="B139" s="36" t="n">
+        <v>836989.831</v>
+      </c>
+      <c r="C139" s="36" t="n">
+        <v>6515729.66</v>
+      </c>
+      <c r="D139" s="37" t="n">
+        <v>120.825</v>
+      </c>
+      <c r="E139" s="38" t="n">
+        <v>15.4039</v>
+      </c>
+      <c r="F139" s="39" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="35" t="inlineStr">
+        <is>
+          <t>3+375</t>
+        </is>
+      </c>
+      <c r="B140" s="36" t="n">
+        <v>836993.875</v>
+      </c>
+      <c r="C140" s="36" t="n">
+        <v>6515754.476</v>
+      </c>
+      <c r="D140" s="37" t="n">
+        <v>120.888</v>
+      </c>
+      <c r="E140" s="38" t="n">
+        <v>15.3582</v>
+      </c>
+      <c r="F140" s="39" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="30" t="inlineStr">
+        <is>
+          <t>3+400</t>
+        </is>
+      </c>
+      <c r="B141" s="31" t="n">
+        <v>836998.029</v>
+      </c>
+      <c r="C141" s="31" t="n">
+        <v>6515779.26</v>
+      </c>
+      <c r="D141" s="32" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="E141" s="33" t="n">
+        <v>15.315</v>
+      </c>
+      <c r="F141" s="34" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="35" t="inlineStr">
+        <is>
+          <t>3+425</t>
+        </is>
+      </c>
+      <c r="B142" s="36" t="n">
+        <v>837002.296</v>
+      </c>
+      <c r="C142" s="36" t="n">
+        <v>6515804.011</v>
+      </c>
+      <c r="D142" s="37" t="n">
+        <v>121.013</v>
+      </c>
+      <c r="E142" s="38" t="n">
+        <v>15.2745</v>
+      </c>
+      <c r="F142" s="39" t="n">
+        <v>3425</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="35" t="inlineStr">
+        <is>
+          <t>3+450</t>
+        </is>
+      </c>
+      <c r="B143" s="36" t="n">
+        <v>837006.684</v>
+      </c>
+      <c r="C143" s="36" t="n">
+        <v>6515828.727</v>
+      </c>
+      <c r="D143" s="37" t="n">
+        <v>121.075</v>
+      </c>
+      <c r="E143" s="38" t="n">
+        <v>15.2367</v>
+      </c>
+      <c r="F143" s="39" t="n">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="35" t="inlineStr">
+        <is>
+          <t>3+475</t>
+        </is>
+      </c>
+      <c r="B144" s="36" t="n">
+        <v>837011.198</v>
+      </c>
+      <c r="C144" s="36" t="n">
+        <v>6515853.408</v>
+      </c>
+      <c r="D144" s="37" t="n">
+        <v>121.138</v>
+      </c>
+      <c r="E144" s="38" t="n">
+        <v>15.2015</v>
+      </c>
+      <c r="F144" s="39" t="n">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="30" t="inlineStr">
+        <is>
+          <t>3+500</t>
+        </is>
+      </c>
+      <c r="B145" s="31" t="n">
+        <v>837015.8419999999</v>
+      </c>
+      <c r="C145" s="31" t="n">
+        <v>6515878.052</v>
+      </c>
+      <c r="D145" s="32" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="E145" s="33" t="n">
+        <v>15.1691</v>
+      </c>
+      <c r="F145" s="34" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="35" t="inlineStr">
+        <is>
+          <t>3+525</t>
+        </is>
+      </c>
+      <c r="B146" s="36" t="n">
+        <v>837020.624</v>
+      </c>
+      <c r="C146" s="36" t="n">
+        <v>6515902.657</v>
+      </c>
+      <c r="D146" s="37" t="n">
+        <v>121.263</v>
+      </c>
+      <c r="E146" s="38" t="n">
+        <v>15.1395</v>
+      </c>
+      <c r="F146" s="39" t="n">
+        <v>3525</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="35" t="inlineStr">
+        <is>
+          <t>3+550</t>
+        </is>
+      </c>
+      <c r="B147" s="36" t="n">
+        <v>837025.547</v>
+      </c>
+      <c r="C147" s="36" t="n">
+        <v>6515927.224</v>
+      </c>
+      <c r="D147" s="37" t="n">
+        <v>121.325</v>
+      </c>
+      <c r="E147" s="38" t="n">
+        <v>15.1126</v>
+      </c>
+      <c r="F147" s="39" t="n">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="35" t="inlineStr">
+        <is>
+          <t>3+575</t>
+        </is>
+      </c>
+      <c r="B148" s="36" t="n">
+        <v>837030.617</v>
+      </c>
+      <c r="C148" s="36" t="n">
+        <v>6515951.75</v>
+      </c>
+      <c r="D148" s="37" t="n">
+        <v>121.388</v>
+      </c>
+      <c r="E148" s="38" t="n">
+        <v>15.0886</v>
+      </c>
+      <c r="F148" s="39" t="n">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="30" t="inlineStr">
+        <is>
+          <t>3+600</t>
+        </is>
+      </c>
+      <c r="B149" s="31" t="n">
+        <v>837035.839</v>
+      </c>
+      <c r="C149" s="31" t="n">
+        <v>6515976.234</v>
+      </c>
+      <c r="D149" s="32" t="n">
+        <v>121.45</v>
+      </c>
+      <c r="E149" s="33" t="n">
+        <v>15.0674</v>
+      </c>
+      <c r="F149" s="34" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="35" t="inlineStr">
+        <is>
+          <t>3+625</t>
+        </is>
+      </c>
+      <c r="B150" s="36" t="n">
+        <v>837041.218</v>
+      </c>
+      <c r="C150" s="36" t="n">
+        <v>6516000.676</v>
+      </c>
+      <c r="D150" s="37" t="n">
+        <v>121.513</v>
+      </c>
+      <c r="E150" s="38" t="n">
+        <v>15.0491</v>
+      </c>
+      <c r="F150" s="39" t="n">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="35" t="inlineStr">
+        <is>
+          <t>3+650</t>
+        </is>
+      </c>
+      <c r="B151" s="36" t="n">
+        <v>837046.759</v>
+      </c>
+      <c r="C151" s="36" t="n">
+        <v>6516025.074</v>
+      </c>
+      <c r="D151" s="37" t="n">
+        <v>121.575</v>
+      </c>
+      <c r="E151" s="38" t="n">
+        <v>15.0336</v>
+      </c>
+      <c r="F151" s="39" t="n">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="35" t="inlineStr">
+        <is>
+          <t>3+675</t>
+        </is>
+      </c>
+      <c r="B152" s="36" t="n">
+        <v>837052.466</v>
+      </c>
+      <c r="C152" s="36" t="n">
+        <v>6516049.427</v>
+      </c>
+      <c r="D152" s="37" t="n">
+        <v>121.638</v>
+      </c>
+      <c r="E152" s="38" t="n">
+        <v>15.0211</v>
+      </c>
+      <c r="F152" s="39" t="n">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="30" t="inlineStr">
+        <is>
+          <t>3+700</t>
+        </is>
+      </c>
+      <c r="B153" s="31" t="n">
+        <v>837058.345</v>
+      </c>
+      <c r="C153" s="31" t="n">
+        <v>6516073.734</v>
+      </c>
+      <c r="D153" s="32" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="E153" s="33" t="n">
+        <v>15.0114</v>
+      </c>
+      <c r="F153" s="34" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="35" t="inlineStr">
+        <is>
+          <t>3+725</t>
+        </is>
+      </c>
+      <c r="B154" s="36" t="n">
+        <v>837064.398</v>
+      </c>
+      <c r="C154" s="36" t="n">
+        <v>6516097.994</v>
+      </c>
+      <c r="D154" s="37" t="n">
+        <v>121.763</v>
+      </c>
+      <c r="E154" s="38" t="n">
+        <v>15.0047</v>
+      </c>
+      <c r="F154" s="39" t="n">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="35" t="inlineStr">
+        <is>
+          <t>3+750</t>
+        </is>
+      </c>
+      <c r="B155" s="36" t="n">
+        <v>837070.63</v>
+      </c>
+      <c r="C155" s="36" t="n">
+        <v>6516122.206</v>
+      </c>
+      <c r="D155" s="37" t="n">
+        <v>121.825</v>
+      </c>
+      <c r="E155" s="38" t="n">
+        <v>15.0009</v>
+      </c>
+      <c r="F155" s="39" t="n">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="35" t="inlineStr">
+        <is>
+          <t>3+775</t>
+        </is>
+      </c>
+      <c r="B156" s="36" t="n">
+        <v>837077.046</v>
+      </c>
+      <c r="C156" s="36" t="n">
+        <v>6516146.369</v>
+      </c>
+      <c r="D156" s="37" t="n">
+        <v>121.888</v>
+      </c>
+      <c r="E156" s="38" t="n">
+        <v>15.0001</v>
+      </c>
+      <c r="F156" s="39" t="n">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="30" t="inlineStr">
+        <is>
+          <t>3+800</t>
+        </is>
+      </c>
+      <c r="B157" s="31" t="n">
+        <v>837083.648</v>
+      </c>
+      <c r="C157" s="31" t="n">
+        <v>6516170.482</v>
+      </c>
+      <c r="D157" s="32" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="E157" s="33" t="n">
+        <v>15.0021</v>
+      </c>
+      <c r="F157" s="34" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="35" t="inlineStr">
+        <is>
+          <t>3+825</t>
+        </is>
+      </c>
+      <c r="B158" s="36" t="n">
+        <v>837090.441</v>
+      </c>
+      <c r="C158" s="36" t="n">
+        <v>6516194.543</v>
+      </c>
+      <c r="D158" s="37" t="n">
+        <v>122.013</v>
+      </c>
+      <c r="E158" s="38" t="n">
+        <v>15.0071</v>
+      </c>
+      <c r="F158" s="39" t="n">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="35" t="inlineStr">
+        <is>
+          <t>3+850</t>
+        </is>
+      </c>
+      <c r="B159" s="36" t="n">
+        <v>837097.428</v>
+      </c>
+      <c r="C159" s="36" t="n">
+        <v>6516218.553</v>
+      </c>
+      <c r="D159" s="37" t="n">
+        <v>122.075</v>
+      </c>
+      <c r="E159" s="38" t="n">
+        <v>15.015</v>
+      </c>
+      <c r="F159" s="39" t="n">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="35" t="inlineStr">
+        <is>
+          <t>3+875</t>
+        </is>
+      </c>
+      <c r="B160" s="36" t="n">
+        <v>837104.612</v>
+      </c>
+      <c r="C160" s="36" t="n">
+        <v>6516242.51</v>
+      </c>
+      <c r="D160" s="37" t="n">
+        <v>122.138</v>
+      </c>
+      <c r="E160" s="38" t="n">
+        <v>15.0258</v>
+      </c>
+      <c r="F160" s="39" t="n">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="30" t="inlineStr">
+        <is>
+          <t>3+900</t>
+        </is>
+      </c>
+      <c r="B161" s="31" t="n">
+        <v>837111.996</v>
+      </c>
+      <c r="C161" s="31" t="n">
+        <v>6516266.413</v>
+      </c>
+      <c r="D161" s="32" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="E161" s="33" t="n">
+        <v>15.0396</v>
+      </c>
+      <c r="F161" s="34" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="35" t="inlineStr">
+        <is>
+          <t>3+925</t>
+        </is>
+      </c>
+      <c r="B162" s="36" t="n">
+        <v>837119.583</v>
+      </c>
+      <c r="C162" s="36" t="n">
+        <v>6516290.261</v>
+      </c>
+      <c r="D162" s="37" t="n">
+        <v>122.263</v>
+      </c>
+      <c r="E162" s="38" t="n">
+        <v>15.0562</v>
+      </c>
+      <c r="F162" s="39" t="n">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="35" t="inlineStr">
+        <is>
+          <t>3+950</t>
+        </is>
+      </c>
+      <c r="B163" s="36" t="n">
+        <v>837127.375</v>
+      </c>
+      <c r="C163" s="36" t="n">
+        <v>6516314.053</v>
+      </c>
+      <c r="D163" s="37" t="n">
+        <v>122.325</v>
+      </c>
+      <c r="E163" s="38" t="n">
+        <v>15.0757</v>
+      </c>
+      <c r="F163" s="39" t="n">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="35" t="inlineStr">
+        <is>
+          <t>3+975</t>
+        </is>
+      </c>
+      <c r="B164" s="36" t="n">
+        <v>837135.374</v>
+      </c>
+      <c r="C164" s="36" t="n">
+        <v>6516337.789</v>
+      </c>
+      <c r="D164" s="37" t="n">
+        <v>122.388</v>
+      </c>
+      <c r="E164" s="38" t="n">
+        <v>15.098</v>
+      </c>
+      <c r="F164" s="39" t="n">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="30" t="inlineStr">
+        <is>
+          <t>4+000</t>
+        </is>
+      </c>
+      <c r="B165" s="31" t="n">
+        <v>837143.584</v>
+      </c>
+      <c r="C165" s="31" t="n">
+        <v>6516361.468</v>
+      </c>
+      <c r="D165" s="32" t="n">
+        <v>122.45</v>
+      </c>
+      <c r="E165" s="33" t="n">
+        <v>15.1232</v>
+      </c>
+      <c r="F165" s="34" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="35" t="inlineStr">
+        <is>
+          <t>4+025</t>
+        </is>
+      </c>
+      <c r="B166" s="36" t="n">
+        <v>837152.004</v>
+      </c>
+      <c r="C166" s="36" t="n">
+        <v>6516385.088</v>
+      </c>
+      <c r="D166" s="37" t="n">
+        <v>122.513</v>
+      </c>
+      <c r="E166" s="38" t="n">
+        <v>15.1512</v>
+      </c>
+      <c r="F166" s="39" t="n">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="35" t="inlineStr">
+        <is>
+          <t>4+050</t>
+        </is>
+      </c>
+      <c r="B167" s="36" t="n">
+        <v>837160.638</v>
+      </c>
+      <c r="C167" s="36" t="n">
+        <v>6516408.65</v>
+      </c>
+      <c r="D167" s="37" t="n">
+        <v>122.575</v>
+      </c>
+      <c r="E167" s="38" t="n">
+        <v>15.182</v>
+      </c>
+      <c r="F167" s="39" t="n">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="35" t="inlineStr">
+        <is>
+          <t>4+075</t>
+        </is>
+      </c>
+      <c r="B168" s="36" t="n">
+        <v>837169.486</v>
+      </c>
+      <c r="C168" s="36" t="n">
+        <v>6516432.153</v>
+      </c>
+      <c r="D168" s="37" t="n">
+        <v>122.638</v>
+      </c>
+      <c r="E168" s="38" t="n">
+        <v>15.2155</v>
+      </c>
+      <c r="F168" s="39" t="n">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="30" t="inlineStr">
+        <is>
+          <t>4+100</t>
+        </is>
+      </c>
+      <c r="B169" s="31" t="n">
+        <v>837178.55</v>
+      </c>
+      <c r="C169" s="31" t="n">
+        <v>6516455.595</v>
+      </c>
+      <c r="D169" s="32" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="E169" s="33" t="n">
+        <v>15.2518</v>
+      </c>
+      <c r="F169" s="34" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="35" t="inlineStr">
+        <is>
+          <t>4+125</t>
+        </is>
+      </c>
+      <c r="B170" s="36" t="n">
+        <v>837187.83</v>
+      </c>
+      <c r="C170" s="36" t="n">
+        <v>6516478.976</v>
+      </c>
+      <c r="D170" s="37" t="n">
+        <v>122.763</v>
+      </c>
+      <c r="E170" s="38" t="n">
+        <v>15.2907</v>
+      </c>
+      <c r="F170" s="39" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="35" t="inlineStr">
+        <is>
+          <t>4+150</t>
+        </is>
+      </c>
+      <c r="B171" s="36" t="n">
+        <v>837197.328</v>
+      </c>
+      <c r="C171" s="36" t="n">
+        <v>6516502.296</v>
+      </c>
+      <c r="D171" s="37" t="n">
+        <v>122.825</v>
+      </c>
+      <c r="E171" s="38" t="n">
+        <v>15.3323</v>
+      </c>
+      <c r="F171" s="39" t="n">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="35" t="inlineStr">
+        <is>
+          <t>4+175</t>
+        </is>
+      </c>
+      <c r="B172" s="36" t="n">
+        <v>837207.0429999999</v>
+      </c>
+      <c r="C172" s="36" t="n">
+        <v>6516525.554</v>
+      </c>
+      <c r="D172" s="37" t="n">
+        <v>122.888</v>
+      </c>
+      <c r="E172" s="38" t="n">
+        <v>15.3765</v>
+      </c>
+      <c r="F172" s="39" t="n">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="30" t="inlineStr">
+        <is>
+          <t>4+200</t>
+        </is>
+      </c>
+      <c r="B173" s="31" t="n">
+        <v>837216.975</v>
+      </c>
+      <c r="C173" s="31" t="n">
+        <v>6516548.749</v>
+      </c>
+      <c r="D173" s="32" t="n">
+        <v>122.95</v>
+      </c>
+      <c r="E173" s="33" t="n">
+        <v>15.4232</v>
+      </c>
+      <c r="F173" s="34" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="35" t="inlineStr">
+        <is>
+          <t>4+225</t>
+        </is>
+      </c>
+      <c r="B174" s="36" t="n">
+        <v>837227.125</v>
+      </c>
+      <c r="C174" s="36" t="n">
+        <v>6516571.881</v>
+      </c>
+      <c r="D174" s="37" t="n">
+        <v>123.013</v>
+      </c>
+      <c r="E174" s="38" t="n">
+        <v>15.4725</v>
+      </c>
+      <c r="F174" s="39" t="n">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="35" t="inlineStr">
+        <is>
+          <t>4+250</t>
+        </is>
+      </c>
+      <c r="B175" s="36" t="n">
+        <v>837237.491</v>
+      </c>
+      <c r="C175" s="36" t="n">
+        <v>6516594.95</v>
+      </c>
+      <c r="D175" s="37" t="n">
+        <v>123.075</v>
+      </c>
+      <c r="E175" s="38" t="n">
+        <v>15.5242</v>
+      </c>
+      <c r="F175" s="39" t="n">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="35" t="inlineStr">
+        <is>
+          <t>4+275</t>
+        </is>
+      </c>
+      <c r="B176" s="36" t="n">
+        <v>837248.075</v>
+      </c>
+      <c r="C176" s="36" t="n">
+        <v>6516617.955</v>
+      </c>
+      <c r="D176" s="37" t="n">
+        <v>123.138</v>
+      </c>
+      <c r="E176" s="38" t="n">
+        <v>15.5783</v>
+      </c>
+      <c r="F176" s="39" t="n">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="30" t="inlineStr">
+        <is>
+          <t>4+300</t>
+        </is>
+      </c>
+      <c r="B177" s="31" t="n">
+        <v>837258.873</v>
+      </c>
+      <c r="C177" s="31" t="n">
+        <v>6516640.895</v>
+      </c>
+      <c r="D177" s="32" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="E177" s="33" t="n">
+        <v>15.6348</v>
+      </c>
+      <c r="F177" s="34" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="35" t="inlineStr">
+        <is>
+          <t>4+325</t>
+        </is>
+      </c>
+      <c r="B178" s="36" t="n">
+        <v>837269.8860000001</v>
+      </c>
+      <c r="C178" s="36" t="n">
+        <v>6516663.771</v>
+      </c>
+      <c r="D178" s="37" t="n">
+        <v>123.263</v>
+      </c>
+      <c r="E178" s="38" t="n">
+        <v>15.6937</v>
+      </c>
+      <c r="F178" s="39" t="n">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="35" t="inlineStr">
+        <is>
+          <t>4+350</t>
+        </is>
+      </c>
+      <c r="B179" s="36" t="n">
+        <v>837281.111</v>
+      </c>
+      <c r="C179" s="36" t="n">
+        <v>6516686.583</v>
+      </c>
+      <c r="D179" s="37" t="n">
+        <v>123.325</v>
+      </c>
+      <c r="E179" s="38" t="n">
+        <v>15.7547</v>
+      </c>
+      <c r="F179" s="39" t="n">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="35" t="inlineStr">
+        <is>
+          <t>4+375</t>
+        </is>
+      </c>
+      <c r="B180" s="36" t="n">
+        <v>837292.547</v>
+      </c>
+      <c r="C180" s="36" t="n">
+        <v>6516709.33</v>
+      </c>
+      <c r="D180" s="37" t="n">
+        <v>123.388</v>
+      </c>
+      <c r="E180" s="38" t="n">
+        <v>15.818</v>
+      </c>
+      <c r="F180" s="39" t="n">
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="30" t="inlineStr">
+        <is>
+          <t>4+400</t>
+        </is>
+      </c>
+      <c r="B181" s="31" t="n">
+        <v>837304.193</v>
+      </c>
+      <c r="C181" s="31" t="n">
+        <v>6516732.011</v>
+      </c>
+      <c r="D181" s="32" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="E181" s="33" t="n">
+        <v>15.8834</v>
+      </c>
+      <c r="F181" s="34" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="35" t="inlineStr">
+        <is>
+          <t>4+425</t>
+        </is>
+      </c>
+      <c r="B182" s="36" t="n">
+        <v>837316.045</v>
+      </c>
+      <c r="C182" s="36" t="n">
+        <v>6516754.628</v>
+      </c>
+      <c r="D182" s="37" t="n">
+        <v>123.513</v>
+      </c>
+      <c r="E182" s="38" t="n">
+        <v>15.9508</v>
+      </c>
+      <c r="F182" s="39" t="n">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="35" t="inlineStr">
+        <is>
+          <t>4+450</t>
+        </is>
+      </c>
+      <c r="B183" s="36" t="n">
+        <v>837328.102</v>
+      </c>
+      <c r="C183" s="36" t="n">
+        <v>6516777.18</v>
+      </c>
+      <c r="D183" s="37" t="n">
+        <v>123.575</v>
+      </c>
+      <c r="E183" s="38" t="n">
+        <v>16.0203</v>
+      </c>
+      <c r="F183" s="39" t="n">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="35" t="inlineStr">
+        <is>
+          <t>4+475</t>
+        </is>
+      </c>
+      <c r="B184" s="36" t="n">
+        <v>837340.36</v>
+      </c>
+      <c r="C184" s="36" t="n">
+        <v>6516799.667</v>
+      </c>
+      <c r="D184" s="37" t="n">
+        <v>123.638</v>
+      </c>
+      <c r="E184" s="38" t="n">
+        <v>16.0917</v>
+      </c>
+      <c r="F184" s="39" t="n">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="30" t="inlineStr">
+        <is>
+          <t>4+500</t>
+        </is>
+      </c>
+      <c r="B185" s="31" t="n">
+        <v>837352.816</v>
+      </c>
+      <c r="C185" s="31" t="n">
+        <v>6516822.089</v>
+      </c>
+      <c r="D185" s="32" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="E185" s="33" t="n">
+        <v>16.165</v>
+      </c>
+      <c r="F185" s="34" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="35" t="inlineStr">
+        <is>
+          <t>4+525</t>
+        </is>
+      </c>
+      <c r="B186" s="36" t="n">
+        <v>837365.468</v>
+      </c>
+      <c r="C186" s="36" t="n">
+        <v>6516844.446</v>
+      </c>
+      <c r="D186" s="37" t="n">
+        <v>123.763</v>
+      </c>
+      <c r="E186" s="38" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="F186" s="39" t="n">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="35" t="inlineStr">
+        <is>
+          <t>4+550</t>
+        </is>
+      </c>
+      <c r="B187" s="36" t="n">
+        <v>837378.312</v>
+      </c>
+      <c r="C187" s="36" t="n">
+        <v>6516866.74</v>
+      </c>
+      <c r="D187" s="37" t="n">
+        <v>123.825</v>
+      </c>
+      <c r="E187" s="38" t="n">
+        <v>16.3168</v>
+      </c>
+      <c r="F187" s="39" t="n">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="35" t="inlineStr">
+        <is>
+          <t>4+575</t>
+        </is>
+      </c>
+      <c r="B188" s="36" t="n">
+        <v>837391.343</v>
+      </c>
+      <c r="C188" s="36" t="n">
+        <v>6516888.97</v>
+      </c>
+      <c r="D188" s="37" t="n">
+        <v>123.888</v>
+      </c>
+      <c r="E188" s="38" t="n">
+        <v>16.3952</v>
+      </c>
+      <c r="F188" s="39" t="n">
+        <v>4575</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="30" t="inlineStr">
+        <is>
+          <t>4+600</t>
+        </is>
+      </c>
+      <c r="B189" s="31" t="n">
+        <v>837404.559</v>
+      </c>
+      <c r="C189" s="31" t="n">
+        <v>6516911.137</v>
+      </c>
+      <c r="D189" s="32" t="n">
+        <v>123.95</v>
+      </c>
+      <c r="E189" s="33" t="n">
+        <v>16.4752</v>
+      </c>
+      <c r="F189" s="34" t="n">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="35" t="inlineStr">
+        <is>
+          <t>4+625</t>
+        </is>
+      </c>
+      <c r="B190" s="36" t="n">
+        <v>837417.953</v>
+      </c>
+      <c r="C190" s="36" t="n">
+        <v>6516933.241</v>
+      </c>
+      <c r="D190" s="37" t="n">
+        <v>124.013</v>
+      </c>
+      <c r="E190" s="38" t="n">
+        <v>16.5566</v>
+      </c>
+      <c r="F190" s="39" t="n">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="35" t="inlineStr">
+        <is>
+          <t>4+650</t>
+        </is>
+      </c>
+      <c r="B191" s="36" t="n">
+        <v>837431.523</v>
+      </c>
+      <c r="C191" s="36" t="n">
+        <v>6516955.283</v>
+      </c>
+      <c r="D191" s="37" t="n">
+        <v>124.075</v>
+      </c>
+      <c r="E191" s="38" t="n">
+        <v>16.6395</v>
+      </c>
+      <c r="F191" s="39" t="n">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="35" t="inlineStr">
+        <is>
+          <t>4+675</t>
+        </is>
+      </c>
+      <c r="B192" s="36" t="n">
+        <v>837445.264</v>
+      </c>
+      <c r="C192" s="36" t="n">
+        <v>6516977.264</v>
+      </c>
+      <c r="D192" s="37" t="n">
+        <v>124.138</v>
+      </c>
+      <c r="E192" s="38" t="n">
+        <v>16.7237</v>
+      </c>
+      <c r="F192" s="39" t="n">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="30" t="inlineStr">
+        <is>
+          <t>4+700</t>
+        </is>
+      </c>
+      <c r="B193" s="31" t="n">
+        <v>837459.169</v>
+      </c>
+      <c r="C193" s="31" t="n">
+        <v>6516999.184</v>
+      </c>
+      <c r="D193" s="32" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="E193" s="33" t="n">
+        <v>16.8092</v>
+      </c>
+      <c r="F193" s="34" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="35" t="inlineStr">
+        <is>
+          <t>4+725</t>
+        </is>
+      </c>
+      <c r="B194" s="36" t="n">
+        <v>837473.235</v>
+      </c>
+      <c r="C194" s="36" t="n">
+        <v>6517021.045</v>
+      </c>
+      <c r="D194" s="37" t="n">
+        <v>124.263</v>
+      </c>
+      <c r="E194" s="38" t="n">
+        <v>16.8958</v>
+      </c>
+      <c r="F194" s="39" t="n">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="35" t="inlineStr">
+        <is>
+          <t>4+750</t>
+        </is>
+      </c>
+      <c r="B195" s="36" t="n">
+        <v>837487.455</v>
+      </c>
+      <c r="C195" s="36" t="n">
+        <v>6517042.848</v>
+      </c>
+      <c r="D195" s="37" t="n">
+        <v>124.325</v>
+      </c>
+      <c r="E195" s="38" t="n">
+        <v>16.9835</v>
+      </c>
+      <c r="F195" s="39" t="n">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="35" t="inlineStr">
+        <is>
+          <t>4+775</t>
+        </is>
+      </c>
+      <c r="B196" s="36" t="n">
+        <v>837501.825</v>
+      </c>
+      <c r="C196" s="36" t="n">
+        <v>6517064.593</v>
+      </c>
+      <c r="D196" s="37" t="n">
+        <v>124.388</v>
+      </c>
+      <c r="E196" s="38" t="n">
+        <v>17.0722</v>
+      </c>
+      <c r="F196" s="39" t="n">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="30" t="inlineStr">
+        <is>
+          <t>4+800</t>
+        </is>
+      </c>
+      <c r="B197" s="31" t="n">
+        <v>837516.3370000001</v>
+      </c>
+      <c r="C197" s="31" t="n">
+        <v>6517086.283</v>
+      </c>
+      <c r="D197" s="32" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="E197" s="33" t="n">
+        <v>17.1618</v>
+      </c>
+      <c r="F197" s="34" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="35" t="inlineStr">
+        <is>
+          <t>4+825</t>
+        </is>
+      </c>
+      <c r="B198" s="36" t="n">
+        <v>837530.987</v>
+      </c>
+      <c r="C198" s="36" t="n">
+        <v>6517107.917</v>
+      </c>
+      <c r="D198" s="37" t="n">
+        <v>124.513</v>
+      </c>
+      <c r="E198" s="38" t="n">
+        <v>17.2522</v>
+      </c>
+      <c r="F198" s="39" t="n">
+        <v>4825</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="35" t="inlineStr">
+        <is>
+          <t>4+850</t>
+        </is>
+      </c>
+      <c r="B199" s="36" t="n">
+        <v>837545.768</v>
+      </c>
+      <c r="C199" s="36" t="n">
+        <v>6517129.498</v>
+      </c>
+      <c r="D199" s="37" t="n">
+        <v>124.575</v>
+      </c>
+      <c r="E199" s="38" t="n">
+        <v>17.3433</v>
+      </c>
+      <c r="F199" s="39" t="n">
+        <v>4850</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="35" t="inlineStr">
+        <is>
+          <t>4+875</t>
+        </is>
+      </c>
+      <c r="B200" s="36" t="n">
+        <v>837560.672</v>
+      </c>
+      <c r="C200" s="36" t="n">
+        <v>6517151.028</v>
+      </c>
+      <c r="D200" s="37" t="n">
+        <v>124.638</v>
+      </c>
+      <c r="E200" s="38" t="n">
+        <v>17.4351</v>
+      </c>
+      <c r="F200" s="39" t="n">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="30" t="inlineStr">
+        <is>
+          <t>4+900</t>
+        </is>
+      </c>
+      <c r="B201" s="31" t="n">
+        <v>837575.6949999999</v>
+      </c>
+      <c r="C201" s="31" t="n">
+        <v>6517172.507</v>
+      </c>
+      <c r="D201" s="32" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="E201" s="33" t="n">
+        <v>17.5274</v>
+      </c>
+      <c r="F201" s="34" t="n">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="35" t="inlineStr">
+        <is>
+          <t>4+925</t>
+        </is>
+      </c>
+      <c r="B202" s="36" t="n">
+        <v>837590.828</v>
+      </c>
+      <c r="C202" s="36" t="n">
+        <v>6517193.938</v>
+      </c>
+      <c r="D202" s="37" t="n">
+        <v>124.763</v>
+      </c>
+      <c r="E202" s="38" t="n">
+        <v>17.6202</v>
+      </c>
+      <c r="F202" s="39" t="n">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="35" t="inlineStr">
+        <is>
+          <t>4+950</t>
+        </is>
+      </c>
+      <c r="B203" s="36" t="n">
+        <v>837606.0649999999</v>
+      </c>
+      <c r="C203" s="36" t="n">
+        <v>6517215.323</v>
+      </c>
+      <c r="D203" s="37" t="n">
+        <v>124.825</v>
+      </c>
+      <c r="E203" s="38" t="n">
+        <v>17.7134</v>
+      </c>
+      <c r="F203" s="39" t="n">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="35" t="inlineStr">
+        <is>
+          <t>4+975</t>
+        </is>
+      </c>
+      <c r="B204" s="36" t="n">
+        <v>837621.399</v>
+      </c>
+      <c r="C204" s="36" t="n">
+        <v>6517236.662</v>
+      </c>
+      <c r="D204" s="37" t="n">
+        <v>124.888</v>
+      </c>
+      <c r="E204" s="38" t="n">
+        <v>17.8068</v>
+      </c>
+      <c r="F204" s="39" t="n">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="30" t="inlineStr">
+        <is>
+          <t>5+000</t>
+        </is>
+      </c>
+      <c r="B205" s="31" t="n">
+        <v>837636.821</v>
+      </c>
+      <c r="C205" s="31" t="n">
+        <v>6517257.96</v>
+      </c>
+      <c r="D205" s="32" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="E205" s="33" t="n">
+        <v>17.9005</v>
+      </c>
+      <c r="F205" s="34" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="40" t="inlineStr">
+        <is>
+          <t>IMPORTANT : Ces coordonnées sont générées automatiquement (projet démo). Remplacer par les coordonnées réelles issues du levé topographique ou du GPS.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F205"/>
+  <mergeCells count="3">
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>DISTANCES TRANSVERSALES / AXE — Autoroute 2x3 voies — 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>SECTION EN TRAVERS TYPE — Vue schématique (de gauche à droite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="43" t="inlineStr"/>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ← GAUCHE (distances négatives)        AXE        DROITE (distances positives) →</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ─────────────────────────────────────── 0 ────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bord_Prop_G ... Canal_G ... Bord_Chaussee_G   |   Bord_Chaussee_D ... Canal_D ... Bord_Prop_D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>Élément</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>Distance / axe (m)</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>Côté</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>Colonne cote référence</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>Onglet source</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>AXE</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>Axe</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t>TPC_Gauche</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>AXE_G</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>TPC_Droit</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="inlineStr">
+        <is>
+          <t>AXE_D</t>
+        </is>
+      </c>
+      <c r="E10" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>BAU_G</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C11" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_G</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>BAU_D</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_D</t>
+        </is>
+      </c>
+      <c r="E12" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>Canal_G (120x120)</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="C13" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_G</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>Canal_D (120x120)</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="inlineStr">
+        <is>
+          <t>Tablier_Fini_D</t>
+        </is>
+      </c>
+      <c r="E14" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>Accotement_G</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="n">
+        <v>-14</v>
+      </c>
+      <c r="C15" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_G</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>Accotement_D</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_D</t>
+        </is>
+      </c>
+      <c r="E16" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_G</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="n">
+        <v>-17</v>
+      </c>
+      <c r="C17" s="48" t="inlineStr">
+        <is>
+          <t>Gauche</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_G</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>Cote_Gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_D</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
+        <is>
+          <t>Droit</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="inlineStr">
+        <is>
+          <t>Bord_Propriete_D</t>
+        </is>
+      </c>
+      <c r="E18" s="50" t="inlineStr">
+        <is>
+          <t>Cote_Droit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>UTILISATION :
+• La colonne 'Distance / axe' donne la position transversale de chaque élément (- = gauche, + = droite).
+• Combinée aux coordonnées XY de PK_Coordonnees, elle permet de calculer la position GPS de chaque élément via : X_elem = X_axe + dist × sin(gisement + 90°) / Y_elem = Y_axe + dist × cos(gisement + 90°).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1"/>
+    <row r="22" ht="18" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A20:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/modeles_recepta/P3_Autoroute_2x3_5km.xlsx
+++ b/data/modeles_recepta/P3_Autoroute_2x3_5km.xlsx
@@ -1,35 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LEGENDE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PK_Coordonnees" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OFFSETS_TRANSVERSAUX" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Gauche" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cote_Droit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPREVUS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROFIL_LONG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECTIONS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEGENDE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PK_Coordonnees'!$A$3:$F$205</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="+0.000;-0.000;0.000"/>
-  </numFmts>
-  <fonts count="21">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +45,24 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="009CA3AF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="7"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0000FFFF"/>
       <sz val="12"/>
@@ -72,77 +83,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0064748B"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001E293B"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <b val="1"/>
-      <color rgb="000F4C35"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="00475569"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F766E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000F766E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -211,27 +153,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1F38"/>
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
+        <fgColor rgb="00374151"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="004B5563"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F9FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -241,31 +188,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F4C35"/>
+        <fgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0FDF4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0FFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="000D1F38"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -289,23 +221,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00FCD34D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -343,125 +303,87 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,6 +459,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26832,6 +26784,2770 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AH4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_BB</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_GB4</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_GNT</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_Fond_Forme</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>AXE_PST</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>G_Bord_Voie3</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>G_Bord_BAU</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>G_Accotement</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>G_BB_Roulement</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>G_GB4_Base</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>G_GNT_SousBase</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>G_Fond_Forme</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>G_PST</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>G_Bordure_Finie</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>G_Tablier_Fini_120x120</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>G_Radier_Interieur</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>G_Beton_Proprete</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>G_Fond_Fouille</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>G_Bord_Propriete</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>D_Bord_Voie3</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>D_Bord_BAU</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>D_Accotement</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>D_BB_Roulement</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>D_GB4_Base</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>D_GNT_SousBase</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>D_Fond_Forme</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>D_PST</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>D_Bordure_Finie</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
+          <t>D_Tablier_Fini_120x120</t>
+        </is>
+      </c>
+      <c r="AE1" s="13" t="inlineStr">
+        <is>
+          <t>D_Radier_Interieur</t>
+        </is>
+      </c>
+      <c r="AF1" s="13" t="inlineStr">
+        <is>
+          <t>D_Beton_Proprete</t>
+        </is>
+      </c>
+      <c r="AG1" s="13" t="inlineStr">
+        <is>
+          <t>D_Fond_Fouille</t>
+        </is>
+      </c>
+      <c r="AH1" s="13" t="inlineStr">
+        <is>
+          <t>D_Bord_Propriete</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>0+012</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>115.072</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>115.012</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>114.892</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>114.692</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>114.542</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>114.791</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>114.716</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>114.691</v>
+      </c>
+      <c r="J2" s="15" t="n">
+        <v>114.716</v>
+      </c>
+      <c r="K2" s="15" t="n">
+        <v>114.656</v>
+      </c>
+      <c r="L2" s="15" t="n">
+        <v>114.536</v>
+      </c>
+      <c r="M2" s="15" t="n">
+        <v>114.336</v>
+      </c>
+      <c r="N2" s="15" t="n">
+        <v>114.186</v>
+      </c>
+      <c r="O2" s="15" t="n">
+        <v>114.671</v>
+      </c>
+      <c r="P2" s="15" t="n">
+        <v>114.671</v>
+      </c>
+      <c r="Q2" s="15" t="n">
+        <v>113.291</v>
+      </c>
+      <c r="R2" s="15" t="n">
+        <v>113.191</v>
+      </c>
+      <c r="S2" s="15" t="n">
+        <v>112.991</v>
+      </c>
+      <c r="T2" s="15" t="n">
+        <v>114.871</v>
+      </c>
+      <c r="U2" s="15" t="n">
+        <v>114.791</v>
+      </c>
+      <c r="V2" s="15" t="n">
+        <v>114.716</v>
+      </c>
+      <c r="W2" s="15" t="n">
+        <v>114.691</v>
+      </c>
+      <c r="X2" s="15" t="n">
+        <v>114.716</v>
+      </c>
+      <c r="Y2" s="15" t="n">
+        <v>114.656</v>
+      </c>
+      <c r="Z2" s="15" t="n">
+        <v>114.536</v>
+      </c>
+      <c r="AA2" s="15" t="n">
+        <v>114.336</v>
+      </c>
+      <c r="AB2" s="15" t="n">
+        <v>114.186</v>
+      </c>
+      <c r="AC2" s="15" t="n">
+        <v>114.671</v>
+      </c>
+      <c r="AD2" s="15" t="n">
+        <v>114.671</v>
+      </c>
+      <c r="AE2" s="15" t="n">
+        <v>113.291</v>
+      </c>
+      <c r="AF2" s="15" t="n">
+        <v>113.191</v>
+      </c>
+      <c r="AG2" s="15" t="n">
+        <v>112.991</v>
+      </c>
+      <c r="AH2" s="15" t="n">
+        <v>114.871</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>0+040</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>115.24</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>115.18</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>114.86</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>114.71</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>114.959</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>114.884</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>114.859</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>114.884</v>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>114.824</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>114.704</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>114.504</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>114.354</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>114.839</v>
+      </c>
+      <c r="P3" s="15" t="n">
+        <v>114.839</v>
+      </c>
+      <c r="Q3" s="15" t="n">
+        <v>113.459</v>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>113.359</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>113.159</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>115.039</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>114.959</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>114.884</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>114.859</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>114.884</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>114.824</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>114.704</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>114.504</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>114.354</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>114.839</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>114.839</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>113.459</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>113.359</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>113.159</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>115.039</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>0+068</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>115.408</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>115.348</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>115.228</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>115.028</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>114.878</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>115.127</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>115.052</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>115.027</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>115.052</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>114.992</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>114.872</v>
+      </c>
+      <c r="M4" s="15" t="n">
+        <v>114.672</v>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>114.522</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>115.007</v>
+      </c>
+      <c r="P4" s="15" t="n">
+        <v>115.007</v>
+      </c>
+      <c r="Q4" s="15" t="n">
+        <v>113.627</v>
+      </c>
+      <c r="R4" s="15" t="n">
+        <v>113.527</v>
+      </c>
+      <c r="S4" s="15" t="n">
+        <v>113.327</v>
+      </c>
+      <c r="T4" s="15" t="n">
+        <v>115.207</v>
+      </c>
+      <c r="U4" s="15" t="n">
+        <v>115.127</v>
+      </c>
+      <c r="V4" s="15" t="n">
+        <v>115.052</v>
+      </c>
+      <c r="W4" s="15" t="n">
+        <v>115.027</v>
+      </c>
+      <c r="X4" s="15" t="n">
+        <v>115.052</v>
+      </c>
+      <c r="Y4" s="15" t="n">
+        <v>114.992</v>
+      </c>
+      <c r="Z4" s="15" t="n">
+        <v>114.872</v>
+      </c>
+      <c r="AA4" s="15" t="n">
+        <v>114.672</v>
+      </c>
+      <c r="AB4" s="15" t="n">
+        <v>114.522</v>
+      </c>
+      <c r="AC4" s="15" t="n">
+        <v>115.007</v>
+      </c>
+      <c r="AD4" s="15" t="n">
+        <v>115.007</v>
+      </c>
+      <c r="AE4" s="15" t="n">
+        <v>113.627</v>
+      </c>
+      <c r="AF4" s="15" t="n">
+        <v>113.527</v>
+      </c>
+      <c r="AG4" s="15" t="n">
+        <v>113.327</v>
+      </c>
+      <c r="AH4" s="15" t="n">
+        <v>115.207</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B202"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Z_axe (m NGF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>0+000</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>0+025</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>115.15</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>0+050</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>0+075</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>115.45</v>
+      </c>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>0+100</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>115.6</v>
+      </c>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>0+125</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>115.75</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>0+150</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>115.9</v>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>0+175</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>116.05</v>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>0+200</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>116.2</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>0+225</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>116.35</v>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>0+250</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>116.5</v>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>0+275</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>116.65</v>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>0+300</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>116.8</v>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>0+325</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>116.95</v>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>0+350</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>117.1</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>0+375</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>117.25</v>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>0+400</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>117.4</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>0+425</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>117.55</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>0+450</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>117.7</v>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>0+475</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>117.85</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>0+500</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>0+525</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>118.15</v>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>0+550</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>0+575</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>118.45</v>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>0+600</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>0+625</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>118.75</v>
+      </c>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>0+650</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>118.9</v>
+      </c>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>0+675</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>119.05</v>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>0+700</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>0+725</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>119.35</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>0+750</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>0+775</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>119.65</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>0+800</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>119.8</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>0+825</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>119.95</v>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>0+850</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>120.1</v>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>0+875</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="n">
+        <v>120.25</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>0+900</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>120.4</v>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>0+925</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>120.55</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>0+950</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>120.7</v>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>0+975</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>120.85</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>1+000</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>1+025</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>121.15</v>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>1+050</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>121.3</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>1+075</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>121.45</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>1+100</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>121.6</v>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>1+125</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>121.75</v>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>1+150</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>1+175</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
+        <v>122.05</v>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>1+200</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>1+225</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>1+250</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>1+275</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>122.65</v>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>1+300</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>1+325</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>122.95</v>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>1+350</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>123.1</v>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>1+375</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>1+400</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="n">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>1+425</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="n">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>1+450</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="n">
+        <v>123.7</v>
+      </c>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>1+475</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n">
+        <v>123.85</v>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>1+500</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>1+525</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="n">
+        <v>124.15</v>
+      </c>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>1+550</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n">
+        <v>124.3</v>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>1+575</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n">
+        <v>124.45</v>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>1+600</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
+        <v>124.6</v>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>1+625</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="n">
+        <v>124.75</v>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>1+650</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="n">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>1+675</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="n">
+        <v>125.05</v>
+      </c>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>1+700</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="n">
+        <v>125.2</v>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>1+725</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="n">
+        <v>125.35</v>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>1+750</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="n">
+        <v>125.5</v>
+      </c>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>1+775</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="n">
+        <v>125.65</v>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>1+800</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>1+825</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n">
+        <v>125.95</v>
+      </c>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>1+850</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n">
+        <v>126.1</v>
+      </c>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>1+875</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n">
+        <v>126.25</v>
+      </c>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>1+900</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="n">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>1+925</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="n">
+        <v>126.55</v>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>1+950</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>1+975</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="n">
+        <v>126.85</v>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>2+000</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>2+025</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="n">
+        <v>127.15</v>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>2+050</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>127.3</v>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>2+075</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="n">
+        <v>127.45</v>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>2+100</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n">
+        <v>127.6</v>
+      </c>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>2+125</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="n">
+        <v>127.75</v>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>2+150</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n">
+        <v>127.9</v>
+      </c>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>2+175</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="n">
+        <v>128.05</v>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>2+200</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="n">
+        <v>128.2</v>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>2+225</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="n">
+        <v>128.35</v>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>2+250</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="n">
+        <v>128.5</v>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>2+275</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="n">
+        <v>128.65</v>
+      </c>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>2+300</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="n">
+        <v>128.8</v>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>2+325</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="n">
+        <v>128.95</v>
+      </c>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>2+350</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="n">
+        <v>129.1</v>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>2+375</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="n">
+        <v>129.25</v>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>2+400</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="n">
+        <v>129.4</v>
+      </c>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>2+425</t>
+        </is>
+      </c>
+      <c r="B99" s="20" t="n">
+        <v>129.55</v>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>2+450</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="n">
+        <v>129.7</v>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>2+475</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="n">
+        <v>129.85</v>
+      </c>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>2+500</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>2+525</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="n">
+        <v>130.15</v>
+      </c>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>2+550</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="n">
+        <v>130.3</v>
+      </c>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>2+575</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n">
+        <v>130.45</v>
+      </c>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>2+600</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="n">
+        <v>130.6</v>
+      </c>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>2+625</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="n">
+        <v>130.75</v>
+      </c>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>2+650</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="n">
+        <v>130.9</v>
+      </c>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>2+675</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="n">
+        <v>131.05</v>
+      </c>
+    </row>
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>2+700</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="n">
+        <v>131.2</v>
+      </c>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>2+725</t>
+        </is>
+      </c>
+      <c r="B111" s="20" t="n">
+        <v>131.35</v>
+      </c>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>2+750</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="n">
+        <v>131.5</v>
+      </c>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>2+775</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="n">
+        <v>131.65</v>
+      </c>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>2+800</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="n">
+        <v>131.8</v>
+      </c>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>2+825</t>
+        </is>
+      </c>
+      <c r="B115" s="20" t="n">
+        <v>131.95</v>
+      </c>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>2+850</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="n">
+        <v>132.1</v>
+      </c>
+    </row>
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>2+875</t>
+        </is>
+      </c>
+      <c r="B117" s="20" t="n">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>2+900</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="n">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>2+925</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="n">
+        <v>132.55</v>
+      </c>
+    </row>
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>2+950</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="n">
+        <v>132.7</v>
+      </c>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>2+975</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="n">
+        <v>132.85</v>
+      </c>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>3+000</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>3+025</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="n">
+        <v>133.15</v>
+      </c>
+    </row>
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>3+050</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="n">
+        <v>133.3</v>
+      </c>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>3+075</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="n">
+        <v>133.45</v>
+      </c>
+    </row>
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>3+100</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="n">
+        <v>133.6</v>
+      </c>
+    </row>
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>3+125</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="n">
+        <v>133.75</v>
+      </c>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>3+150</t>
+        </is>
+      </c>
+      <c r="B128" s="18" t="n">
+        <v>133.9</v>
+      </c>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="19" t="inlineStr">
+        <is>
+          <t>3+175</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="n">
+        <v>134.05</v>
+      </c>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>3+200</t>
+        </is>
+      </c>
+      <c r="B130" s="18" t="n">
+        <v>134.2</v>
+      </c>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>3+225</t>
+        </is>
+      </c>
+      <c r="B131" s="20" t="n">
+        <v>134.35</v>
+      </c>
+    </row>
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>3+250</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="n">
+        <v>134.5</v>
+      </c>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t>3+275</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="n">
+        <v>134.65</v>
+      </c>
+    </row>
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>3+300</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="n">
+        <v>134.8</v>
+      </c>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="19" t="inlineStr">
+        <is>
+          <t>3+325</t>
+        </is>
+      </c>
+      <c r="B135" s="20" t="n">
+        <v>134.95</v>
+      </c>
+    </row>
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>3+350</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="n">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="19" t="inlineStr">
+        <is>
+          <t>3+375</t>
+        </is>
+      </c>
+      <c r="B137" s="20" t="n">
+        <v>135.25</v>
+      </c>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>3+400</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="n">
+        <v>135.4</v>
+      </c>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="19" t="inlineStr">
+        <is>
+          <t>3+425</t>
+        </is>
+      </c>
+      <c r="B139" s="20" t="n">
+        <v>135.55</v>
+      </c>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t>3+450</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="n">
+        <v>135.7</v>
+      </c>
+    </row>
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="19" t="inlineStr">
+        <is>
+          <t>3+475</t>
+        </is>
+      </c>
+      <c r="B141" s="20" t="n">
+        <v>135.85</v>
+      </c>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>3+500</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="19" t="inlineStr">
+        <is>
+          <t>3+525</t>
+        </is>
+      </c>
+      <c r="B143" s="20" t="n">
+        <v>136.15</v>
+      </c>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t>3+550</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="n">
+        <v>136.3</v>
+      </c>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="19" t="inlineStr">
+        <is>
+          <t>3+575</t>
+        </is>
+      </c>
+      <c r="B145" s="20" t="n">
+        <v>136.45</v>
+      </c>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t>3+600</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="n">
+        <v>136.6</v>
+      </c>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>3+625</t>
+        </is>
+      </c>
+      <c r="B147" s="20" t="n">
+        <v>136.75</v>
+      </c>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t>3+650</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="n">
+        <v>136.9</v>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t>3+675</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="n">
+        <v>137.05</v>
+      </c>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t>3+700</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="n">
+        <v>137.2</v>
+      </c>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="19" t="inlineStr">
+        <is>
+          <t>3+725</t>
+        </is>
+      </c>
+      <c r="B151" s="20" t="n">
+        <v>137.35</v>
+      </c>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>3+750</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="n">
+        <v>137.5</v>
+      </c>
+    </row>
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="19" t="inlineStr">
+        <is>
+          <t>3+775</t>
+        </is>
+      </c>
+      <c r="B153" s="20" t="n">
+        <v>137.65</v>
+      </c>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>3+800</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="n">
+        <v>137.8</v>
+      </c>
+    </row>
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="19" t="inlineStr">
+        <is>
+          <t>3+825</t>
+        </is>
+      </c>
+      <c r="B155" s="20" t="n">
+        <v>137.95</v>
+      </c>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>3+850</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="n">
+        <v>138.1</v>
+      </c>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="19" t="inlineStr">
+        <is>
+          <t>3+875</t>
+        </is>
+      </c>
+      <c r="B157" s="20" t="n">
+        <v>138.25</v>
+      </c>
+    </row>
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>3+900</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="n">
+        <v>138.4</v>
+      </c>
+    </row>
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="19" t="inlineStr">
+        <is>
+          <t>3+925</t>
+        </is>
+      </c>
+      <c r="B159" s="20" t="n">
+        <v>138.55</v>
+      </c>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t>3+950</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="n">
+        <v>138.7</v>
+      </c>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>3+975</t>
+        </is>
+      </c>
+      <c r="B161" s="20" t="n">
+        <v>138.85</v>
+      </c>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t>4+000</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>4+025</t>
+        </is>
+      </c>
+      <c r="B163" s="20" t="n">
+        <v>139.15</v>
+      </c>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="17" t="inlineStr">
+        <is>
+          <t>4+050</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="n">
+        <v>139.3</v>
+      </c>
+    </row>
+    <row r="165" ht="14" customHeight="1">
+      <c r="A165" s="19" t="inlineStr">
+        <is>
+          <t>4+075</t>
+        </is>
+      </c>
+      <c r="B165" s="20" t="n">
+        <v>139.45</v>
+      </c>
+    </row>
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="17" t="inlineStr">
+        <is>
+          <t>4+100</t>
+        </is>
+      </c>
+      <c r="B166" s="18" t="n">
+        <v>139.6</v>
+      </c>
+    </row>
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="19" t="inlineStr">
+        <is>
+          <t>4+125</t>
+        </is>
+      </c>
+      <c r="B167" s="20" t="n">
+        <v>139.75</v>
+      </c>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="17" t="inlineStr">
+        <is>
+          <t>4+150</t>
+        </is>
+      </c>
+      <c r="B168" s="18" t="n">
+        <v>139.9</v>
+      </c>
+    </row>
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="19" t="inlineStr">
+        <is>
+          <t>4+175</t>
+        </is>
+      </c>
+      <c r="B169" s="20" t="n">
+        <v>140.05</v>
+      </c>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="17" t="inlineStr">
+        <is>
+          <t>4+200</t>
+        </is>
+      </c>
+      <c r="B170" s="18" t="n">
+        <v>140.2</v>
+      </c>
+    </row>
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="19" t="inlineStr">
+        <is>
+          <t>4+225</t>
+        </is>
+      </c>
+      <c r="B171" s="20" t="n">
+        <v>140.35</v>
+      </c>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="17" t="inlineStr">
+        <is>
+          <t>4+250</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="n">
+        <v>140.5</v>
+      </c>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>4+275</t>
+        </is>
+      </c>
+      <c r="B173" s="20" t="n">
+        <v>140.65</v>
+      </c>
+    </row>
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="17" t="inlineStr">
+        <is>
+          <t>4+300</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="n">
+        <v>140.8</v>
+      </c>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>4+325</t>
+        </is>
+      </c>
+      <c r="B175" s="20" t="n">
+        <v>140.95</v>
+      </c>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="17" t="inlineStr">
+        <is>
+          <t>4+350</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="n">
+        <v>141.1</v>
+      </c>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="19" t="inlineStr">
+        <is>
+          <t>4+375</t>
+        </is>
+      </c>
+      <c r="B177" s="20" t="n">
+        <v>141.25</v>
+      </c>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="17" t="inlineStr">
+        <is>
+          <t>4+400</t>
+        </is>
+      </c>
+      <c r="B178" s="18" t="n">
+        <v>141.4</v>
+      </c>
+    </row>
+    <row r="179" ht="14" customHeight="1">
+      <c r="A179" s="19" t="inlineStr">
+        <is>
+          <t>4+425</t>
+        </is>
+      </c>
+      <c r="B179" s="20" t="n">
+        <v>141.55</v>
+      </c>
+    </row>
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="17" t="inlineStr">
+        <is>
+          <t>4+450</t>
+        </is>
+      </c>
+      <c r="B180" s="18" t="n">
+        <v>141.7</v>
+      </c>
+    </row>
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="19" t="inlineStr">
+        <is>
+          <t>4+475</t>
+        </is>
+      </c>
+      <c r="B181" s="20" t="n">
+        <v>141.85</v>
+      </c>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="17" t="inlineStr">
+        <is>
+          <t>4+500</t>
+        </is>
+      </c>
+      <c r="B182" s="18" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="19" t="inlineStr">
+        <is>
+          <t>4+525</t>
+        </is>
+      </c>
+      <c r="B183" s="20" t="n">
+        <v>142.15</v>
+      </c>
+    </row>
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="17" t="inlineStr">
+        <is>
+          <t>4+550</t>
+        </is>
+      </c>
+      <c r="B184" s="18" t="n">
+        <v>142.3</v>
+      </c>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="19" t="inlineStr">
+        <is>
+          <t>4+575</t>
+        </is>
+      </c>
+      <c r="B185" s="20" t="n">
+        <v>142.45</v>
+      </c>
+    </row>
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="17" t="inlineStr">
+        <is>
+          <t>4+600</t>
+        </is>
+      </c>
+      <c r="B186" s="18" t="n">
+        <v>142.6</v>
+      </c>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="19" t="inlineStr">
+        <is>
+          <t>4+625</t>
+        </is>
+      </c>
+      <c r="B187" s="20" t="n">
+        <v>142.75</v>
+      </c>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="17" t="inlineStr">
+        <is>
+          <t>4+650</t>
+        </is>
+      </c>
+      <c r="B188" s="18" t="n">
+        <v>142.9</v>
+      </c>
+    </row>
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="19" t="inlineStr">
+        <is>
+          <t>4+675</t>
+        </is>
+      </c>
+      <c r="B189" s="20" t="n">
+        <v>143.05</v>
+      </c>
+    </row>
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="17" t="inlineStr">
+        <is>
+          <t>4+700</t>
+        </is>
+      </c>
+      <c r="B190" s="18" t="n">
+        <v>143.2</v>
+      </c>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="19" t="inlineStr">
+        <is>
+          <t>4+725</t>
+        </is>
+      </c>
+      <c r="B191" s="20" t="n">
+        <v>143.35</v>
+      </c>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="17" t="inlineStr">
+        <is>
+          <t>4+750</t>
+        </is>
+      </c>
+      <c r="B192" s="18" t="n">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="19" t="inlineStr">
+        <is>
+          <t>4+775</t>
+        </is>
+      </c>
+      <c r="B193" s="20" t="n">
+        <v>143.65</v>
+      </c>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="17" t="inlineStr">
+        <is>
+          <t>4+800</t>
+        </is>
+      </c>
+      <c r="B194" s="18" t="n">
+        <v>143.8</v>
+      </c>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="19" t="inlineStr">
+        <is>
+          <t>4+825</t>
+        </is>
+      </c>
+      <c r="B195" s="20" t="n">
+        <v>143.95</v>
+      </c>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="17" t="inlineStr">
+        <is>
+          <t>4+850</t>
+        </is>
+      </c>
+      <c r="B196" s="18" t="n">
+        <v>144.1</v>
+      </c>
+    </row>
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="19" t="inlineStr">
+        <is>
+          <t>4+875</t>
+        </is>
+      </c>
+      <c r="B197" s="20" t="n">
+        <v>144.25</v>
+      </c>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="17" t="inlineStr">
+        <is>
+          <t>4+900</t>
+        </is>
+      </c>
+      <c r="B198" s="18" t="n">
+        <v>144.4</v>
+      </c>
+    </row>
+    <row r="199" ht="14" customHeight="1">
+      <c r="A199" s="19" t="inlineStr">
+        <is>
+          <t>4+925</t>
+        </is>
+      </c>
+      <c r="B199" s="20" t="n">
+        <v>144.55</v>
+      </c>
+    </row>
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="17" t="inlineStr">
+        <is>
+          <t>4+950</t>
+        </is>
+      </c>
+      <c r="B200" s="18" t="n">
+        <v>144.7</v>
+      </c>
+    </row>
+    <row r="201" ht="14" customHeight="1">
+      <c r="A201" s="19" t="inlineStr">
+        <is>
+          <t>4+975</t>
+        </is>
+      </c>
+      <c r="B201" s="20" t="n">
+        <v>144.85</v>
+      </c>
+    </row>
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="17" t="inlineStr">
+        <is>
+          <t>5+000</t>
+        </is>
+      </c>
+      <c r="B202" s="18" t="n">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>SECTIONS — Paramètres variables par tronçon  |  Ajouter une ligne si épaisseurs / dévers / distances changent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Nom_Section</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>PK_debut</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>PK_fin</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>e_BB_m</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>e_GB4_m</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>e_GNT_m</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>e_FF_m</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>Devers_G_pct</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>Devers_D_pct</t>
+        </is>
+      </c>
+      <c r="K2" s="22" t="inlineStr">
+        <is>
+          <t>Dist_G_m</t>
+        </is>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>Dist_D_m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Section principale</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>0+000</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>5+000</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F3" s="24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G3" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I3" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J3" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K3" s="24" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="L3" s="24" t="n">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="26" t="inlineStr"/>
+      <c r="C4" s="26" t="inlineStr"/>
+      <c r="D4" s="26" t="inlineStr"/>
+      <c r="E4" s="26" t="inlineStr"/>
+      <c r="F4" s="26" t="inlineStr"/>
+      <c r="G4" s="26" t="inlineStr"/>
+      <c r="H4" s="26" t="inlineStr"/>
+      <c r="I4" s="26" t="inlineStr"/>
+      <c r="J4" s="26" t="inlineStr"/>
+      <c r="K4" s="26" t="inlineStr"/>
+      <c r="L4" s="26" t="inlineStr"/>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="26" t="inlineStr"/>
+      <c r="C5" s="26" t="inlineStr"/>
+      <c r="D5" s="26" t="inlineStr"/>
+      <c r="E5" s="26" t="inlineStr"/>
+      <c r="F5" s="26" t="inlineStr"/>
+      <c r="G5" s="26" t="inlineStr"/>
+      <c r="H5" s="26" t="inlineStr"/>
+      <c r="I5" s="26" t="inlineStr"/>
+      <c r="J5" s="26" t="inlineStr"/>
+      <c r="K5" s="26" t="inlineStr"/>
+      <c r="L5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Légende : e_BB/GB4/GNT/FF en mètres  |  Devers_G/D en %  |  Dist_G/D = distance axe→bord en m  |  e_GB4 vide = couche absente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B25:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -26863,436 +29579,436 @@
     <row r="23" ht="17" customHeight="1"/>
     <row r="24" ht="17" customHeight="1"/>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>SPECIFICATIONS DU PROJET</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Titre:          Autoroute 2x3 voies + BAU + accotement</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Devers:         G:2.5% | D:2.5%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Largeurs:       3x3.75m voies + BAU 3.0m + accotement 1.0m | dist axe/bord = 15.25m</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Couches:        BB 6cm / GB4 12cm / GNT 20cm / FF 30cm / PST 15cm</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pente long.:    0.6%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cote axe Z0:    115.000 m NGF</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  PK debut/fin:   0+000 / 5+000</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pas PK:         25 m</t>
         </is>
       </c>
     </row>
     <row r="35" ht="11" customHeight="1">
-      <c r="B35" s="15" t="inlineStr"/>
+      <c r="B35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>ASSAINISSEMENT GAUCHE — 120x120 (H=1.20m)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Caniveau ferme 120x120 — H int=1.20m / dalle=18cm / radier=10cm / BP=20cm</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>ASSAINISSEMENT DROIT  — 120x120 (H=1.20m)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Caniveau ferme 120x120 — H int=1.20m / dalle=18cm / radier=10cm / BP=20cm</t>
         </is>
       </c>
     </row>
     <row r="40" ht="11" customHeight="1">
-      <c r="B40" s="15" t="inlineStr"/>
+      <c r="B40" s="30" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>STRATIGRAPHIE ASSAINISSEMENT (de bas en haut) :</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  Fond de Fouille                         (cote la plus basse)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + 20 cm  → Beton de Proprete (BP)       dessus de la couche de 20cm</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + 10 cm  → Radier Interieur             interieur fond du caniveau</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + H canal (100 / 80 / 60 / 50 cm...)   hauteur utile interieure</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  + e dalle                               Tablier Fini = bord chaussee</t>
         </is>
       </c>
     </row>
     <row r="47" ht="11" customHeight="1">
-      <c r="B47" s="15" t="inlineStr"/>
+      <c r="B47" s="30" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="37" t="inlineStr">
         <is>
           <t>COLONNES COTE_GAUCHE</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  PK</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_BB</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_GB4</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_GNT</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_PST</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B55" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Bord_Voie3</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Bord_BAU</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Accotement</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_BB_Roulement</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_GB4_Base</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_GNT_SousBase</t>
         </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_PST</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Bordure_Finie</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Tablier_Fini_120x120</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B65" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Radier_Interieur</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="B66" s="23" t="inlineStr">
+      <c r="B66" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Beton_Proprete</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
-      <c r="B67" s="23" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Fond_Fouille</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  G_Bord_Propriete</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="B69" s="24" t="inlineStr">
+      <c r="B69" s="39" t="inlineStr">
         <is>
           <t>COLONNES COTE_DROIT</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
-      <c r="B70" s="25" t="inlineStr">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  PK</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
-      <c r="B71" s="25" t="inlineStr">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_BB</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
-      <c r="B72" s="25" t="inlineStr">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_GB4</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
-      <c r="B73" s="25" t="inlineStr">
+      <c r="B73" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_GNT</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
-      <c r="B74" s="25" t="inlineStr">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
-      <c r="B75" s="25" t="inlineStr">
+      <c r="B75" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  AXE_PST</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
-      <c r="B76" s="25" t="inlineStr">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Bord_Voie3</t>
         </is>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
-      <c r="B77" s="25" t="inlineStr">
+      <c r="B77" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Bord_BAU</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
-      <c r="B78" s="25" t="inlineStr">
+      <c r="B78" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Accotement</t>
         </is>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
-      <c r="B79" s="25" t="inlineStr">
+      <c r="B79" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_BB_Roulement</t>
         </is>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
-      <c r="B80" s="25" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_GB4_Base</t>
         </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
-      <c r="B81" s="25" t="inlineStr">
+      <c r="B81" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_GNT_SousBase</t>
         </is>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
-      <c r="B82" s="25" t="inlineStr">
+      <c r="B82" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Fond_Forme</t>
         </is>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
-      <c r="B83" s="25" t="inlineStr">
+      <c r="B83" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_PST</t>
         </is>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
-      <c r="B84" s="25" t="inlineStr">
+      <c r="B84" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Bordure_Finie</t>
         </is>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
-      <c r="B85" s="25" t="inlineStr">
+      <c r="B85" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Tablier_Fini_120x120</t>
         </is>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
-      <c r="B86" s="25" t="inlineStr">
+      <c r="B86" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Radier_Interieur</t>
         </is>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
-      <c r="B87" s="25" t="inlineStr">
+      <c r="B87" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Beton_Proprete</t>
         </is>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
-      <c r="B88" s="25" t="inlineStr">
+      <c r="B88" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Fond_Fouille</t>
         </is>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
-      <c r="B89" s="25" t="inlineStr">
+      <c r="B89" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  D_Bord_Propriete</t>
         </is>
@@ -27300,4921 +30016,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F207"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>COORDONNÉES DE L'AXE — Autoroute 2x3 voies — 5 km</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>Système de référence : Lambert 93 (EPSG:2154)  —  Données à renseigner avec les coordonnées réelles du levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
-        <is>
-          <t>X (m)</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>Y (m)</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>Z axe (m)</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
-        <is>
-          <t>Gisement (°)</t>
-        </is>
-      </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>Dist. cumulée (m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>Point kilométrique</t>
-        </is>
-      </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Lambert 93 — Est</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>Lambert 93 — Nord</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
-        <is>
-          <t>Cote NGF de l'axe chaussée</t>
-        </is>
-      </c>
-      <c r="E4" s="29" t="inlineStr">
-        <is>
-          <t>Direction route (0°=N, 90°=E)</t>
-        </is>
-      </c>
-      <c r="F4" s="29" t="inlineStr">
-        <is>
-          <t>Distance depuis l'origine</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>0+000</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="n">
-        <v>836100</v>
-      </c>
-      <c r="C5" s="31" t="n">
-        <v>6512500</v>
-      </c>
-      <c r="D5" s="32" t="n">
-        <v>112.45</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>0+025</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="n">
-        <v>836107.764</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>6512523.764</v>
-      </c>
-      <c r="D6" s="37" t="n">
-        <v>112.513</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>18.0937</v>
-      </c>
-      <c r="F6" s="39" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>0+050</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="n">
-        <v>836115.606</v>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>6512547.502</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>112.575</v>
-      </c>
-      <c r="E7" s="38" t="n">
-        <v>18.1874</v>
-      </c>
-      <c r="F7" s="39" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>0+075</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="n">
-        <v>836123.526</v>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>6512571.215</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>112.638</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>18.2808</v>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>0+100</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="n">
-        <v>836131.522</v>
-      </c>
-      <c r="C9" s="31" t="n">
-        <v>6512594.902</v>
-      </c>
-      <c r="D9" s="32" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>18.374</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>0+125</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>836139.594</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>6512618.563</v>
-      </c>
-      <c r="D10" s="37" t="n">
-        <v>112.763</v>
-      </c>
-      <c r="E10" s="38" t="n">
-        <v>18.4668</v>
-      </c>
-      <c r="F10" s="39" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>0+150</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>836147.743</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>6512642.199</v>
-      </c>
-      <c r="D11" s="37" t="n">
-        <v>112.825</v>
-      </c>
-      <c r="E11" s="38" t="n">
-        <v>18.5592</v>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>0+175</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>836155.966</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>6512665.81</v>
-      </c>
-      <c r="D12" s="37" t="n">
-        <v>112.888</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>18.651</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>0+200</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="n">
-        <v>836164.262</v>
-      </c>
-      <c r="C13" s="31" t="n">
-        <v>6512689.395</v>
-      </c>
-      <c r="D13" s="32" t="n">
-        <v>112.95</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>18.7422</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>0+225</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="n">
-        <v>836172.6310000001</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>6512712.955</v>
-      </c>
-      <c r="D14" s="37" t="n">
-        <v>113.013</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>18.8327</v>
-      </c>
-      <c r="F14" s="39" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>0+250</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="n">
-        <v>836181.071</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>6512736.49</v>
-      </c>
-      <c r="D15" s="37" t="n">
-        <v>113.075</v>
-      </c>
-      <c r="E15" s="38" t="n">
-        <v>18.9223</v>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>0+275</t>
-        </is>
-      </c>
-      <c r="B16" s="36" t="n">
-        <v>836189.581</v>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>6512760</v>
-      </c>
-      <c r="D16" s="37" t="n">
-        <v>113.138</v>
-      </c>
-      <c r="E16" s="38" t="n">
-        <v>19.0111</v>
-      </c>
-      <c r="F16" s="39" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>0+300</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="n">
-        <v>836198.16</v>
-      </c>
-      <c r="C17" s="31" t="n">
-        <v>6512783.487</v>
-      </c>
-      <c r="D17" s="32" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>19.0988</v>
-      </c>
-      <c r="F17" s="34" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>0+325</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="n">
-        <v>836206.804</v>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>6512806.949</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <v>113.263</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>19.1855</v>
-      </c>
-      <c r="F18" s="39" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>0+350</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="n">
-        <v>836215.513</v>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>6512830.389</v>
-      </c>
-      <c r="D19" s="37" t="n">
-        <v>113.325</v>
-      </c>
-      <c r="E19" s="38" t="n">
-        <v>19.271</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>0+375</t>
-        </is>
-      </c>
-      <c r="B20" s="36" t="n">
-        <v>836224.285</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>6512853.806</v>
-      </c>
-      <c r="D20" s="37" t="n">
-        <v>113.388</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>19.3553</v>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>0+400</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="n">
-        <v>836233.116</v>
-      </c>
-      <c r="C21" s="31" t="n">
-        <v>6512877.2</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>113.45</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>19.4383</v>
-      </c>
-      <c r="F21" s="34" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>0+425</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="n">
-        <v>836242.007</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>6512900.573</v>
-      </c>
-      <c r="D22" s="37" t="n">
-        <v>113.513</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>19.5198</v>
-      </c>
-      <c r="F22" s="39" t="n">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>0+450</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="n">
-        <v>836250.953</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>6512923.926</v>
-      </c>
-      <c r="D23" s="37" t="n">
-        <v>113.575</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <v>19.5999</v>
-      </c>
-      <c r="F23" s="39" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>0+475</t>
-        </is>
-      </c>
-      <c r="B24" s="36" t="n">
-        <v>836259.952</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>6512947.259</v>
-      </c>
-      <c r="D24" s="37" t="n">
-        <v>113.638</v>
-      </c>
-      <c r="E24" s="38" t="n">
-        <v>19.6784</v>
-      </c>
-      <c r="F24" s="39" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>0+500</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="n">
-        <v>836269.002</v>
-      </c>
-      <c r="C25" s="31" t="n">
-        <v>6512970.572</v>
-      </c>
-      <c r="D25" s="32" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="E25" s="33" t="n">
-        <v>19.7553</v>
-      </c>
-      <c r="F25" s="34" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>0+525</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>836278.1</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>6512993.868</v>
-      </c>
-      <c r="D26" s="37" t="n">
-        <v>113.763</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <v>19.8305</v>
-      </c>
-      <c r="F26" s="39" t="n">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="inlineStr">
-        <is>
-          <t>0+550</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="n">
-        <v>836287.243</v>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>6513017.146</v>
-      </c>
-      <c r="D27" s="37" t="n">
-        <v>113.825</v>
-      </c>
-      <c r="E27" s="38" t="n">
-        <v>19.9038</v>
-      </c>
-      <c r="F27" s="39" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="35" t="inlineStr">
-        <is>
-          <t>0+575</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>836296.429</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>6513040.408</v>
-      </c>
-      <c r="D28" s="37" t="n">
-        <v>113.888</v>
-      </c>
-      <c r="E28" s="38" t="n">
-        <v>19.9753</v>
-      </c>
-      <c r="F28" s="39" t="n">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>0+600</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="n">
-        <v>836305.654</v>
-      </c>
-      <c r="C29" s="31" t="n">
-        <v>6513063.655</v>
-      </c>
-      <c r="D29" s="32" t="n">
-        <v>113.95</v>
-      </c>
-      <c r="E29" s="33" t="n">
-        <v>20.0449</v>
-      </c>
-      <c r="F29" s="34" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t>0+625</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n">
-        <v>836314.915</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>6513086.887</v>
-      </c>
-      <c r="D30" s="37" t="n">
-        <v>114.013</v>
-      </c>
-      <c r="E30" s="38" t="n">
-        <v>20.1125</v>
-      </c>
-      <c r="F30" s="39" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="35" t="inlineStr">
-        <is>
-          <t>0+650</t>
-        </is>
-      </c>
-      <c r="B31" s="36" t="n">
-        <v>836324.21</v>
-      </c>
-      <c r="C31" s="36" t="n">
-        <v>6513110.106</v>
-      </c>
-      <c r="D31" s="37" t="n">
-        <v>114.075</v>
-      </c>
-      <c r="E31" s="38" t="n">
-        <v>20.178</v>
-      </c>
-      <c r="F31" s="39" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>0+675</t>
-        </is>
-      </c>
-      <c r="B32" s="36" t="n">
-        <v>836333.534</v>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>6513133.314</v>
-      </c>
-      <c r="D32" s="37" t="n">
-        <v>114.138</v>
-      </c>
-      <c r="E32" s="38" t="n">
-        <v>20.2414</v>
-      </c>
-      <c r="F32" s="39" t="n">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>0+700</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
-        <v>836342.885</v>
-      </c>
-      <c r="C33" s="31" t="n">
-        <v>6513156.511</v>
-      </c>
-      <c r="D33" s="32" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="E33" s="33" t="n">
-        <v>20.3026</v>
-      </c>
-      <c r="F33" s="34" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>0+725</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="n">
-        <v>836352.259</v>
-      </c>
-      <c r="C34" s="36" t="n">
-        <v>6513179.699</v>
-      </c>
-      <c r="D34" s="37" t="n">
-        <v>114.263</v>
-      </c>
-      <c r="E34" s="38" t="n">
-        <v>20.3616</v>
-      </c>
-      <c r="F34" s="39" t="n">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>0+750</t>
-        </is>
-      </c>
-      <c r="B35" s="36" t="n">
-        <v>836361.653</v>
-      </c>
-      <c r="C35" s="36" t="n">
-        <v>6513202.878</v>
-      </c>
-      <c r="D35" s="37" t="n">
-        <v>114.325</v>
-      </c>
-      <c r="E35" s="38" t="n">
-        <v>20.4182</v>
-      </c>
-      <c r="F35" s="39" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="35" t="inlineStr">
-        <is>
-          <t>0+775</t>
-        </is>
-      </c>
-      <c r="B36" s="36" t="n">
-        <v>836371.063</v>
-      </c>
-      <c r="C36" s="36" t="n">
-        <v>6513226.051</v>
-      </c>
-      <c r="D36" s="37" t="n">
-        <v>114.388</v>
-      </c>
-      <c r="E36" s="38" t="n">
-        <v>20.4725</v>
-      </c>
-      <c r="F36" s="39" t="n">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>0+800</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="n">
-        <v>836380.485</v>
-      </c>
-      <c r="C37" s="31" t="n">
-        <v>6513249.218</v>
-      </c>
-      <c r="D37" s="32" t="n">
-        <v>114.45</v>
-      </c>
-      <c r="E37" s="33" t="n">
-        <v>20.5244</v>
-      </c>
-      <c r="F37" s="34" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="inlineStr">
-        <is>
-          <t>0+825</t>
-        </is>
-      </c>
-      <c r="B38" s="36" t="n">
-        <v>836389.917</v>
-      </c>
-      <c r="C38" s="36" t="n">
-        <v>6513272.382</v>
-      </c>
-      <c r="D38" s="37" t="n">
-        <v>114.513</v>
-      </c>
-      <c r="E38" s="38" t="n">
-        <v>20.5738</v>
-      </c>
-      <c r="F38" s="39" t="n">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="inlineStr">
-        <is>
-          <t>0+850</t>
-        </is>
-      </c>
-      <c r="B39" s="36" t="n">
-        <v>836399.353</v>
-      </c>
-      <c r="C39" s="36" t="n">
-        <v>6513295.542</v>
-      </c>
-      <c r="D39" s="37" t="n">
-        <v>114.575</v>
-      </c>
-      <c r="E39" s="38" t="n">
-        <v>20.6207</v>
-      </c>
-      <c r="F39" s="39" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
-        <is>
-          <t>0+875</t>
-        </is>
-      </c>
-      <c r="B40" s="36" t="n">
-        <v>836408.791</v>
-      </c>
-      <c r="C40" s="36" t="n">
-        <v>6513318.702</v>
-      </c>
-      <c r="D40" s="37" t="n">
-        <v>114.638</v>
-      </c>
-      <c r="E40" s="38" t="n">
-        <v>20.6651</v>
-      </c>
-      <c r="F40" s="39" t="n">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>0+900</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>836418.227</v>
-      </c>
-      <c r="C41" s="31" t="n">
-        <v>6513341.862</v>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="E41" s="33" t="n">
-        <v>20.7068</v>
-      </c>
-      <c r="F41" s="34" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="inlineStr">
-        <is>
-          <t>0+925</t>
-        </is>
-      </c>
-      <c r="B42" s="36" t="n">
-        <v>836427.657</v>
-      </c>
-      <c r="C42" s="36" t="n">
-        <v>6513365.024</v>
-      </c>
-      <c r="D42" s="37" t="n">
-        <v>114.763</v>
-      </c>
-      <c r="E42" s="38" t="n">
-        <v>20.7459</v>
-      </c>
-      <c r="F42" s="39" t="n">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="35" t="inlineStr">
-        <is>
-          <t>0+950</t>
-        </is>
-      </c>
-      <c r="B43" s="36" t="n">
-        <v>836437.077</v>
-      </c>
-      <c r="C43" s="36" t="n">
-        <v>6513388.189</v>
-      </c>
-      <c r="D43" s="37" t="n">
-        <v>114.825</v>
-      </c>
-      <c r="E43" s="38" t="n">
-        <v>20.7823</v>
-      </c>
-      <c r="F43" s="39" t="n">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="35" t="inlineStr">
-        <is>
-          <t>0+975</t>
-        </is>
-      </c>
-      <c r="B44" s="36" t="n">
-        <v>836446.4840000001</v>
-      </c>
-      <c r="C44" s="36" t="n">
-        <v>6513411.358</v>
-      </c>
-      <c r="D44" s="37" t="n">
-        <v>114.888</v>
-      </c>
-      <c r="E44" s="38" t="n">
-        <v>20.816</v>
-      </c>
-      <c r="F44" s="39" t="n">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t>1+000</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="n">
-        <v>836455.873</v>
-      </c>
-      <c r="C45" s="31" t="n">
-        <v>6513434.534</v>
-      </c>
-      <c r="D45" s="32" t="n">
-        <v>114.95</v>
-      </c>
-      <c r="E45" s="33" t="n">
-        <v>20.847</v>
-      </c>
-      <c r="F45" s="34" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="35" t="inlineStr">
-        <is>
-          <t>1+025</t>
-        </is>
-      </c>
-      <c r="B46" s="36" t="n">
-        <v>836465.241</v>
-      </c>
-      <c r="C46" s="36" t="n">
-        <v>6513457.718</v>
-      </c>
-      <c r="D46" s="37" t="n">
-        <v>115.013</v>
-      </c>
-      <c r="E46" s="38" t="n">
-        <v>20.8751</v>
-      </c>
-      <c r="F46" s="39" t="n">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="35" t="inlineStr">
-        <is>
-          <t>1+050</t>
-        </is>
-      </c>
-      <c r="B47" s="36" t="n">
-        <v>836474.583</v>
-      </c>
-      <c r="C47" s="36" t="n">
-        <v>6513480.912</v>
-      </c>
-      <c r="D47" s="37" t="n">
-        <v>115.075</v>
-      </c>
-      <c r="E47" s="38" t="n">
-        <v>20.9005</v>
-      </c>
-      <c r="F47" s="39" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="35" t="inlineStr">
-        <is>
-          <t>1+075</t>
-        </is>
-      </c>
-      <c r="B48" s="36" t="n">
-        <v>836483.897</v>
-      </c>
-      <c r="C48" s="36" t="n">
-        <v>6513504.116</v>
-      </c>
-      <c r="D48" s="37" t="n">
-        <v>115.138</v>
-      </c>
-      <c r="E48" s="38" t="n">
-        <v>20.923</v>
-      </c>
-      <c r="F48" s="39" t="n">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>1+100</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="n">
-        <v>836493.177</v>
-      </c>
-      <c r="C49" s="31" t="n">
-        <v>6513527.332</v>
-      </c>
-      <c r="D49" s="32" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="E49" s="33" t="n">
-        <v>20.9427</v>
-      </c>
-      <c r="F49" s="34" t="n">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="35" t="inlineStr">
-        <is>
-          <t>1+125</t>
-        </is>
-      </c>
-      <c r="B50" s="36" t="n">
-        <v>836502.421</v>
-      </c>
-      <c r="C50" s="36" t="n">
-        <v>6513550.563</v>
-      </c>
-      <c r="D50" s="37" t="n">
-        <v>115.263</v>
-      </c>
-      <c r="E50" s="38" t="n">
-        <v>20.9595</v>
-      </c>
-      <c r="F50" s="39" t="n">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="35" t="inlineStr">
-        <is>
-          <t>1+150</t>
-        </is>
-      </c>
-      <c r="B51" s="36" t="n">
-        <v>836511.624</v>
-      </c>
-      <c r="C51" s="36" t="n">
-        <v>6513573.809</v>
-      </c>
-      <c r="D51" s="37" t="n">
-        <v>115.325</v>
-      </c>
-      <c r="E51" s="38" t="n">
-        <v>20.9734</v>
-      </c>
-      <c r="F51" s="39" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="35" t="inlineStr">
-        <is>
-          <t>1+175</t>
-        </is>
-      </c>
-      <c r="B52" s="36" t="n">
-        <v>836520.784</v>
-      </c>
-      <c r="C52" s="36" t="n">
-        <v>6513597.072</v>
-      </c>
-      <c r="D52" s="37" t="n">
-        <v>115.388</v>
-      </c>
-      <c r="E52" s="38" t="n">
-        <v>20.9844</v>
-      </c>
-      <c r="F52" s="39" t="n">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="30" t="inlineStr">
-        <is>
-          <t>1+200</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="n">
-        <v>836529.895</v>
-      </c>
-      <c r="C53" s="31" t="n">
-        <v>6513620.353</v>
-      </c>
-      <c r="D53" s="32" t="n">
-        <v>115.45</v>
-      </c>
-      <c r="E53" s="33" t="n">
-        <v>20.9925</v>
-      </c>
-      <c r="F53" s="34" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="35" t="inlineStr">
-        <is>
-          <t>1+225</t>
-        </is>
-      </c>
-      <c r="B54" s="36" t="n">
-        <v>836538.954</v>
-      </c>
-      <c r="C54" s="36" t="n">
-        <v>6513643.654</v>
-      </c>
-      <c r="D54" s="37" t="n">
-        <v>115.513</v>
-      </c>
-      <c r="E54" s="38" t="n">
-        <v>20.9977</v>
-      </c>
-      <c r="F54" s="39" t="n">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="35" t="inlineStr">
-        <is>
-          <t>1+250</t>
-        </is>
-      </c>
-      <c r="B55" s="36" t="n">
-        <v>836547.958</v>
-      </c>
-      <c r="C55" s="36" t="n">
-        <v>6513666.976</v>
-      </c>
-      <c r="D55" s="37" t="n">
-        <v>115.575</v>
-      </c>
-      <c r="E55" s="38" t="n">
-        <v>20.9999</v>
-      </c>
-      <c r="F55" s="39" t="n">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="35" t="inlineStr">
-        <is>
-          <t>1+275</t>
-        </is>
-      </c>
-      <c r="B56" s="36" t="n">
-        <v>836556.903</v>
-      </c>
-      <c r="C56" s="36" t="n">
-        <v>6513690.321</v>
-      </c>
-      <c r="D56" s="37" t="n">
-        <v>115.638</v>
-      </c>
-      <c r="E56" s="38" t="n">
-        <v>20.9992</v>
-      </c>
-      <c r="F56" s="39" t="n">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="30" t="inlineStr">
-        <is>
-          <t>1+300</t>
-        </is>
-      </c>
-      <c r="B57" s="31" t="n">
-        <v>836565.785</v>
-      </c>
-      <c r="C57" s="31" t="n">
-        <v>6513713.69</v>
-      </c>
-      <c r="D57" s="32" t="n">
-        <v>115.7</v>
-      </c>
-      <c r="E57" s="33" t="n">
-        <v>20.9956</v>
-      </c>
-      <c r="F57" s="34" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="35" t="inlineStr">
-        <is>
-          <t>1+325</t>
-        </is>
-      </c>
-      <c r="B58" s="36" t="n">
-        <v>836574.601</v>
-      </c>
-      <c r="C58" s="36" t="n">
-        <v>6513737.085</v>
-      </c>
-      <c r="D58" s="37" t="n">
-        <v>115.763</v>
-      </c>
-      <c r="E58" s="38" t="n">
-        <v>20.9891</v>
-      </c>
-      <c r="F58" s="39" t="n">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="35" t="inlineStr">
-        <is>
-          <t>1+350</t>
-        </is>
-      </c>
-      <c r="B59" s="36" t="n">
-        <v>836583.348</v>
-      </c>
-      <c r="C59" s="36" t="n">
-        <v>6513760.506</v>
-      </c>
-      <c r="D59" s="37" t="n">
-        <v>115.825</v>
-      </c>
-      <c r="E59" s="38" t="n">
-        <v>20.9796</v>
-      </c>
-      <c r="F59" s="39" t="n">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>1+375</t>
-        </is>
-      </c>
-      <c r="B60" s="36" t="n">
-        <v>836592.022</v>
-      </c>
-      <c r="C60" s="36" t="n">
-        <v>6513783.955</v>
-      </c>
-      <c r="D60" s="37" t="n">
-        <v>115.888</v>
-      </c>
-      <c r="E60" s="38" t="n">
-        <v>20.9672</v>
-      </c>
-      <c r="F60" s="39" t="n">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>1+400</t>
-        </is>
-      </c>
-      <c r="B61" s="31" t="n">
-        <v>836600.6189999999</v>
-      </c>
-      <c r="C61" s="31" t="n">
-        <v>6513807.433</v>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>115.95</v>
-      </c>
-      <c r="E61" s="33" t="n">
-        <v>20.952</v>
-      </c>
-      <c r="F61" s="34" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="35" t="inlineStr">
-        <is>
-          <t>1+425</t>
-        </is>
-      </c>
-      <c r="B62" s="36" t="n">
-        <v>836609.137</v>
-      </c>
-      <c r="C62" s="36" t="n">
-        <v>6513830.941</v>
-      </c>
-      <c r="D62" s="37" t="n">
-        <v>116.013</v>
-      </c>
-      <c r="E62" s="38" t="n">
-        <v>20.9338</v>
-      </c>
-      <c r="F62" s="39" t="n">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="35" t="inlineStr">
-        <is>
-          <t>1+450</t>
-        </is>
-      </c>
-      <c r="B63" s="36" t="n">
-        <v>836617.573</v>
-      </c>
-      <c r="C63" s="36" t="n">
-        <v>6513854.481</v>
-      </c>
-      <c r="D63" s="37" t="n">
-        <v>116.075</v>
-      </c>
-      <c r="E63" s="38" t="n">
-        <v>20.9128</v>
-      </c>
-      <c r="F63" s="39" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="35" t="inlineStr">
-        <is>
-          <t>1+475</t>
-        </is>
-      </c>
-      <c r="B64" s="36" t="n">
-        <v>836625.922</v>
-      </c>
-      <c r="C64" s="36" t="n">
-        <v>6513878.053</v>
-      </c>
-      <c r="D64" s="37" t="n">
-        <v>116.138</v>
-      </c>
-      <c r="E64" s="38" t="n">
-        <v>20.8889</v>
-      </c>
-      <c r="F64" s="39" t="n">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t>1+500</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="n">
-        <v>836634.184</v>
-      </c>
-      <c r="C65" s="31" t="n">
-        <v>6513901.659</v>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>116.2</v>
-      </c>
-      <c r="E65" s="33" t="n">
-        <v>20.8623</v>
-      </c>
-      <c r="F65" s="34" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="35" t="inlineStr">
-        <is>
-          <t>1+525</t>
-        </is>
-      </c>
-      <c r="B66" s="36" t="n">
-        <v>836642.3540000001</v>
-      </c>
-      <c r="C66" s="36" t="n">
-        <v>6513925.299</v>
-      </c>
-      <c r="D66" s="37" t="n">
-        <v>116.263</v>
-      </c>
-      <c r="E66" s="38" t="n">
-        <v>20.8328</v>
-      </c>
-      <c r="F66" s="39" t="n">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="35" t="inlineStr">
-        <is>
-          <t>1+550</t>
-        </is>
-      </c>
-      <c r="B67" s="36" t="n">
-        <v>836650.4300000001</v>
-      </c>
-      <c r="C67" s="36" t="n">
-        <v>6513948.975</v>
-      </c>
-      <c r="D67" s="37" t="n">
-        <v>116.325</v>
-      </c>
-      <c r="E67" s="38" t="n">
-        <v>20.8005</v>
-      </c>
-      <c r="F67" s="39" t="n">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="35" t="inlineStr">
-        <is>
-          <t>1+575</t>
-        </is>
-      </c>
-      <c r="B68" s="36" t="n">
-        <v>836658.409</v>
-      </c>
-      <c r="C68" s="36" t="n">
-        <v>6513972.686</v>
-      </c>
-      <c r="D68" s="37" t="n">
-        <v>116.388</v>
-      </c>
-      <c r="E68" s="38" t="n">
-        <v>20.7656</v>
-      </c>
-      <c r="F68" s="39" t="n">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>1+600</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>836666.2879999999</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>6513996.435</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>116.45</v>
-      </c>
-      <c r="E69" s="33" t="n">
-        <v>20.7279</v>
-      </c>
-      <c r="F69" s="34" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="35" t="inlineStr">
-        <is>
-          <t>1+625</t>
-        </is>
-      </c>
-      <c r="B70" s="36" t="n">
-        <v>836674.066</v>
-      </c>
-      <c r="C70" s="36" t="n">
-        <v>6514020.221</v>
-      </c>
-      <c r="D70" s="37" t="n">
-        <v>116.513</v>
-      </c>
-      <c r="E70" s="38" t="n">
-        <v>20.6876</v>
-      </c>
-      <c r="F70" s="39" t="n">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="35" t="inlineStr">
-        <is>
-          <t>1+650</t>
-        </is>
-      </c>
-      <c r="B71" s="36" t="n">
-        <v>836681.741</v>
-      </c>
-      <c r="C71" s="36" t="n">
-        <v>6514044.046</v>
-      </c>
-      <c r="D71" s="37" t="n">
-        <v>116.575</v>
-      </c>
-      <c r="E71" s="38" t="n">
-        <v>20.6446</v>
-      </c>
-      <c r="F71" s="39" t="n">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="35" t="inlineStr">
-        <is>
-          <t>1+675</t>
-        </is>
-      </c>
-      <c r="B72" s="36" t="n">
-        <v>836689.309</v>
-      </c>
-      <c r="C72" s="36" t="n">
-        <v>6514067.91</v>
-      </c>
-      <c r="D72" s="37" t="n">
-        <v>116.638</v>
-      </c>
-      <c r="E72" s="38" t="n">
-        <v>20.599</v>
-      </c>
-      <c r="F72" s="39" t="n">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>1+700</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>836696.769</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>6514091.813</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>116.7</v>
-      </c>
-      <c r="E73" s="33" t="n">
-        <v>20.551</v>
-      </c>
-      <c r="F73" s="34" t="n">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="35" t="inlineStr">
-        <is>
-          <t>1+725</t>
-        </is>
-      </c>
-      <c r="B74" s="36" t="n">
-        <v>836704.1189999999</v>
-      </c>
-      <c r="C74" s="36" t="n">
-        <v>6514115.755</v>
-      </c>
-      <c r="D74" s="37" t="n">
-        <v>116.763</v>
-      </c>
-      <c r="E74" s="38" t="n">
-        <v>20.5004</v>
-      </c>
-      <c r="F74" s="39" t="n">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="35" t="inlineStr">
-        <is>
-          <t>1+750</t>
-        </is>
-      </c>
-      <c r="B75" s="36" t="n">
-        <v>836711.357</v>
-      </c>
-      <c r="C75" s="36" t="n">
-        <v>6514139.739</v>
-      </c>
-      <c r="D75" s="37" t="n">
-        <v>116.825</v>
-      </c>
-      <c r="E75" s="38" t="n">
-        <v>20.4474</v>
-      </c>
-      <c r="F75" s="39" t="n">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="35" t="inlineStr">
-        <is>
-          <t>1+775</t>
-        </is>
-      </c>
-      <c r="B76" s="36" t="n">
-        <v>836718.482</v>
-      </c>
-      <c r="C76" s="36" t="n">
-        <v>6514163.762</v>
-      </c>
-      <c r="D76" s="37" t="n">
-        <v>116.888</v>
-      </c>
-      <c r="E76" s="38" t="n">
-        <v>20.392</v>
-      </c>
-      <c r="F76" s="39" t="n">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>1+800</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>836725.492</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>6514187.827</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>116.95</v>
-      </c>
-      <c r="E77" s="33" t="n">
-        <v>20.3342</v>
-      </c>
-      <c r="F77" s="34" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="35" t="inlineStr">
-        <is>
-          <t>1+825</t>
-        </is>
-      </c>
-      <c r="B78" s="36" t="n">
-        <v>836732.387</v>
-      </c>
-      <c r="C78" s="36" t="n">
-        <v>6514211.932</v>
-      </c>
-      <c r="D78" s="37" t="n">
-        <v>117.013</v>
-      </c>
-      <c r="E78" s="38" t="n">
-        <v>20.2742</v>
-      </c>
-      <c r="F78" s="39" t="n">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="35" t="inlineStr">
-        <is>
-          <t>1+850</t>
-        </is>
-      </c>
-      <c r="B79" s="36" t="n">
-        <v>836739.164</v>
-      </c>
-      <c r="C79" s="36" t="n">
-        <v>6514236.079</v>
-      </c>
-      <c r="D79" s="37" t="n">
-        <v>117.075</v>
-      </c>
-      <c r="E79" s="38" t="n">
-        <v>20.212</v>
-      </c>
-      <c r="F79" s="39" t="n">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="35" t="inlineStr">
-        <is>
-          <t>1+875</t>
-        </is>
-      </c>
-      <c r="B80" s="36" t="n">
-        <v>836745.823</v>
-      </c>
-      <c r="C80" s="36" t="n">
-        <v>6514260.266</v>
-      </c>
-      <c r="D80" s="37" t="n">
-        <v>117.138</v>
-      </c>
-      <c r="E80" s="38" t="n">
-        <v>20.1476</v>
-      </c>
-      <c r="F80" s="39" t="n">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>1+900</t>
-        </is>
-      </c>
-      <c r="B81" s="31" t="n">
-        <v>836752.363</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>6514284.495</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="E81" s="33" t="n">
-        <v>20.0811</v>
-      </c>
-      <c r="F81" s="34" t="n">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="35" t="inlineStr">
-        <is>
-          <t>1+925</t>
-        </is>
-      </c>
-      <c r="B82" s="36" t="n">
-        <v>836758.784</v>
-      </c>
-      <c r="C82" s="36" t="n">
-        <v>6514308.764</v>
-      </c>
-      <c r="D82" s="37" t="n">
-        <v>117.263</v>
-      </c>
-      <c r="E82" s="38" t="n">
-        <v>20.0125</v>
-      </c>
-      <c r="F82" s="39" t="n">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="35" t="inlineStr">
-        <is>
-          <t>1+950</t>
-        </is>
-      </c>
-      <c r="B83" s="36" t="n">
-        <v>836765.085</v>
-      </c>
-      <c r="C83" s="36" t="n">
-        <v>6514333.074</v>
-      </c>
-      <c r="D83" s="37" t="n">
-        <v>117.325</v>
-      </c>
-      <c r="E83" s="38" t="n">
-        <v>19.942</v>
-      </c>
-      <c r="F83" s="39" t="n">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="35" t="inlineStr">
-        <is>
-          <t>1+975</t>
-        </is>
-      </c>
-      <c r="B84" s="36" t="n">
-        <v>836771.265</v>
-      </c>
-      <c r="C84" s="36" t="n">
-        <v>6514357.425</v>
-      </c>
-      <c r="D84" s="37" t="n">
-        <v>117.388</v>
-      </c>
-      <c r="E84" s="38" t="n">
-        <v>19.8696</v>
-      </c>
-      <c r="F84" s="39" t="n">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t>2+000</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="n">
-        <v>836777.325</v>
-      </c>
-      <c r="C85" s="31" t="n">
-        <v>6514381.816</v>
-      </c>
-      <c r="D85" s="32" t="n">
-        <v>117.45</v>
-      </c>
-      <c r="E85" s="33" t="n">
-        <v>19.7954</v>
-      </c>
-      <c r="F85" s="34" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="35" t="inlineStr">
-        <is>
-          <t>2+025</t>
-        </is>
-      </c>
-      <c r="B86" s="36" t="n">
-        <v>836783.265</v>
-      </c>
-      <c r="C86" s="36" t="n">
-        <v>6514406.246</v>
-      </c>
-      <c r="D86" s="37" t="n">
-        <v>117.513</v>
-      </c>
-      <c r="E86" s="38" t="n">
-        <v>19.7194</v>
-      </c>
-      <c r="F86" s="39" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="35" t="inlineStr">
-        <is>
-          <t>2+050</t>
-        </is>
-      </c>
-      <c r="B87" s="36" t="n">
-        <v>836789.084</v>
-      </c>
-      <c r="C87" s="36" t="n">
-        <v>6514430.716</v>
-      </c>
-      <c r="D87" s="37" t="n">
-        <v>117.575</v>
-      </c>
-      <c r="E87" s="38" t="n">
-        <v>19.6418</v>
-      </c>
-      <c r="F87" s="39" t="n">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="35" t="inlineStr">
-        <is>
-          <t>2+075</t>
-        </is>
-      </c>
-      <c r="B88" s="36" t="n">
-        <v>836794.784</v>
-      </c>
-      <c r="C88" s="36" t="n">
-        <v>6514455.224</v>
-      </c>
-      <c r="D88" s="37" t="n">
-        <v>117.638</v>
-      </c>
-      <c r="E88" s="38" t="n">
-        <v>19.5625</v>
-      </c>
-      <c r="F88" s="39" t="n">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="30" t="inlineStr">
-        <is>
-          <t>2+100</t>
-        </is>
-      </c>
-      <c r="B89" s="31" t="n">
-        <v>836800.3639999999</v>
-      </c>
-      <c r="C89" s="31" t="n">
-        <v>6514479.77</v>
-      </c>
-      <c r="D89" s="32" t="n">
-        <v>117.7</v>
-      </c>
-      <c r="E89" s="33" t="n">
-        <v>19.4818</v>
-      </c>
-      <c r="F89" s="34" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="35" t="inlineStr">
-        <is>
-          <t>2+125</t>
-        </is>
-      </c>
-      <c r="B90" s="36" t="n">
-        <v>836805.826</v>
-      </c>
-      <c r="C90" s="36" t="n">
-        <v>6514504.354</v>
-      </c>
-      <c r="D90" s="37" t="n">
-        <v>117.763</v>
-      </c>
-      <c r="E90" s="38" t="n">
-        <v>19.3995</v>
-      </c>
-      <c r="F90" s="39" t="n">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="35" t="inlineStr">
-        <is>
-          <t>2+150</t>
-        </is>
-      </c>
-      <c r="B91" s="36" t="n">
-        <v>836811.17</v>
-      </c>
-      <c r="C91" s="36" t="n">
-        <v>6514528.974</v>
-      </c>
-      <c r="D91" s="37" t="n">
-        <v>117.825</v>
-      </c>
-      <c r="E91" s="38" t="n">
-        <v>19.3159</v>
-      </c>
-      <c r="F91" s="39" t="n">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="35" t="inlineStr">
-        <is>
-          <t>2+175</t>
-        </is>
-      </c>
-      <c r="B92" s="36" t="n">
-        <v>836816.398</v>
-      </c>
-      <c r="C92" s="36" t="n">
-        <v>6514553.631</v>
-      </c>
-      <c r="D92" s="37" t="n">
-        <v>117.888</v>
-      </c>
-      <c r="E92" s="38" t="n">
-        <v>19.2311</v>
-      </c>
-      <c r="F92" s="39" t="n">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="30" t="inlineStr">
-        <is>
-          <t>2+200</t>
-        </is>
-      </c>
-      <c r="B93" s="31" t="n">
-        <v>836821.5110000001</v>
-      </c>
-      <c r="C93" s="31" t="n">
-        <v>6514578.322</v>
-      </c>
-      <c r="D93" s="32" t="n">
-        <v>117.95</v>
-      </c>
-      <c r="E93" s="33" t="n">
-        <v>19.145</v>
-      </c>
-      <c r="F93" s="34" t="n">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="35" t="inlineStr">
-        <is>
-          <t>2+225</t>
-        </is>
-      </c>
-      <c r="B94" s="36" t="n">
-        <v>836826.5110000001</v>
-      </c>
-      <c r="C94" s="36" t="n">
-        <v>6514603.047</v>
-      </c>
-      <c r="D94" s="37" t="n">
-        <v>118.013</v>
-      </c>
-      <c r="E94" s="38" t="n">
-        <v>19.0578</v>
-      </c>
-      <c r="F94" s="39" t="n">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="35" t="inlineStr">
-        <is>
-          <t>2+250</t>
-        </is>
-      </c>
-      <c r="B95" s="36" t="n">
-        <v>836831.398</v>
-      </c>
-      <c r="C95" s="36" t="n">
-        <v>6514627.806</v>
-      </c>
-      <c r="D95" s="37" t="n">
-        <v>118.075</v>
-      </c>
-      <c r="E95" s="38" t="n">
-        <v>18.9696</v>
-      </c>
-      <c r="F95" s="39" t="n">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="35" t="inlineStr">
-        <is>
-          <t>2+275</t>
-        </is>
-      </c>
-      <c r="B96" s="36" t="n">
-        <v>836836.175</v>
-      </c>
-      <c r="C96" s="36" t="n">
-        <v>6514652.596</v>
-      </c>
-      <c r="D96" s="37" t="n">
-        <v>118.138</v>
-      </c>
-      <c r="E96" s="38" t="n">
-        <v>18.8804</v>
-      </c>
-      <c r="F96" s="39" t="n">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="30" t="inlineStr">
-        <is>
-          <t>2+300</t>
-        </is>
-      </c>
-      <c r="B97" s="31" t="n">
-        <v>836840.844</v>
-      </c>
-      <c r="C97" s="31" t="n">
-        <v>6514677.418</v>
-      </c>
-      <c r="D97" s="32" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="E97" s="33" t="n">
-        <v>18.7903</v>
-      </c>
-      <c r="F97" s="34" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="35" t="inlineStr">
-        <is>
-          <t>2+325</t>
-        </is>
-      </c>
-      <c r="B98" s="36" t="n">
-        <v>836845.407</v>
-      </c>
-      <c r="C98" s="36" t="n">
-        <v>6514702.27</v>
-      </c>
-      <c r="D98" s="37" t="n">
-        <v>118.263</v>
-      </c>
-      <c r="E98" s="38" t="n">
-        <v>18.6995</v>
-      </c>
-      <c r="F98" s="39" t="n">
-        <v>2325</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="35" t="inlineStr">
-        <is>
-          <t>2+350</t>
-        </is>
-      </c>
-      <c r="B99" s="36" t="n">
-        <v>836849.867</v>
-      </c>
-      <c r="C99" s="36" t="n">
-        <v>6514727.151</v>
-      </c>
-      <c r="D99" s="37" t="n">
-        <v>118.325</v>
-      </c>
-      <c r="E99" s="38" t="n">
-        <v>18.608</v>
-      </c>
-      <c r="F99" s="39" t="n">
-        <v>2350</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="35" t="inlineStr">
-        <is>
-          <t>2+375</t>
-        </is>
-      </c>
-      <c r="B100" s="36" t="n">
-        <v>836854.226</v>
-      </c>
-      <c r="C100" s="36" t="n">
-        <v>6514752.059</v>
-      </c>
-      <c r="D100" s="37" t="n">
-        <v>118.388</v>
-      </c>
-      <c r="E100" s="38" t="n">
-        <v>18.516</v>
-      </c>
-      <c r="F100" s="39" t="n">
-        <v>2375</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="30" t="inlineStr">
-        <is>
-          <t>2+400</t>
-        </is>
-      </c>
-      <c r="B101" s="31" t="n">
-        <v>836858.486</v>
-      </c>
-      <c r="C101" s="31" t="n">
-        <v>6514776.993</v>
-      </c>
-      <c r="D101" s="32" t="n">
-        <v>118.45</v>
-      </c>
-      <c r="E101" s="33" t="n">
-        <v>18.4234</v>
-      </c>
-      <c r="F101" s="34" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="35" t="inlineStr">
-        <is>
-          <t>2+425</t>
-        </is>
-      </c>
-      <c r="B102" s="36" t="n">
-        <v>836862.651</v>
-      </c>
-      <c r="C102" s="36" t="n">
-        <v>6514801.953</v>
-      </c>
-      <c r="D102" s="37" t="n">
-        <v>118.513</v>
-      </c>
-      <c r="E102" s="38" t="n">
-        <v>18.3304</v>
-      </c>
-      <c r="F102" s="39" t="n">
-        <v>2425</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="35" t="inlineStr">
-        <is>
-          <t>2+450</t>
-        </is>
-      </c>
-      <c r="B103" s="36" t="n">
-        <v>836866.725</v>
-      </c>
-      <c r="C103" s="36" t="n">
-        <v>6514826.936</v>
-      </c>
-      <c r="D103" s="37" t="n">
-        <v>118.575</v>
-      </c>
-      <c r="E103" s="38" t="n">
-        <v>18.237</v>
-      </c>
-      <c r="F103" s="39" t="n">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="35" t="inlineStr">
-        <is>
-          <t>2+475</t>
-        </is>
-      </c>
-      <c r="B104" s="36" t="n">
-        <v>836870.709</v>
-      </c>
-      <c r="C104" s="36" t="n">
-        <v>6514851.942</v>
-      </c>
-      <c r="D104" s="37" t="n">
-        <v>118.638</v>
-      </c>
-      <c r="E104" s="38" t="n">
-        <v>18.1435</v>
-      </c>
-      <c r="F104" s="39" t="n">
-        <v>2475</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="30" t="inlineStr">
-        <is>
-          <t>2+500</t>
-        </is>
-      </c>
-      <c r="B105" s="31" t="n">
-        <v>836874.608</v>
-      </c>
-      <c r="C105" s="31" t="n">
-        <v>6514876.969</v>
-      </c>
-      <c r="D105" s="32" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="E105" s="33" t="n">
-        <v>18.0498</v>
-      </c>
-      <c r="F105" s="34" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="35" t="inlineStr">
-        <is>
-          <t>2+525</t>
-        </is>
-      </c>
-      <c r="B106" s="36" t="n">
-        <v>836878.425</v>
-      </c>
-      <c r="C106" s="36" t="n">
-        <v>6514902.016</v>
-      </c>
-      <c r="D106" s="37" t="n">
-        <v>118.763</v>
-      </c>
-      <c r="E106" s="38" t="n">
-        <v>17.956</v>
-      </c>
-      <c r="F106" s="39" t="n">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="35" t="inlineStr">
-        <is>
-          <t>2+550</t>
-        </is>
-      </c>
-      <c r="B107" s="36" t="n">
-        <v>836882.164</v>
-      </c>
-      <c r="C107" s="36" t="n">
-        <v>6514927.081</v>
-      </c>
-      <c r="D107" s="37" t="n">
-        <v>118.825</v>
-      </c>
-      <c r="E107" s="38" t="n">
-        <v>17.8623</v>
-      </c>
-      <c r="F107" s="39" t="n">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="35" t="inlineStr">
-        <is>
-          <t>2+575</t>
-        </is>
-      </c>
-      <c r="B108" s="36" t="n">
-        <v>836885.828</v>
-      </c>
-      <c r="C108" s="36" t="n">
-        <v>6514952.162</v>
-      </c>
-      <c r="D108" s="37" t="n">
-        <v>118.888</v>
-      </c>
-      <c r="E108" s="38" t="n">
-        <v>17.7688</v>
-      </c>
-      <c r="F108" s="39" t="n">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="30" t="inlineStr">
-        <is>
-          <t>2+600</t>
-        </is>
-      </c>
-      <c r="B109" s="31" t="n">
-        <v>836889.423</v>
-      </c>
-      <c r="C109" s="31" t="n">
-        <v>6514977.259</v>
-      </c>
-      <c r="D109" s="32" t="n">
-        <v>118.95</v>
-      </c>
-      <c r="E109" s="33" t="n">
-        <v>17.6754</v>
-      </c>
-      <c r="F109" s="34" t="n">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="35" t="inlineStr">
-        <is>
-          <t>2+625</t>
-        </is>
-      </c>
-      <c r="B110" s="36" t="n">
-        <v>836892.952</v>
-      </c>
-      <c r="C110" s="36" t="n">
-        <v>6515002.369</v>
-      </c>
-      <c r="D110" s="37" t="n">
-        <v>119.013</v>
-      </c>
-      <c r="E110" s="38" t="n">
-        <v>17.5824</v>
-      </c>
-      <c r="F110" s="39" t="n">
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="35" t="inlineStr">
-        <is>
-          <t>2+650</t>
-        </is>
-      </c>
-      <c r="B111" s="36" t="n">
-        <v>836896.419</v>
-      </c>
-      <c r="C111" s="36" t="n">
-        <v>6515027.492</v>
-      </c>
-      <c r="D111" s="37" t="n">
-        <v>119.075</v>
-      </c>
-      <c r="E111" s="38" t="n">
-        <v>17.4898</v>
-      </c>
-      <c r="F111" s="39" t="n">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="35" t="inlineStr">
-        <is>
-          <t>2+675</t>
-        </is>
-      </c>
-      <c r="B112" s="36" t="n">
-        <v>836899.829</v>
-      </c>
-      <c r="C112" s="36" t="n">
-        <v>6515052.626</v>
-      </c>
-      <c r="D112" s="37" t="n">
-        <v>119.138</v>
-      </c>
-      <c r="E112" s="38" t="n">
-        <v>17.3977</v>
-      </c>
-      <c r="F112" s="39" t="n">
-        <v>2675</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="30" t="inlineStr">
-        <is>
-          <t>2+700</t>
-        </is>
-      </c>
-      <c r="B113" s="31" t="n">
-        <v>836903.187</v>
-      </c>
-      <c r="C113" s="31" t="n">
-        <v>6515077.768</v>
-      </c>
-      <c r="D113" s="32" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="E113" s="33" t="n">
-        <v>17.3061</v>
-      </c>
-      <c r="F113" s="34" t="n">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="35" t="inlineStr">
-        <is>
-          <t>2+725</t>
-        </is>
-      </c>
-      <c r="B114" s="36" t="n">
-        <v>836906.498</v>
-      </c>
-      <c r="C114" s="36" t="n">
-        <v>6515102.919</v>
-      </c>
-      <c r="D114" s="37" t="n">
-        <v>119.263</v>
-      </c>
-      <c r="E114" s="38" t="n">
-        <v>17.2153</v>
-      </c>
-      <c r="F114" s="39" t="n">
-        <v>2725</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="35" t="inlineStr">
-        <is>
-          <t>2+750</t>
-        </is>
-      </c>
-      <c r="B115" s="36" t="n">
-        <v>836909.7659999999</v>
-      </c>
-      <c r="C115" s="36" t="n">
-        <v>6515128.075</v>
-      </c>
-      <c r="D115" s="37" t="n">
-        <v>119.325</v>
-      </c>
-      <c r="E115" s="38" t="n">
-        <v>17.1252</v>
-      </c>
-      <c r="F115" s="39" t="n">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="35" t="inlineStr">
-        <is>
-          <t>2+775</t>
-        </is>
-      </c>
-      <c r="B116" s="36" t="n">
-        <v>836912.996</v>
-      </c>
-      <c r="C116" s="36" t="n">
-        <v>6515153.236</v>
-      </c>
-      <c r="D116" s="37" t="n">
-        <v>119.388</v>
-      </c>
-      <c r="E116" s="38" t="n">
-        <v>17.0359</v>
-      </c>
-      <c r="F116" s="39" t="n">
-        <v>2775</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="30" t="inlineStr">
-        <is>
-          <t>2+800</t>
-        </is>
-      </c>
-      <c r="B117" s="31" t="n">
-        <v>836916.194</v>
-      </c>
-      <c r="C117" s="31" t="n">
-        <v>6515178.4</v>
-      </c>
-      <c r="D117" s="32" t="n">
-        <v>119.45</v>
-      </c>
-      <c r="E117" s="33" t="n">
-        <v>16.9477</v>
-      </c>
-      <c r="F117" s="34" t="n">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="35" t="inlineStr">
-        <is>
-          <t>2+825</t>
-        </is>
-      </c>
-      <c r="B118" s="36" t="n">
-        <v>836919.365</v>
-      </c>
-      <c r="C118" s="36" t="n">
-        <v>6515203.566</v>
-      </c>
-      <c r="D118" s="37" t="n">
-        <v>119.513</v>
-      </c>
-      <c r="E118" s="38" t="n">
-        <v>16.8604</v>
-      </c>
-      <c r="F118" s="39" t="n">
-        <v>2825</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="35" t="inlineStr">
-        <is>
-          <t>2+850</t>
-        </is>
-      </c>
-      <c r="B119" s="36" t="n">
-        <v>836922.514</v>
-      </c>
-      <c r="C119" s="36" t="n">
-        <v>6515228.731</v>
-      </c>
-      <c r="D119" s="37" t="n">
-        <v>119.575</v>
-      </c>
-      <c r="E119" s="38" t="n">
-        <v>16.7742</v>
-      </c>
-      <c r="F119" s="39" t="n">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="35" t="inlineStr">
-        <is>
-          <t>2+875</t>
-        </is>
-      </c>
-      <c r="B120" s="36" t="n">
-        <v>836925.6459999999</v>
-      </c>
-      <c r="C120" s="36" t="n">
-        <v>6515253.894</v>
-      </c>
-      <c r="D120" s="37" t="n">
-        <v>119.638</v>
-      </c>
-      <c r="E120" s="38" t="n">
-        <v>16.6893</v>
-      </c>
-      <c r="F120" s="39" t="n">
-        <v>2875</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="30" t="inlineStr">
-        <is>
-          <t>2+900</t>
-        </is>
-      </c>
-      <c r="B121" s="31" t="n">
-        <v>836928.768</v>
-      </c>
-      <c r="C121" s="31" t="n">
-        <v>6515279.054</v>
-      </c>
-      <c r="D121" s="32" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="E121" s="33" t="n">
-        <v>16.6056</v>
-      </c>
-      <c r="F121" s="34" t="n">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="35" t="inlineStr">
-        <is>
-          <t>2+925</t>
-        </is>
-      </c>
-      <c r="B122" s="36" t="n">
-        <v>836931.885</v>
-      </c>
-      <c r="C122" s="36" t="n">
-        <v>6515304.21</v>
-      </c>
-      <c r="D122" s="37" t="n">
-        <v>119.763</v>
-      </c>
-      <c r="E122" s="38" t="n">
-        <v>16.5233</v>
-      </c>
-      <c r="F122" s="39" t="n">
-        <v>2925</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="35" t="inlineStr">
-        <is>
-          <t>2+950</t>
-        </is>
-      </c>
-      <c r="B123" s="36" t="n">
-        <v>836935.002</v>
-      </c>
-      <c r="C123" s="36" t="n">
-        <v>6515329.359</v>
-      </c>
-      <c r="D123" s="37" t="n">
-        <v>119.825</v>
-      </c>
-      <c r="E123" s="38" t="n">
-        <v>16.4424</v>
-      </c>
-      <c r="F123" s="39" t="n">
-        <v>2950</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="35" t="inlineStr">
-        <is>
-          <t>2+975</t>
-        </is>
-      </c>
-      <c r="B124" s="36" t="n">
-        <v>836938.126</v>
-      </c>
-      <c r="C124" s="36" t="n">
-        <v>6515354.5</v>
-      </c>
-      <c r="D124" s="37" t="n">
-        <v>119.888</v>
-      </c>
-      <c r="E124" s="38" t="n">
-        <v>16.3631</v>
-      </c>
-      <c r="F124" s="39" t="n">
-        <v>2975</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="30" t="inlineStr">
-        <is>
-          <t>3+000</t>
-        </is>
-      </c>
-      <c r="B125" s="31" t="n">
-        <v>836941.262</v>
-      </c>
-      <c r="C125" s="31" t="n">
-        <v>6515379.632</v>
-      </c>
-      <c r="D125" s="32" t="n">
-        <v>119.95</v>
-      </c>
-      <c r="E125" s="33" t="n">
-        <v>16.2853</v>
-      </c>
-      <c r="F125" s="34" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="35" t="inlineStr">
-        <is>
-          <t>3+025</t>
-        </is>
-      </c>
-      <c r="B126" s="36" t="n">
-        <v>836944.416</v>
-      </c>
-      <c r="C126" s="36" t="n">
-        <v>6515404.752</v>
-      </c>
-      <c r="D126" s="37" t="n">
-        <v>120.013</v>
-      </c>
-      <c r="E126" s="38" t="n">
-        <v>16.2092</v>
-      </c>
-      <c r="F126" s="39" t="n">
-        <v>3025</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="35" t="inlineStr">
-        <is>
-          <t>3+050</t>
-        </is>
-      </c>
-      <c r="B127" s="36" t="n">
-        <v>836947.595</v>
-      </c>
-      <c r="C127" s="36" t="n">
-        <v>6515429.861</v>
-      </c>
-      <c r="D127" s="37" t="n">
-        <v>120.075</v>
-      </c>
-      <c r="E127" s="38" t="n">
-        <v>16.1349</v>
-      </c>
-      <c r="F127" s="39" t="n">
-        <v>3050</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="35" t="inlineStr">
-        <is>
-          <t>3+075</t>
-        </is>
-      </c>
-      <c r="B128" s="36" t="n">
-        <v>836950.804</v>
-      </c>
-      <c r="C128" s="36" t="n">
-        <v>6515454.955</v>
-      </c>
-      <c r="D128" s="37" t="n">
-        <v>120.138</v>
-      </c>
-      <c r="E128" s="38" t="n">
-        <v>16.0624</v>
-      </c>
-      <c r="F128" s="39" t="n">
-        <v>3075</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="30" t="inlineStr">
-        <is>
-          <t>3+100</t>
-        </is>
-      </c>
-      <c r="B129" s="31" t="n">
-        <v>836954.049</v>
-      </c>
-      <c r="C129" s="31" t="n">
-        <v>6515480.034</v>
-      </c>
-      <c r="D129" s="32" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="E129" s="33" t="n">
-        <v>15.9918</v>
-      </c>
-      <c r="F129" s="34" t="n">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="35" t="inlineStr">
-        <is>
-          <t>3+125</t>
-        </is>
-      </c>
-      <c r="B130" s="36" t="n">
-        <v>836957.336</v>
-      </c>
-      <c r="C130" s="36" t="n">
-        <v>6515505.096</v>
-      </c>
-      <c r="D130" s="37" t="n">
-        <v>120.263</v>
-      </c>
-      <c r="E130" s="38" t="n">
-        <v>15.9231</v>
-      </c>
-      <c r="F130" s="39" t="n">
-        <v>3125</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="35" t="inlineStr">
-        <is>
-          <t>3+150</t>
-        </is>
-      </c>
-      <c r="B131" s="36" t="n">
-        <v>836960.671</v>
-      </c>
-      <c r="C131" s="36" t="n">
-        <v>6515530.139</v>
-      </c>
-      <c r="D131" s="37" t="n">
-        <v>120.325</v>
-      </c>
-      <c r="E131" s="38" t="n">
-        <v>15.8565</v>
-      </c>
-      <c r="F131" s="39" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="35" t="inlineStr">
-        <is>
-          <t>3+175</t>
-        </is>
-      </c>
-      <c r="B132" s="36" t="n">
-        <v>836964.062</v>
-      </c>
-      <c r="C132" s="36" t="n">
-        <v>6515555.163</v>
-      </c>
-      <c r="D132" s="37" t="n">
-        <v>120.388</v>
-      </c>
-      <c r="E132" s="38" t="n">
-        <v>15.792</v>
-      </c>
-      <c r="F132" s="39" t="n">
-        <v>3175</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="30" t="inlineStr">
-        <is>
-          <t>3+200</t>
-        </is>
-      </c>
-      <c r="B133" s="31" t="n">
-        <v>836967.512</v>
-      </c>
-      <c r="C133" s="31" t="n">
-        <v>6515580.166</v>
-      </c>
-      <c r="D133" s="32" t="n">
-        <v>120.45</v>
-      </c>
-      <c r="E133" s="33" t="n">
-        <v>15.7296</v>
-      </c>
-      <c r="F133" s="34" t="n">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="35" t="inlineStr">
-        <is>
-          <t>3+225</t>
-        </is>
-      </c>
-      <c r="B134" s="36" t="n">
-        <v>836971.03</v>
-      </c>
-      <c r="C134" s="36" t="n">
-        <v>6515605.146</v>
-      </c>
-      <c r="D134" s="37" t="n">
-        <v>120.513</v>
-      </c>
-      <c r="E134" s="38" t="n">
-        <v>15.6694</v>
-      </c>
-      <c r="F134" s="39" t="n">
-        <v>3225</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="35" t="inlineStr">
-        <is>
-          <t>3+250</t>
-        </is>
-      </c>
-      <c r="B135" s="36" t="n">
-        <v>836974.62</v>
-      </c>
-      <c r="C135" s="36" t="n">
-        <v>6515630.102</v>
-      </c>
-      <c r="D135" s="37" t="n">
-        <v>120.575</v>
-      </c>
-      <c r="E135" s="38" t="n">
-        <v>15.6115</v>
-      </c>
-      <c r="F135" s="39" t="n">
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="35" t="inlineStr">
-        <is>
-          <t>3+275</t>
-        </is>
-      </c>
-      <c r="B136" s="36" t="n">
-        <v>836978.289</v>
-      </c>
-      <c r="C136" s="36" t="n">
-        <v>6515655.033</v>
-      </c>
-      <c r="D136" s="37" t="n">
-        <v>120.638</v>
-      </c>
-      <c r="E136" s="38" t="n">
-        <v>15.556</v>
-      </c>
-      <c r="F136" s="39" t="n">
-        <v>3275</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="30" t="inlineStr">
-        <is>
-          <t>3+300</t>
-        </is>
-      </c>
-      <c r="B137" s="31" t="n">
-        <v>836982.044</v>
-      </c>
-      <c r="C137" s="31" t="n">
-        <v>6515679.937</v>
-      </c>
-      <c r="D137" s="32" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="E137" s="33" t="n">
-        <v>15.5028</v>
-      </c>
-      <c r="F137" s="34" t="n">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="35" t="inlineStr">
-        <is>
-          <t>3+325</t>
-        </is>
-      </c>
-      <c r="B138" s="36" t="n">
-        <v>836985.889</v>
-      </c>
-      <c r="C138" s="36" t="n">
-        <v>6515704.813</v>
-      </c>
-      <c r="D138" s="37" t="n">
-        <v>120.763</v>
-      </c>
-      <c r="E138" s="38" t="n">
-        <v>15.4521</v>
-      </c>
-      <c r="F138" s="39" t="n">
-        <v>3325</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="35" t="inlineStr">
-        <is>
-          <t>3+350</t>
-        </is>
-      </c>
-      <c r="B139" s="36" t="n">
-        <v>836989.831</v>
-      </c>
-      <c r="C139" s="36" t="n">
-        <v>6515729.66</v>
-      </c>
-      <c r="D139" s="37" t="n">
-        <v>120.825</v>
-      </c>
-      <c r="E139" s="38" t="n">
-        <v>15.4039</v>
-      </c>
-      <c r="F139" s="39" t="n">
-        <v>3350</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="35" t="inlineStr">
-        <is>
-          <t>3+375</t>
-        </is>
-      </c>
-      <c r="B140" s="36" t="n">
-        <v>836993.875</v>
-      </c>
-      <c r="C140" s="36" t="n">
-        <v>6515754.476</v>
-      </c>
-      <c r="D140" s="37" t="n">
-        <v>120.888</v>
-      </c>
-      <c r="E140" s="38" t="n">
-        <v>15.3582</v>
-      </c>
-      <c r="F140" s="39" t="n">
-        <v>3375</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="30" t="inlineStr">
-        <is>
-          <t>3+400</t>
-        </is>
-      </c>
-      <c r="B141" s="31" t="n">
-        <v>836998.029</v>
-      </c>
-      <c r="C141" s="31" t="n">
-        <v>6515779.26</v>
-      </c>
-      <c r="D141" s="32" t="n">
-        <v>120.95</v>
-      </c>
-      <c r="E141" s="33" t="n">
-        <v>15.315</v>
-      </c>
-      <c r="F141" s="34" t="n">
-        <v>3400</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="35" t="inlineStr">
-        <is>
-          <t>3+425</t>
-        </is>
-      </c>
-      <c r="B142" s="36" t="n">
-        <v>837002.296</v>
-      </c>
-      <c r="C142" s="36" t="n">
-        <v>6515804.011</v>
-      </c>
-      <c r="D142" s="37" t="n">
-        <v>121.013</v>
-      </c>
-      <c r="E142" s="38" t="n">
-        <v>15.2745</v>
-      </c>
-      <c r="F142" s="39" t="n">
-        <v>3425</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="35" t="inlineStr">
-        <is>
-          <t>3+450</t>
-        </is>
-      </c>
-      <c r="B143" s="36" t="n">
-        <v>837006.684</v>
-      </c>
-      <c r="C143" s="36" t="n">
-        <v>6515828.727</v>
-      </c>
-      <c r="D143" s="37" t="n">
-        <v>121.075</v>
-      </c>
-      <c r="E143" s="38" t="n">
-        <v>15.2367</v>
-      </c>
-      <c r="F143" s="39" t="n">
-        <v>3450</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="35" t="inlineStr">
-        <is>
-          <t>3+475</t>
-        </is>
-      </c>
-      <c r="B144" s="36" t="n">
-        <v>837011.198</v>
-      </c>
-      <c r="C144" s="36" t="n">
-        <v>6515853.408</v>
-      </c>
-      <c r="D144" s="37" t="n">
-        <v>121.138</v>
-      </c>
-      <c r="E144" s="38" t="n">
-        <v>15.2015</v>
-      </c>
-      <c r="F144" s="39" t="n">
-        <v>3475</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="30" t="inlineStr">
-        <is>
-          <t>3+500</t>
-        </is>
-      </c>
-      <c r="B145" s="31" t="n">
-        <v>837015.8419999999</v>
-      </c>
-      <c r="C145" s="31" t="n">
-        <v>6515878.052</v>
-      </c>
-      <c r="D145" s="32" t="n">
-        <v>121.2</v>
-      </c>
-      <c r="E145" s="33" t="n">
-        <v>15.1691</v>
-      </c>
-      <c r="F145" s="34" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="35" t="inlineStr">
-        <is>
-          <t>3+525</t>
-        </is>
-      </c>
-      <c r="B146" s="36" t="n">
-        <v>837020.624</v>
-      </c>
-      <c r="C146" s="36" t="n">
-        <v>6515902.657</v>
-      </c>
-      <c r="D146" s="37" t="n">
-        <v>121.263</v>
-      </c>
-      <c r="E146" s="38" t="n">
-        <v>15.1395</v>
-      </c>
-      <c r="F146" s="39" t="n">
-        <v>3525</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="35" t="inlineStr">
-        <is>
-          <t>3+550</t>
-        </is>
-      </c>
-      <c r="B147" s="36" t="n">
-        <v>837025.547</v>
-      </c>
-      <c r="C147" s="36" t="n">
-        <v>6515927.224</v>
-      </c>
-      <c r="D147" s="37" t="n">
-        <v>121.325</v>
-      </c>
-      <c r="E147" s="38" t="n">
-        <v>15.1126</v>
-      </c>
-      <c r="F147" s="39" t="n">
-        <v>3550</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="35" t="inlineStr">
-        <is>
-          <t>3+575</t>
-        </is>
-      </c>
-      <c r="B148" s="36" t="n">
-        <v>837030.617</v>
-      </c>
-      <c r="C148" s="36" t="n">
-        <v>6515951.75</v>
-      </c>
-      <c r="D148" s="37" t="n">
-        <v>121.388</v>
-      </c>
-      <c r="E148" s="38" t="n">
-        <v>15.0886</v>
-      </c>
-      <c r="F148" s="39" t="n">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="30" t="inlineStr">
-        <is>
-          <t>3+600</t>
-        </is>
-      </c>
-      <c r="B149" s="31" t="n">
-        <v>837035.839</v>
-      </c>
-      <c r="C149" s="31" t="n">
-        <v>6515976.234</v>
-      </c>
-      <c r="D149" s="32" t="n">
-        <v>121.45</v>
-      </c>
-      <c r="E149" s="33" t="n">
-        <v>15.0674</v>
-      </c>
-      <c r="F149" s="34" t="n">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="35" t="inlineStr">
-        <is>
-          <t>3+625</t>
-        </is>
-      </c>
-      <c r="B150" s="36" t="n">
-        <v>837041.218</v>
-      </c>
-      <c r="C150" s="36" t="n">
-        <v>6516000.676</v>
-      </c>
-      <c r="D150" s="37" t="n">
-        <v>121.513</v>
-      </c>
-      <c r="E150" s="38" t="n">
-        <v>15.0491</v>
-      </c>
-      <c r="F150" s="39" t="n">
-        <v>3625</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="35" t="inlineStr">
-        <is>
-          <t>3+650</t>
-        </is>
-      </c>
-      <c r="B151" s="36" t="n">
-        <v>837046.759</v>
-      </c>
-      <c r="C151" s="36" t="n">
-        <v>6516025.074</v>
-      </c>
-      <c r="D151" s="37" t="n">
-        <v>121.575</v>
-      </c>
-      <c r="E151" s="38" t="n">
-        <v>15.0336</v>
-      </c>
-      <c r="F151" s="39" t="n">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="35" t="inlineStr">
-        <is>
-          <t>3+675</t>
-        </is>
-      </c>
-      <c r="B152" s="36" t="n">
-        <v>837052.466</v>
-      </c>
-      <c r="C152" s="36" t="n">
-        <v>6516049.427</v>
-      </c>
-      <c r="D152" s="37" t="n">
-        <v>121.638</v>
-      </c>
-      <c r="E152" s="38" t="n">
-        <v>15.0211</v>
-      </c>
-      <c r="F152" s="39" t="n">
-        <v>3675</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="30" t="inlineStr">
-        <is>
-          <t>3+700</t>
-        </is>
-      </c>
-      <c r="B153" s="31" t="n">
-        <v>837058.345</v>
-      </c>
-      <c r="C153" s="31" t="n">
-        <v>6516073.734</v>
-      </c>
-      <c r="D153" s="32" t="n">
-        <v>121.7</v>
-      </c>
-      <c r="E153" s="33" t="n">
-        <v>15.0114</v>
-      </c>
-      <c r="F153" s="34" t="n">
-        <v>3700</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="35" t="inlineStr">
-        <is>
-          <t>3+725</t>
-        </is>
-      </c>
-      <c r="B154" s="36" t="n">
-        <v>837064.398</v>
-      </c>
-      <c r="C154" s="36" t="n">
-        <v>6516097.994</v>
-      </c>
-      <c r="D154" s="37" t="n">
-        <v>121.763</v>
-      </c>
-      <c r="E154" s="38" t="n">
-        <v>15.0047</v>
-      </c>
-      <c r="F154" s="39" t="n">
-        <v>3725</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="35" t="inlineStr">
-        <is>
-          <t>3+750</t>
-        </is>
-      </c>
-      <c r="B155" s="36" t="n">
-        <v>837070.63</v>
-      </c>
-      <c r="C155" s="36" t="n">
-        <v>6516122.206</v>
-      </c>
-      <c r="D155" s="37" t="n">
-        <v>121.825</v>
-      </c>
-      <c r="E155" s="38" t="n">
-        <v>15.0009</v>
-      </c>
-      <c r="F155" s="39" t="n">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="35" t="inlineStr">
-        <is>
-          <t>3+775</t>
-        </is>
-      </c>
-      <c r="B156" s="36" t="n">
-        <v>837077.046</v>
-      </c>
-      <c r="C156" s="36" t="n">
-        <v>6516146.369</v>
-      </c>
-      <c r="D156" s="37" t="n">
-        <v>121.888</v>
-      </c>
-      <c r="E156" s="38" t="n">
-        <v>15.0001</v>
-      </c>
-      <c r="F156" s="39" t="n">
-        <v>3775</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="30" t="inlineStr">
-        <is>
-          <t>3+800</t>
-        </is>
-      </c>
-      <c r="B157" s="31" t="n">
-        <v>837083.648</v>
-      </c>
-      <c r="C157" s="31" t="n">
-        <v>6516170.482</v>
-      </c>
-      <c r="D157" s="32" t="n">
-        <v>121.95</v>
-      </c>
-      <c r="E157" s="33" t="n">
-        <v>15.0021</v>
-      </c>
-      <c r="F157" s="34" t="n">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="35" t="inlineStr">
-        <is>
-          <t>3+825</t>
-        </is>
-      </c>
-      <c r="B158" s="36" t="n">
-        <v>837090.441</v>
-      </c>
-      <c r="C158" s="36" t="n">
-        <v>6516194.543</v>
-      </c>
-      <c r="D158" s="37" t="n">
-        <v>122.013</v>
-      </c>
-      <c r="E158" s="38" t="n">
-        <v>15.0071</v>
-      </c>
-      <c r="F158" s="39" t="n">
-        <v>3825</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="35" t="inlineStr">
-        <is>
-          <t>3+850</t>
-        </is>
-      </c>
-      <c r="B159" s="36" t="n">
-        <v>837097.428</v>
-      </c>
-      <c r="C159" s="36" t="n">
-        <v>6516218.553</v>
-      </c>
-      <c r="D159" s="37" t="n">
-        <v>122.075</v>
-      </c>
-      <c r="E159" s="38" t="n">
-        <v>15.015</v>
-      </c>
-      <c r="F159" s="39" t="n">
-        <v>3850</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="35" t="inlineStr">
-        <is>
-          <t>3+875</t>
-        </is>
-      </c>
-      <c r="B160" s="36" t="n">
-        <v>837104.612</v>
-      </c>
-      <c r="C160" s="36" t="n">
-        <v>6516242.51</v>
-      </c>
-      <c r="D160" s="37" t="n">
-        <v>122.138</v>
-      </c>
-      <c r="E160" s="38" t="n">
-        <v>15.0258</v>
-      </c>
-      <c r="F160" s="39" t="n">
-        <v>3875</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="30" t="inlineStr">
-        <is>
-          <t>3+900</t>
-        </is>
-      </c>
-      <c r="B161" s="31" t="n">
-        <v>837111.996</v>
-      </c>
-      <c r="C161" s="31" t="n">
-        <v>6516266.413</v>
-      </c>
-      <c r="D161" s="32" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="E161" s="33" t="n">
-        <v>15.0396</v>
-      </c>
-      <c r="F161" s="34" t="n">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="35" t="inlineStr">
-        <is>
-          <t>3+925</t>
-        </is>
-      </c>
-      <c r="B162" s="36" t="n">
-        <v>837119.583</v>
-      </c>
-      <c r="C162" s="36" t="n">
-        <v>6516290.261</v>
-      </c>
-      <c r="D162" s="37" t="n">
-        <v>122.263</v>
-      </c>
-      <c r="E162" s="38" t="n">
-        <v>15.0562</v>
-      </c>
-      <c r="F162" s="39" t="n">
-        <v>3925</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="35" t="inlineStr">
-        <is>
-          <t>3+950</t>
-        </is>
-      </c>
-      <c r="B163" s="36" t="n">
-        <v>837127.375</v>
-      </c>
-      <c r="C163" s="36" t="n">
-        <v>6516314.053</v>
-      </c>
-      <c r="D163" s="37" t="n">
-        <v>122.325</v>
-      </c>
-      <c r="E163" s="38" t="n">
-        <v>15.0757</v>
-      </c>
-      <c r="F163" s="39" t="n">
-        <v>3950</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="35" t="inlineStr">
-        <is>
-          <t>3+975</t>
-        </is>
-      </c>
-      <c r="B164" s="36" t="n">
-        <v>837135.374</v>
-      </c>
-      <c r="C164" s="36" t="n">
-        <v>6516337.789</v>
-      </c>
-      <c r="D164" s="37" t="n">
-        <v>122.388</v>
-      </c>
-      <c r="E164" s="38" t="n">
-        <v>15.098</v>
-      </c>
-      <c r="F164" s="39" t="n">
-        <v>3975</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="30" t="inlineStr">
-        <is>
-          <t>4+000</t>
-        </is>
-      </c>
-      <c r="B165" s="31" t="n">
-        <v>837143.584</v>
-      </c>
-      <c r="C165" s="31" t="n">
-        <v>6516361.468</v>
-      </c>
-      <c r="D165" s="32" t="n">
-        <v>122.45</v>
-      </c>
-      <c r="E165" s="33" t="n">
-        <v>15.1232</v>
-      </c>
-      <c r="F165" s="34" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="35" t="inlineStr">
-        <is>
-          <t>4+025</t>
-        </is>
-      </c>
-      <c r="B166" s="36" t="n">
-        <v>837152.004</v>
-      </c>
-      <c r="C166" s="36" t="n">
-        <v>6516385.088</v>
-      </c>
-      <c r="D166" s="37" t="n">
-        <v>122.513</v>
-      </c>
-      <c r="E166" s="38" t="n">
-        <v>15.1512</v>
-      </c>
-      <c r="F166" s="39" t="n">
-        <v>4025</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="35" t="inlineStr">
-        <is>
-          <t>4+050</t>
-        </is>
-      </c>
-      <c r="B167" s="36" t="n">
-        <v>837160.638</v>
-      </c>
-      <c r="C167" s="36" t="n">
-        <v>6516408.65</v>
-      </c>
-      <c r="D167" s="37" t="n">
-        <v>122.575</v>
-      </c>
-      <c r="E167" s="38" t="n">
-        <v>15.182</v>
-      </c>
-      <c r="F167" s="39" t="n">
-        <v>4050</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="35" t="inlineStr">
-        <is>
-          <t>4+075</t>
-        </is>
-      </c>
-      <c r="B168" s="36" t="n">
-        <v>837169.486</v>
-      </c>
-      <c r="C168" s="36" t="n">
-        <v>6516432.153</v>
-      </c>
-      <c r="D168" s="37" t="n">
-        <v>122.638</v>
-      </c>
-      <c r="E168" s="38" t="n">
-        <v>15.2155</v>
-      </c>
-      <c r="F168" s="39" t="n">
-        <v>4075</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="30" t="inlineStr">
-        <is>
-          <t>4+100</t>
-        </is>
-      </c>
-      <c r="B169" s="31" t="n">
-        <v>837178.55</v>
-      </c>
-      <c r="C169" s="31" t="n">
-        <v>6516455.595</v>
-      </c>
-      <c r="D169" s="32" t="n">
-        <v>122.7</v>
-      </c>
-      <c r="E169" s="33" t="n">
-        <v>15.2518</v>
-      </c>
-      <c r="F169" s="34" t="n">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="35" t="inlineStr">
-        <is>
-          <t>4+125</t>
-        </is>
-      </c>
-      <c r="B170" s="36" t="n">
-        <v>837187.83</v>
-      </c>
-      <c r="C170" s="36" t="n">
-        <v>6516478.976</v>
-      </c>
-      <c r="D170" s="37" t="n">
-        <v>122.763</v>
-      </c>
-      <c r="E170" s="38" t="n">
-        <v>15.2907</v>
-      </c>
-      <c r="F170" s="39" t="n">
-        <v>4125</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="35" t="inlineStr">
-        <is>
-          <t>4+150</t>
-        </is>
-      </c>
-      <c r="B171" s="36" t="n">
-        <v>837197.328</v>
-      </c>
-      <c r="C171" s="36" t="n">
-        <v>6516502.296</v>
-      </c>
-      <c r="D171" s="37" t="n">
-        <v>122.825</v>
-      </c>
-      <c r="E171" s="38" t="n">
-        <v>15.3323</v>
-      </c>
-      <c r="F171" s="39" t="n">
-        <v>4150</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="35" t="inlineStr">
-        <is>
-          <t>4+175</t>
-        </is>
-      </c>
-      <c r="B172" s="36" t="n">
-        <v>837207.0429999999</v>
-      </c>
-      <c r="C172" s="36" t="n">
-        <v>6516525.554</v>
-      </c>
-      <c r="D172" s="37" t="n">
-        <v>122.888</v>
-      </c>
-      <c r="E172" s="38" t="n">
-        <v>15.3765</v>
-      </c>
-      <c r="F172" s="39" t="n">
-        <v>4175</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="30" t="inlineStr">
-        <is>
-          <t>4+200</t>
-        </is>
-      </c>
-      <c r="B173" s="31" t="n">
-        <v>837216.975</v>
-      </c>
-      <c r="C173" s="31" t="n">
-        <v>6516548.749</v>
-      </c>
-      <c r="D173" s="32" t="n">
-        <v>122.95</v>
-      </c>
-      <c r="E173" s="33" t="n">
-        <v>15.4232</v>
-      </c>
-      <c r="F173" s="34" t="n">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="35" t="inlineStr">
-        <is>
-          <t>4+225</t>
-        </is>
-      </c>
-      <c r="B174" s="36" t="n">
-        <v>837227.125</v>
-      </c>
-      <c r="C174" s="36" t="n">
-        <v>6516571.881</v>
-      </c>
-      <c r="D174" s="37" t="n">
-        <v>123.013</v>
-      </c>
-      <c r="E174" s="38" t="n">
-        <v>15.4725</v>
-      </c>
-      <c r="F174" s="39" t="n">
-        <v>4225</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="35" t="inlineStr">
-        <is>
-          <t>4+250</t>
-        </is>
-      </c>
-      <c r="B175" s="36" t="n">
-        <v>837237.491</v>
-      </c>
-      <c r="C175" s="36" t="n">
-        <v>6516594.95</v>
-      </c>
-      <c r="D175" s="37" t="n">
-        <v>123.075</v>
-      </c>
-      <c r="E175" s="38" t="n">
-        <v>15.5242</v>
-      </c>
-      <c r="F175" s="39" t="n">
-        <v>4250</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="35" t="inlineStr">
-        <is>
-          <t>4+275</t>
-        </is>
-      </c>
-      <c r="B176" s="36" t="n">
-        <v>837248.075</v>
-      </c>
-      <c r="C176" s="36" t="n">
-        <v>6516617.955</v>
-      </c>
-      <c r="D176" s="37" t="n">
-        <v>123.138</v>
-      </c>
-      <c r="E176" s="38" t="n">
-        <v>15.5783</v>
-      </c>
-      <c r="F176" s="39" t="n">
-        <v>4275</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="30" t="inlineStr">
-        <is>
-          <t>4+300</t>
-        </is>
-      </c>
-      <c r="B177" s="31" t="n">
-        <v>837258.873</v>
-      </c>
-      <c r="C177" s="31" t="n">
-        <v>6516640.895</v>
-      </c>
-      <c r="D177" s="32" t="n">
-        <v>123.2</v>
-      </c>
-      <c r="E177" s="33" t="n">
-        <v>15.6348</v>
-      </c>
-      <c r="F177" s="34" t="n">
-        <v>4300</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="35" t="inlineStr">
-        <is>
-          <t>4+325</t>
-        </is>
-      </c>
-      <c r="B178" s="36" t="n">
-        <v>837269.8860000001</v>
-      </c>
-      <c r="C178" s="36" t="n">
-        <v>6516663.771</v>
-      </c>
-      <c r="D178" s="37" t="n">
-        <v>123.263</v>
-      </c>
-      <c r="E178" s="38" t="n">
-        <v>15.6937</v>
-      </c>
-      <c r="F178" s="39" t="n">
-        <v>4325</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="35" t="inlineStr">
-        <is>
-          <t>4+350</t>
-        </is>
-      </c>
-      <c r="B179" s="36" t="n">
-        <v>837281.111</v>
-      </c>
-      <c r="C179" s="36" t="n">
-        <v>6516686.583</v>
-      </c>
-      <c r="D179" s="37" t="n">
-        <v>123.325</v>
-      </c>
-      <c r="E179" s="38" t="n">
-        <v>15.7547</v>
-      </c>
-      <c r="F179" s="39" t="n">
-        <v>4350</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="35" t="inlineStr">
-        <is>
-          <t>4+375</t>
-        </is>
-      </c>
-      <c r="B180" s="36" t="n">
-        <v>837292.547</v>
-      </c>
-      <c r="C180" s="36" t="n">
-        <v>6516709.33</v>
-      </c>
-      <c r="D180" s="37" t="n">
-        <v>123.388</v>
-      </c>
-      <c r="E180" s="38" t="n">
-        <v>15.818</v>
-      </c>
-      <c r="F180" s="39" t="n">
-        <v>4375</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="30" t="inlineStr">
-        <is>
-          <t>4+400</t>
-        </is>
-      </c>
-      <c r="B181" s="31" t="n">
-        <v>837304.193</v>
-      </c>
-      <c r="C181" s="31" t="n">
-        <v>6516732.011</v>
-      </c>
-      <c r="D181" s="32" t="n">
-        <v>123.45</v>
-      </c>
-      <c r="E181" s="33" t="n">
-        <v>15.8834</v>
-      </c>
-      <c r="F181" s="34" t="n">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="35" t="inlineStr">
-        <is>
-          <t>4+425</t>
-        </is>
-      </c>
-      <c r="B182" s="36" t="n">
-        <v>837316.045</v>
-      </c>
-      <c r="C182" s="36" t="n">
-        <v>6516754.628</v>
-      </c>
-      <c r="D182" s="37" t="n">
-        <v>123.513</v>
-      </c>
-      <c r="E182" s="38" t="n">
-        <v>15.9508</v>
-      </c>
-      <c r="F182" s="39" t="n">
-        <v>4425</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="35" t="inlineStr">
-        <is>
-          <t>4+450</t>
-        </is>
-      </c>
-      <c r="B183" s="36" t="n">
-        <v>837328.102</v>
-      </c>
-      <c r="C183" s="36" t="n">
-        <v>6516777.18</v>
-      </c>
-      <c r="D183" s="37" t="n">
-        <v>123.575</v>
-      </c>
-      <c r="E183" s="38" t="n">
-        <v>16.0203</v>
-      </c>
-      <c r="F183" s="39" t="n">
-        <v>4450</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="35" t="inlineStr">
-        <is>
-          <t>4+475</t>
-        </is>
-      </c>
-      <c r="B184" s="36" t="n">
-        <v>837340.36</v>
-      </c>
-      <c r="C184" s="36" t="n">
-        <v>6516799.667</v>
-      </c>
-      <c r="D184" s="37" t="n">
-        <v>123.638</v>
-      </c>
-      <c r="E184" s="38" t="n">
-        <v>16.0917</v>
-      </c>
-      <c r="F184" s="39" t="n">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="30" t="inlineStr">
-        <is>
-          <t>4+500</t>
-        </is>
-      </c>
-      <c r="B185" s="31" t="n">
-        <v>837352.816</v>
-      </c>
-      <c r="C185" s="31" t="n">
-        <v>6516822.089</v>
-      </c>
-      <c r="D185" s="32" t="n">
-        <v>123.7</v>
-      </c>
-      <c r="E185" s="33" t="n">
-        <v>16.165</v>
-      </c>
-      <c r="F185" s="34" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="35" t="inlineStr">
-        <is>
-          <t>4+525</t>
-        </is>
-      </c>
-      <c r="B186" s="36" t="n">
-        <v>837365.468</v>
-      </c>
-      <c r="C186" s="36" t="n">
-        <v>6516844.446</v>
-      </c>
-      <c r="D186" s="37" t="n">
-        <v>123.763</v>
-      </c>
-      <c r="E186" s="38" t="n">
-        <v>16.24</v>
-      </c>
-      <c r="F186" s="39" t="n">
-        <v>4525</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="35" t="inlineStr">
-        <is>
-          <t>4+550</t>
-        </is>
-      </c>
-      <c r="B187" s="36" t="n">
-        <v>837378.312</v>
-      </c>
-      <c r="C187" s="36" t="n">
-        <v>6516866.74</v>
-      </c>
-      <c r="D187" s="37" t="n">
-        <v>123.825</v>
-      </c>
-      <c r="E187" s="38" t="n">
-        <v>16.3168</v>
-      </c>
-      <c r="F187" s="39" t="n">
-        <v>4550</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="35" t="inlineStr">
-        <is>
-          <t>4+575</t>
-        </is>
-      </c>
-      <c r="B188" s="36" t="n">
-        <v>837391.343</v>
-      </c>
-      <c r="C188" s="36" t="n">
-        <v>6516888.97</v>
-      </c>
-      <c r="D188" s="37" t="n">
-        <v>123.888</v>
-      </c>
-      <c r="E188" s="38" t="n">
-        <v>16.3952</v>
-      </c>
-      <c r="F188" s="39" t="n">
-        <v>4575</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="30" t="inlineStr">
-        <is>
-          <t>4+600</t>
-        </is>
-      </c>
-      <c r="B189" s="31" t="n">
-        <v>837404.559</v>
-      </c>
-      <c r="C189" s="31" t="n">
-        <v>6516911.137</v>
-      </c>
-      <c r="D189" s="32" t="n">
-        <v>123.95</v>
-      </c>
-      <c r="E189" s="33" t="n">
-        <v>16.4752</v>
-      </c>
-      <c r="F189" s="34" t="n">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="35" t="inlineStr">
-        <is>
-          <t>4+625</t>
-        </is>
-      </c>
-      <c r="B190" s="36" t="n">
-        <v>837417.953</v>
-      </c>
-      <c r="C190" s="36" t="n">
-        <v>6516933.241</v>
-      </c>
-      <c r="D190" s="37" t="n">
-        <v>124.013</v>
-      </c>
-      <c r="E190" s="38" t="n">
-        <v>16.5566</v>
-      </c>
-      <c r="F190" s="39" t="n">
-        <v>4625</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="35" t="inlineStr">
-        <is>
-          <t>4+650</t>
-        </is>
-      </c>
-      <c r="B191" s="36" t="n">
-        <v>837431.523</v>
-      </c>
-      <c r="C191" s="36" t="n">
-        <v>6516955.283</v>
-      </c>
-      <c r="D191" s="37" t="n">
-        <v>124.075</v>
-      </c>
-      <c r="E191" s="38" t="n">
-        <v>16.6395</v>
-      </c>
-      <c r="F191" s="39" t="n">
-        <v>4650</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="35" t="inlineStr">
-        <is>
-          <t>4+675</t>
-        </is>
-      </c>
-      <c r="B192" s="36" t="n">
-        <v>837445.264</v>
-      </c>
-      <c r="C192" s="36" t="n">
-        <v>6516977.264</v>
-      </c>
-      <c r="D192" s="37" t="n">
-        <v>124.138</v>
-      </c>
-      <c r="E192" s="38" t="n">
-        <v>16.7237</v>
-      </c>
-      <c r="F192" s="39" t="n">
-        <v>4675</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="30" t="inlineStr">
-        <is>
-          <t>4+700</t>
-        </is>
-      </c>
-      <c r="B193" s="31" t="n">
-        <v>837459.169</v>
-      </c>
-      <c r="C193" s="31" t="n">
-        <v>6516999.184</v>
-      </c>
-      <c r="D193" s="32" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="E193" s="33" t="n">
-        <v>16.8092</v>
-      </c>
-      <c r="F193" s="34" t="n">
-        <v>4700</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="35" t="inlineStr">
-        <is>
-          <t>4+725</t>
-        </is>
-      </c>
-      <c r="B194" s="36" t="n">
-        <v>837473.235</v>
-      </c>
-      <c r="C194" s="36" t="n">
-        <v>6517021.045</v>
-      </c>
-      <c r="D194" s="37" t="n">
-        <v>124.263</v>
-      </c>
-      <c r="E194" s="38" t="n">
-        <v>16.8958</v>
-      </c>
-      <c r="F194" s="39" t="n">
-        <v>4725</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="35" t="inlineStr">
-        <is>
-          <t>4+750</t>
-        </is>
-      </c>
-      <c r="B195" s="36" t="n">
-        <v>837487.455</v>
-      </c>
-      <c r="C195" s="36" t="n">
-        <v>6517042.848</v>
-      </c>
-      <c r="D195" s="37" t="n">
-        <v>124.325</v>
-      </c>
-      <c r="E195" s="38" t="n">
-        <v>16.9835</v>
-      </c>
-      <c r="F195" s="39" t="n">
-        <v>4750</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="35" t="inlineStr">
-        <is>
-          <t>4+775</t>
-        </is>
-      </c>
-      <c r="B196" s="36" t="n">
-        <v>837501.825</v>
-      </c>
-      <c r="C196" s="36" t="n">
-        <v>6517064.593</v>
-      </c>
-      <c r="D196" s="37" t="n">
-        <v>124.388</v>
-      </c>
-      <c r="E196" s="38" t="n">
-        <v>17.0722</v>
-      </c>
-      <c r="F196" s="39" t="n">
-        <v>4775</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="30" t="inlineStr">
-        <is>
-          <t>4+800</t>
-        </is>
-      </c>
-      <c r="B197" s="31" t="n">
-        <v>837516.3370000001</v>
-      </c>
-      <c r="C197" s="31" t="n">
-        <v>6517086.283</v>
-      </c>
-      <c r="D197" s="32" t="n">
-        <v>124.45</v>
-      </c>
-      <c r="E197" s="33" t="n">
-        <v>17.1618</v>
-      </c>
-      <c r="F197" s="34" t="n">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="35" t="inlineStr">
-        <is>
-          <t>4+825</t>
-        </is>
-      </c>
-      <c r="B198" s="36" t="n">
-        <v>837530.987</v>
-      </c>
-      <c r="C198" s="36" t="n">
-        <v>6517107.917</v>
-      </c>
-      <c r="D198" s="37" t="n">
-        <v>124.513</v>
-      </c>
-      <c r="E198" s="38" t="n">
-        <v>17.2522</v>
-      </c>
-      <c r="F198" s="39" t="n">
-        <v>4825</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="35" t="inlineStr">
-        <is>
-          <t>4+850</t>
-        </is>
-      </c>
-      <c r="B199" s="36" t="n">
-        <v>837545.768</v>
-      </c>
-      <c r="C199" s="36" t="n">
-        <v>6517129.498</v>
-      </c>
-      <c r="D199" s="37" t="n">
-        <v>124.575</v>
-      </c>
-      <c r="E199" s="38" t="n">
-        <v>17.3433</v>
-      </c>
-      <c r="F199" s="39" t="n">
-        <v>4850</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="35" t="inlineStr">
-        <is>
-          <t>4+875</t>
-        </is>
-      </c>
-      <c r="B200" s="36" t="n">
-        <v>837560.672</v>
-      </c>
-      <c r="C200" s="36" t="n">
-        <v>6517151.028</v>
-      </c>
-      <c r="D200" s="37" t="n">
-        <v>124.638</v>
-      </c>
-      <c r="E200" s="38" t="n">
-        <v>17.4351</v>
-      </c>
-      <c r="F200" s="39" t="n">
-        <v>4875</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="30" t="inlineStr">
-        <is>
-          <t>4+900</t>
-        </is>
-      </c>
-      <c r="B201" s="31" t="n">
-        <v>837575.6949999999</v>
-      </c>
-      <c r="C201" s="31" t="n">
-        <v>6517172.507</v>
-      </c>
-      <c r="D201" s="32" t="n">
-        <v>124.7</v>
-      </c>
-      <c r="E201" s="33" t="n">
-        <v>17.5274</v>
-      </c>
-      <c r="F201" s="34" t="n">
-        <v>4900</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="35" t="inlineStr">
-        <is>
-          <t>4+925</t>
-        </is>
-      </c>
-      <c r="B202" s="36" t="n">
-        <v>837590.828</v>
-      </c>
-      <c r="C202" s="36" t="n">
-        <v>6517193.938</v>
-      </c>
-      <c r="D202" s="37" t="n">
-        <v>124.763</v>
-      </c>
-      <c r="E202" s="38" t="n">
-        <v>17.6202</v>
-      </c>
-      <c r="F202" s="39" t="n">
-        <v>4925</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="35" t="inlineStr">
-        <is>
-          <t>4+950</t>
-        </is>
-      </c>
-      <c r="B203" s="36" t="n">
-        <v>837606.0649999999</v>
-      </c>
-      <c r="C203" s="36" t="n">
-        <v>6517215.323</v>
-      </c>
-      <c r="D203" s="37" t="n">
-        <v>124.825</v>
-      </c>
-      <c r="E203" s="38" t="n">
-        <v>17.7134</v>
-      </c>
-      <c r="F203" s="39" t="n">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="35" t="inlineStr">
-        <is>
-          <t>4+975</t>
-        </is>
-      </c>
-      <c r="B204" s="36" t="n">
-        <v>837621.399</v>
-      </c>
-      <c r="C204" s="36" t="n">
-        <v>6517236.662</v>
-      </c>
-      <c r="D204" s="37" t="n">
-        <v>124.888</v>
-      </c>
-      <c r="E204" s="38" t="n">
-        <v>17.8068</v>
-      </c>
-      <c r="F204" s="39" t="n">
-        <v>4975</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="30" t="inlineStr">
-        <is>
-          <t>5+000</t>
-        </is>
-      </c>
-      <c r="B205" s="31" t="n">
-        <v>837636.821</v>
-      </c>
-      <c r="C205" s="31" t="n">
-        <v>6517257.96</v>
-      </c>
-      <c r="D205" s="32" t="n">
-        <v>124.95</v>
-      </c>
-      <c r="E205" s="33" t="n">
-        <v>17.9005</v>
-      </c>
-      <c r="F205" s="34" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="40" t="inlineStr">
-        <is>
-          <t>IMPORTANT : Ces coordonnées sont générées automatiquement (projet démo). Remplacer par les coordonnées réelles issues du levé topographique ou du GPS.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:F205"/>
-  <mergeCells count="3">
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>DISTANCES TRANSVERSALES / AXE — Autoroute 2x3 voies — 5 km</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
-        <is>
-          <t>SECTION EN TRAVERS TYPE — Vue schématique (de gauche à droite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="43" t="inlineStr"/>
-    </row>
-    <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ← GAUCHE (distances négatives)        AXE        DROITE (distances positives) →</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ─────────────────────────────────────── 0 ────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Bord_Prop_G ... Canal_G ... Bord_Chaussee_G   |   Bord_Chaussee_D ... Canal_D ... Bord_Prop_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>Élément</t>
-        </is>
-      </c>
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>Distance / axe (m)</t>
-        </is>
-      </c>
-      <c r="C7" s="44" t="inlineStr">
-        <is>
-          <t>Côté</t>
-        </is>
-      </c>
-      <c r="D7" s="44" t="inlineStr">
-        <is>
-          <t>Colonne cote référence</t>
-        </is>
-      </c>
-      <c r="E7" s="44" t="inlineStr">
-        <is>
-          <t>Onglet source</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t>AXE</t>
-        </is>
-      </c>
-      <c r="B8" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
-        <is>
-          <t>Axe</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="48" t="inlineStr">
-        <is>
-          <t>TPC_Gauche</t>
-        </is>
-      </c>
-      <c r="B9" s="49" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>AXE_G</t>
-        </is>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="50" t="inlineStr">
-        <is>
-          <t>TPC_Droit</t>
-        </is>
-      </c>
-      <c r="B10" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D10" s="50" t="inlineStr">
-        <is>
-          <t>AXE_D</t>
-        </is>
-      </c>
-      <c r="E10" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="48" t="inlineStr">
-        <is>
-          <t>BAU_G</t>
-        </is>
-      </c>
-      <c r="B11" s="49" t="n">
-        <v>-11</v>
-      </c>
-      <c r="C11" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_G</t>
-        </is>
-      </c>
-      <c r="E11" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t>BAU_D</t>
-        </is>
-      </c>
-      <c r="B12" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D12" s="50" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_D</t>
-        </is>
-      </c>
-      <c r="E12" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="48" t="inlineStr">
-        <is>
-          <t>Canal_G (120x120)</t>
-        </is>
-      </c>
-      <c r="B13" s="49" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="C13" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_G</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="50" t="inlineStr">
-        <is>
-          <t>Canal_D (120x120)</t>
-        </is>
-      </c>
-      <c r="B14" s="51" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="C14" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D14" s="50" t="inlineStr">
-        <is>
-          <t>Tablier_Fini_D</t>
-        </is>
-      </c>
-      <c r="E14" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="48" t="inlineStr">
-        <is>
-          <t>Accotement_G</t>
-        </is>
-      </c>
-      <c r="B15" s="49" t="n">
-        <v>-14</v>
-      </c>
-      <c r="C15" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_G</t>
-        </is>
-      </c>
-      <c r="E15" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="50" t="inlineStr">
-        <is>
-          <t>Accotement_D</t>
-        </is>
-      </c>
-      <c r="B16" s="51" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D16" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_D</t>
-        </is>
-      </c>
-      <c r="E16" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_G</t>
-        </is>
-      </c>
-      <c r="B17" s="49" t="n">
-        <v>-17</v>
-      </c>
-      <c r="C17" s="48" t="inlineStr">
-        <is>
-          <t>Gauche</t>
-        </is>
-      </c>
-      <c r="D17" s="48" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_G</t>
-        </is>
-      </c>
-      <c r="E17" s="48" t="inlineStr">
-        <is>
-          <t>Cote_Gauche</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_D</t>
-        </is>
-      </c>
-      <c r="B18" s="51" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t>Droit</t>
-        </is>
-      </c>
-      <c r="D18" s="50" t="inlineStr">
-        <is>
-          <t>Bord_Propriete_D</t>
-        </is>
-      </c>
-      <c r="E18" s="50" t="inlineStr">
-        <is>
-          <t>Cote_Droit</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="52" t="inlineStr">
-        <is>
-          <t>UTILISATION :
-• La colonne 'Distance / axe' donne la position transversale de chaque élément (- = gauche, + = droite).
-• Combinée aux coordonnées XY de PK_Coordonnees, elle permet de calculer la position GPS de chaque élément via : X_elem = X_axe + dist × sin(gisement + 90°) / Y_elem = Y_axe + dist × cos(gisement + 90°).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1"/>
-    <row r="22" ht="18" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A20:E22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:E3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>